--- a/docs/reports/WTE_Dashboard_Report.xlsx
+++ b/docs/reports/WTE_Dashboard_Report.xlsx
@@ -825,7 +825,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generato: 2026-05-13 17:38</t>
+          <t>Generato: 2026-05-14 16:40</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1431,7 +1431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2.5.1.5</t>
+          <t>8.2.11.1</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Laboratory services - testing of concrete mix and hardened concrete ECd_31</t>
+          <t>TV ECd_33</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="E2" s="13" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>132060</v>
+        <v>11980</v>
       </c>
       <c r="G2" s="5" t="n"/>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>8.2.7.1</t>
+          <t>8.7.1.5</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Open order - office supplies ECd_32</t>
+          <t>Temporary Traffic Management ECd_34</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="E3" s="13" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>90000</v>
+        <v>950</v>
       </c>
       <c r="G3" s="5" t="n"/>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>8.2.9.1</t>
+          <t>1.2.7.1</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Coffee machine rental ECd_28</t>
+          <t>Preparation of an application for an integrated permit, together with all necessary documents.</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="E4" s="13" t="n">
-        <v>46063</v>
+        <v>46066</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>50000</v>
+        <v>113000</v>
       </c>
       <c r="G4" s="5" t="n"/>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8.6.2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Laboratory services ECd_31</t>
+          <t>Foundation works</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="E5" s="13" t="n">
-        <v>46063</v>
+        <v>46068</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>49500</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="n"/>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>8.8.2.2</t>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Monitoring - installation of timelaps camera ECd_30</t>
+          <t>Diaphragm wall 100 cm thick and 6 adjacent barrettes</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1618,12 +1618,16 @@
         </is>
       </c>
       <c r="E6" s="13" t="n">
-        <v>46063</v>
+        <v>46068</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G6" s="5" t="n"/>
+        <v>3176000</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Jank Szczubiał</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -1633,12 +1637,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>8.2.11.1</t>
+          <t>2.1.2</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>TV ECd_33</t>
+          <t>Slotted wall 100 cm thick and 6 berets</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1647,12 +1651,16 @@
         </is>
       </c>
       <c r="E7" s="13" t="n">
-        <v>46064</v>
+        <v>46068</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>11980</v>
-      </c>
-      <c r="G7" s="5" t="n"/>
+        <v>1124000</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Jank Szczubiał</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -1662,12 +1670,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.5</t>
+          <t>8.1.5</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Temporary Traffic Management ECd_34</t>
+          <t>Stationary Cranes</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1676,12 +1684,16 @@
         </is>
       </c>
       <c r="E8" s="13" t="n">
-        <v>46064</v>
+        <v>46068</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>950</v>
-      </c>
-      <c r="G8" s="5" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Damian Gadowski</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1691,12 +1703,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>1.2.7.1</t>
+          <t>8.1.5.1</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Preparation of an application for an integrated permit, together with all necessary documents.</t>
+          <t>Stationary tower crane + self-erecting crane</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1705,12 +1717,16 @@
         </is>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46066</v>
+        <v>46068</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>113000</v>
-      </c>
-      <c r="G9" s="5" t="n"/>
+        <v>1170200</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Damian Gadowski</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -1720,12 +1736,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>8.2.1.1</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Foundation works</t>
+          <t>Office Space or Container Rental - Consortium's facility ECd_20</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1737,9 +1753,13 @@
         <v>46068</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="n"/>
+        <v>821840</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Urszula Szwarc</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1749,12 +1769,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2.1.1</t>
+          <t>8.2.8.1</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Diaphragm wall 100 cm thick and 6 adjacent barrettes</t>
+          <t>Cleaning services ECd_35</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1763,16 +1783,12 @@
         </is>
       </c>
       <c r="E11" s="13" t="n">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>3176000</v>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Jank Szczubiał</t>
-        </is>
-      </c>
+        <v>178200</v>
+      </c>
+      <c r="G11" s="5" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1782,12 +1798,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2.1.2</t>
+          <t>8.5.2.2</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Slotted wall 100 cm thick and 6 berets</t>
+          <t>Office kitchen furniture  ECd_36</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1796,16 +1812,12 @@
         </is>
       </c>
       <c r="E12" s="13" t="n">
-        <v>46068</v>
+        <v>46070</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>1124000</v>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Jank Szczubiał</t>
-        </is>
-      </c>
+        <v>13414.64</v>
+      </c>
+      <c r="G12" s="5" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1815,12 +1827,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>8.1.5</t>
+          <t>8.5.1</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Stationary Cranes</t>
+          <t>Internet Connection ECd_37</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1829,16 +1841,12 @@
         </is>
       </c>
       <c r="E13" s="13" t="n">
-        <v>46068</v>
+        <v>46073</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Damian Gadowski</t>
-        </is>
-      </c>
+        <v>27350</v>
+      </c>
+      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1848,12 +1856,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>8.1.5.1</t>
+          <t>8.1.3.3</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Stationary tower crane + self-erecting crane</t>
+          <t>Open order - sanitary industry assortment ECd_39</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1862,16 +1870,12 @@
         </is>
       </c>
       <c r="E14" s="13" t="n">
-        <v>46068</v>
+        <v>46077</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1170200</v>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Damian Gadowski</t>
-        </is>
-      </c>
+        <v>30000</v>
+      </c>
+      <c r="G14" s="5" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1881,12 +1885,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>8.2.1.1</t>
+          <t>8.1.3.4</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Office Space or Container Rental - Consortium's facility ECd_20</t>
+          <t>Open order - sanitary industry assortment ECd_40</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1895,16 +1899,12 @@
         </is>
       </c>
       <c r="E15" s="13" t="n">
-        <v>46068</v>
+        <v>46077</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>821840</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Urszula Szwarc</t>
-        </is>
-      </c>
+        <v>30000</v>
+      </c>
+      <c r="G15" s="5" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1914,26 +1914,30 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>8.2.8.1</t>
+          <t>5.4.1</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Cleaning services ECd_35</t>
+          <t>Boiler - pressure parts</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E16" s="13" t="n">
-        <v>46069</v>
+        <v>46081</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>178200</v>
-      </c>
-      <c r="G16" s="5" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Roger Gołombek</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1943,26 +1947,30 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>8.5.2.2</t>
+          <t>5.4.1.1</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Office kitchen furniture  ECd_36</t>
+          <t>Boiler - pressure parts</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E17" s="13" t="n">
-        <v>46070</v>
+        <v>46081</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>13414.64</v>
-      </c>
-      <c r="G17" s="5" t="n"/>
+        <v>45990000</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Roger Gołombek</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -1972,12 +1980,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>8.5.1</t>
+          <t>8.4.1.1</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Internet Connection ECd_37</t>
+          <t>Personal Occupational Health and Safety Equipment ECd_43</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1986,10 +1994,10 @@
         </is>
       </c>
       <c r="E18" s="13" t="n">
-        <v>46073</v>
+        <v>46090</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>27350</v>
+        <v>30000</v>
       </c>
       <c r="G18" s="5" t="n"/>
     </row>
@@ -2001,12 +2009,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>8.1.3.3</t>
+          <t>8.3.1.2</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Open order - sanitary industry assortment ECd_39</t>
+          <t>Generator rental ECd_44</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -2015,10 +2023,10 @@
         </is>
       </c>
       <c r="E19" s="13" t="n">
-        <v>46077</v>
+        <v>46096</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>30000</v>
+        <v>23904</v>
       </c>
       <c r="G19" s="5" t="n"/>
     </row>
@@ -2030,12 +2038,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>8.1.3.4</t>
+          <t>8.7.1.6</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Open order - sanitary industry assortment ECd_40</t>
+          <t>Purchase of road signs ECd_42</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2044,10 +2052,10 @@
         </is>
       </c>
       <c r="E20" s="13" t="n">
-        <v>46077</v>
+        <v>46096</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="G20" s="5" t="n"/>
     </row>
@@ -2059,30 +2067,26 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>8.7.1.7</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Boiler - pressure parts</t>
+          <t>Purchase of rubble for the construction of storage yards and work platforms ECd_45</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E21" s="13" t="n">
-        <v>46081</v>
+        <v>46096</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
+        <v>83200</v>
+      </c>
+      <c r="G21" s="5" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -2092,28 +2096,28 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>5.4.1.1</t>
+          <t>2.11.5.3</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Boiler - pressure parts</t>
+          <t>Concrete slab installation on the ground</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E22" s="13" t="n">
-        <v>46081</v>
+        <v>46106</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>45990000</v>
+        <v>1735392.78</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Agnieszka Zając</t>
         </is>
       </c>
     </row>
@@ -2125,12 +2129,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>8.4.1.1</t>
+          <t>2.14.2.2</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Personal Occupational Health and Safety Equipment ECd_43</t>
+          <t>External road - aggregate delivery ECd_46</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2139,12 +2143,16 @@
         </is>
       </c>
       <c r="E23" s="13" t="n">
-        <v>46090</v>
+        <v>46106</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G23" s="5" t="n"/>
+        <v>134400</v>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Agnieszka Zając</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -2154,12 +2162,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>8.3.1.2</t>
+          <t>2.4.1</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Generator rental ECd_44</t>
+          <t>Insulation - work</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -2168,12 +2176,16 @@
         </is>
       </c>
       <c r="E24" s="13" t="n">
-        <v>46096</v>
+        <v>46106</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>23904</v>
-      </c>
-      <c r="G24" s="5" t="n"/>
+        <v>733045.25</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Agnieszka Zając</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -2183,12 +2195,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.6</t>
+          <t>2.5.1.3</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Purchase of road signs ECd_42</t>
+          <t>Construction of reinforced concrete foundations and underground structures</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2197,12 +2209,16 @@
         </is>
       </c>
       <c r="E25" s="13" t="n">
-        <v>46096</v>
+        <v>46106</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G25" s="5" t="n"/>
+        <v>5276959.37</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Agnieszka Zając</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -2212,12 +2228,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.7</t>
+          <t>2.5.2.1</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Purchase of rubble for the construction of storage yards and work platforms ECd_45</t>
+          <t>Reinforced concrete structure of the above-ground part of the B1 building - delivery and assembly of prefabricated elements</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -2226,12 +2242,16 @@
         </is>
       </c>
       <c r="E26" s="13" t="n">
-        <v>46096</v>
+        <v>46106</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>83200</v>
-      </c>
-      <c r="G26" s="5" t="n"/>
+        <v>16616880</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Jan Szczubiał</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -2241,12 +2261,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2.11.5.3</t>
+          <t>2.5.2.2.3</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Concrete slab installation on the ground</t>
+          <t>Reinforced concrete structure of the above-ground part of the B3 building - delivery and assembly of prefabricated elements</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2258,11 +2278,11 @@
         <v>46106</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1735392.78</v>
+        <v>2115950</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Jan Szczubiał</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2294,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2.14.2.2</t>
+          <t>2.5.2.2.4</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>External road - aggregate delivery ECd_46</t>
+          <t>Reinforced concrete structure of the above-ground part of the other buildings</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2291,11 +2311,11 @@
         <v>46106</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>134400</v>
+        <v>708072.75</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Jan Szczubiał</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2327,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2.4.1</t>
+          <t>2.6.2.1</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Insulation - work</t>
+          <t>Precast reinforced concrete structure of facility B3 (change from steel structure compared to the acquisition stage)</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2324,11 +2344,11 @@
         <v>46106</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>733045.25</v>
+        <v>1004390</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Robert Klimczak</t>
         </is>
       </c>
     </row>
@@ -2340,12 +2360,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2.5.1.3</t>
+          <t>2.6.3.1</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Construction of reinforced concrete foundations and underground structures</t>
+          <t>Precast reinforced concrete structure of facility B4 (change from steel structure compared to the acquisition stage)</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2357,11 +2377,11 @@
         <v>46106</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>5276959.37</v>
+        <v>246780</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Robert Klimczak</t>
         </is>
       </c>
     </row>
@@ -2373,28 +2393,28 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.1</t>
+          <t>5.10.2</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the B1 building - delivery and assembly of prefabricated elements</t>
+          <t>Auxiliary crane and hoists for the maintenance of the steam turbine</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E31" s="13" t="n">
-        <v>46106</v>
+        <v>46115</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>16616880</v>
+        <v>499000</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Jan Szczubiał</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2406,28 +2426,28 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.2.3</t>
+          <t>5.2.1</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the B3 building - delivery and assembly of prefabricated elements</t>
+          <t>Overhead crane, grab and operator seat + Spare Grab</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E32" s="13" t="n">
-        <v>46106</v>
+        <v>46115</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>2115950</v>
+        <v>8701000</v>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Jan Szczubiał</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2439,28 +2459,28 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.2.4</t>
+          <t>2.14.2.1</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the other buildings</t>
+          <t>External road- sub-base construction</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E33" s="13" t="n">
-        <v>46106</v>
+        <v>46122</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>708072.75</v>
+        <v>250640</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Jan Szczubiał</t>
+          <t>Agnieszka Zając</t>
         </is>
       </c>
     </row>
@@ -2472,30 +2492,26 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>2.6.2.1</t>
+          <t>8.3.1.1</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Precast reinforced concrete structure of facility B3 (change from steel structure compared to the acquisition stage)</t>
+          <t>Electricity Costs</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E34" s="13" t="n">
-        <v>46106</v>
+        <v>46122</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1004390</v>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Robert Klimczak</t>
-        </is>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="G34" s="5" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -2505,28 +2521,28 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2.6.3.1</t>
+          <t>8.7.1.4</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Precast reinforced concrete structure of facility B4 (change from steel structure compared to the acquisition stage)</t>
+          <t>Construction of aggregate squares</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E35" s="13" t="n">
-        <v>46106</v>
+        <v>46122</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>246780</v>
+        <v>124700</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Robert Klimczak</t>
+          <t>Agnieszka Zając</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2554,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>5.10.2</t>
+          <t>8.8.4</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary crane and hoists for the maintenance of the steam turbine</t>
+          <t>Removing collisions related to site preparation and construction</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2552,173 +2568,169 @@
         </is>
       </c>
       <c r="E36" s="13" t="n">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>499000</v>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>50000</v>
+      </c>
+      <c r="G36" s="5" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>5.2.1</t>
+          <t>1.2.6</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Overhead crane, grab and operator seat + Spare Grab</t>
+          <t>Piping and ducts design</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E37" s="13" t="n">
-        <v>46115</v>
+        <v>46157</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>8701000</v>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>2000000</v>
+      </c>
+      <c r="G37" s="5" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>2.14.2.1</t>
+          <t>1.2.6.2</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>External road- sub-base construction</t>
+          <t>Piping design</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E38" s="13" t="n">
-        <v>46122</v>
+        <v>46157</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>250640</v>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>Agnieszka Zając</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>8.3.1.1</t>
+          <t>5.10.12</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Electricity Costs</t>
+          <t>Stabilising pumps 2 x 100%, network pumps 3 x 50%, condensate pumps 2 x 100%, feed water pumps 3 pcs., cooling pumps</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E39" s="13" t="n">
-        <v>46122</v>
+        <v>46157</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G39" s="5" t="n"/>
+        <v>5517325</v>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Stanisław Rucki</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.4</t>
+          <t>5.10.3</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Construction of aggregate squares</t>
+          <t>Air cooled condenser</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E40" s="13" t="n">
-        <v>46122</v>
+        <v>46157</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>124700</v>
+        <v>9000000</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>8.8.4</t>
+          <t>5.7.4</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Removing collisions related to site preparation and construction</t>
+          <t>Fly ash silos</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E41" s="13" t="n">
-        <v>46122</v>
+        <v>46157</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G41" s="5" t="n"/>
+        <v>2000000</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Roger Gołombek</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
@@ -2728,12 +2740,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>1.2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Piping and ducts design</t>
+          <t>Brick walls</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -2742,10 +2754,10 @@
         </is>
       </c>
       <c r="E42" s="13" t="n">
-        <v>46157</v>
+        <v>46173</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>2000000</v>
+        <v>687451.25</v>
       </c>
       <c r="G42" s="5" t="n"/>
     </row>
@@ -2757,12 +2769,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>1.2.6.2</t>
+          <t>3.4.3</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Piping design</t>
+          <t>Emission monitoring system (CEMS)</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2771,12 +2783,16 @@
         </is>
       </c>
       <c r="E43" s="13" t="n">
-        <v>46157</v>
+        <v>46173</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="5" t="n"/>
+        <v>1960000</v>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Radosław Zdancewicz</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -2786,12 +2802,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>5.10.12</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Stabilising pumps 2 x 100%, network pumps 3 x 50%, condensate pumps 2 x 100%, feed water pumps 3 pcs., cooling pumps</t>
+          <t>Deodorization system</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2800,10 +2816,10 @@
         </is>
       </c>
       <c r="E44" s="13" t="n">
-        <v>46157</v>
+        <v>46173</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>5517325</v>
+        <v>1009700</v>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
@@ -2819,28 +2835,28 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>5.10.3</t>
+          <t>4.2.1</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Air cooled condenser</t>
+          <t>Fire detection and alarm system</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E45" s="13" t="n">
-        <v>46157</v>
+        <v>46173</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>9000000</v>
+        <v>2211870</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2852,28 +2868,28 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>5.7.4</t>
+          <t>4.2.10</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Fly ash silos</t>
+          <t>Smoke extraction from waste bunker and tipping hall</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E46" s="13" t="n">
-        <v>46157</v>
+        <v>46173</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>2000000</v>
+        <v>1178293</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2885,26 +2901,30 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>4.2.2</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Brick walls</t>
+          <t>Firefighting water tank</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E47" s="13" t="n">
         <v>46173</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>687451.25</v>
-      </c>
-      <c r="G47" s="5" t="n"/>
+        <v>275700</v>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -2914,28 +2934,28 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>3.4.3</t>
+          <t>4.2.3</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Emission monitoring system (CEMS)</t>
+          <t>Firefighting water pumping</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E48" s="13" t="n">
         <v>46173</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>1960000</v>
+        <v>715920</v>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Radosław Zdancewicz</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2947,28 +2967,28 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.2.4</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Deodorization system</t>
+          <t>Firefighting water external distribution, hoses, sprinklers</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E49" s="13" t="n">
         <v>46173</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1009700</v>
+        <v>821016</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2980,12 +3000,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>4.2.5</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Fire detection and alarm system</t>
+          <t>Installation of internal hydrants in buildings B1 and B2</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -2997,7 +3017,7 @@
         <v>46173</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>2211870</v>
+        <v>240990</v>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
@@ -3013,12 +3033,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>4.2.10</t>
+          <t>4.2.6</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Smoke extraction from waste bunker and tipping hall</t>
+          <t>Wireless radio controller system type WRC, gun control</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -3030,7 +3050,7 @@
         <v>46173</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1178293</v>
+        <v>45500</v>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
@@ -3046,12 +3066,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>4.2.2</t>
+          <t>4.2.7</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water tank</t>
+          <t>Firefighting water external distribution, hoses, sprinklers</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -3063,7 +3083,7 @@
         <v>46173</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>275700</v>
+        <v>542750</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
@@ -3079,12 +3099,12 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>4.2.3</t>
+          <t>4.2.8</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water pumping</t>
+          <t>Dry bunker sprinkler system. Installation of water and foam cannons in the bunker hall, and assembly of the valve sub-control unit.</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3096,7 +3116,7 @@
         <v>46173</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>715920</v>
+        <v>1925350</v>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
@@ -3112,12 +3132,12 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>4.2.4</t>
+          <t>4.2.9</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water external distribution, hoses, sprinklers</t>
+          <t>Natural gas (if any) and ammonia detection system</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -3129,7 +3149,7 @@
         <v>46173</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>821016</v>
+        <v>285000</v>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
@@ -3145,28 +3165,28 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>4.2.5</t>
+          <t>5.10.13.5</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Installation of internal hydrants in buildings B1 and B2</t>
+          <t>Control valves</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E55" s="13" t="n">
         <v>46173</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>240990</v>
+        <v>700000</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -3178,30 +3198,26 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>4.2.6</t>
+          <t>5.2.2</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Wireless radio controller system type WRC, gun control</t>
+          <t>Trapdoors for grab maintenance</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E56" s="13" t="n">
         <v>46173</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>45500</v>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>81600</v>
+      </c>
+      <c r="G56" s="5" t="n"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
@@ -3211,30 +3227,26 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>4.2.7</t>
+          <t>5.3.6</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water external distribution, hoses, sprinklers</t>
+          <t>Primary &amp; secondary air dampers</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E57" s="13" t="n">
         <v>46173</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>542750</v>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>220000</v>
+      </c>
+      <c r="G57" s="5" t="n"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -3244,30 +3256,26 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>4.2.8</t>
+          <t>5.3.7</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Dry bunker sprinkler system. Installation of water and foam cannons in the bunker hall, and assembly of the valve sub-control unit.</t>
+          <t>Flue gas recirculation dampers</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E58" s="13" t="n">
         <v>46173</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>1925350</v>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>40000</v>
+      </c>
+      <c r="G58" s="5" t="n"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
@@ -3277,28 +3285,28 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>4.2.9</t>
+          <t>5.10.8</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Natural gas (if any) and ammonia detection system</t>
+          <t>Cooler tank, condensate tank</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E59" s="13" t="n">
-        <v>46173</v>
+        <v>46188</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>285000</v>
+        <v>1000000</v>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -3310,12 +3318,12 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>5.10.13.5</t>
+          <t>5.13.4</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Control valves</t>
+          <t>Auxiliary fuel pumps (light oil/diesel oil), demi water pumps, other water pumps</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -3324,14 +3332,14 @@
         </is>
       </c>
       <c r="E60" s="13" t="n">
-        <v>46173</v>
+        <v>46188</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>700000</v>
+        <v>3337500</v>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3351,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>5.2.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Trapdoors for grab maintenance</t>
+          <t>Notification Bodies</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -3357,10 +3365,10 @@
         </is>
       </c>
       <c r="E61" s="13" t="n">
-        <v>46173</v>
+        <v>46201</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>81600</v>
+        <v>350000</v>
       </c>
       <c r="G61" s="5" t="n"/>
     </row>
@@ -3372,12 +3380,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>5.3.6</t>
+          <t>5.10.11</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Primary &amp; secondary air dampers</t>
+          <t>Heat exchangers 2 pcs., LP pre-heater, external economizer</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -3386,12 +3394,16 @@
         </is>
       </c>
       <c r="E62" s="13" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>220000</v>
-      </c>
-      <c r="G62" s="5" t="n"/>
+        <v>3242866</v>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>Stanisław Rucki</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
@@ -3401,12 +3413,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>5.3.7</t>
+          <t>5.13.3</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Flue gas recirculation dampers</t>
+          <t>Light oil unloading installation with TDT documentation approval</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -3415,10 +3427,10 @@
         </is>
       </c>
       <c r="E63" s="13" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>40000</v>
+        <v>200000</v>
       </c>
       <c r="G63" s="5" t="n"/>
     </row>
@@ -3430,12 +3442,12 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>5.10.8</t>
+          <t>5.4.4</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Cooler tank, condensate tank</t>
+          <t>Sampling system</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3444,14 +3456,14 @@
         </is>
       </c>
       <c r="E64" s="13" t="n">
-        <v>46188</v>
+        <v>46203</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>1000000</v>
+        <v>1010500</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3475,12 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>5.13.4</t>
+          <t>5.4.5</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary fuel pumps (light oil/diesel oil), demi water pumps, other water pumps</t>
+          <t>Chemical dosing for the boiler</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -3477,14 +3489,14 @@
         </is>
       </c>
       <c r="E65" s="13" t="n">
-        <v>46188</v>
+        <v>46203</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>3337500</v>
+        <v>223600</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -3496,12 +3508,12 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>5.7.1</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Notification Bodies</t>
+          <t>SNCR DeNOx system including silo, pumps</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -3510,12 +3522,16 @@
         </is>
       </c>
       <c r="E66" s="13" t="n">
-        <v>46201</v>
+        <v>46203</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>350000</v>
-      </c>
-      <c r="G66" s="5" t="n"/>
+        <v>1090000</v>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
@@ -3525,12 +3541,12 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>5.10.11</t>
+          <t>4.3.1</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Heat exchangers 2 pcs., LP pre-heater, external economizer</t>
+          <t>Boiler room roof ventilators and wall shutters</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -3539,14 +3555,14 @@
         </is>
       </c>
       <c r="E67" s="13" t="n">
-        <v>46203</v>
+        <v>46218</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>3242866</v>
+        <v>1500000</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Magdalena Przeździak</t>
         </is>
       </c>
     </row>
@@ -3558,12 +3574,12 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>5.13.3</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Light oil unloading installation with TDT documentation approval</t>
+          <t>HVAC for the technological buildings</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -3572,12 +3588,16 @@
         </is>
       </c>
       <c r="E68" s="13" t="n">
-        <v>46203</v>
+        <v>46218</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G68" s="5" t="n"/>
+        <v>3107033</v>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Przeździak</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -3587,12 +3607,12 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>5.4.4</t>
+          <t>4.3.3</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Sampling system</t>
+          <t xml:space="preserve">HVAC for the other buildings </t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -3601,14 +3621,14 @@
         </is>
       </c>
       <c r="E69" s="13" t="n">
-        <v>46203</v>
+        <v>46218</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1010500</v>
+        <v>1548256</v>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Magdalena Przeździak</t>
         </is>
       </c>
     </row>
@@ -3620,12 +3640,12 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>5.4.5</t>
+          <t>2.11.1</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Chemical dosing for the boiler</t>
+          <t>Painting</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -3634,10 +3654,10 @@
         </is>
       </c>
       <c r="E70" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>223600</v>
+        <v>669442.8</v>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
@@ -3653,12 +3673,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>5.7.1</t>
+          <t>2.11.10</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>SNCR DeNOx system including silo, pumps</t>
+          <t>Plasterboard wall, sandwich panel wall</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -3667,16 +3687,12 @@
         </is>
       </c>
       <c r="E71" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>39026.75</v>
+      </c>
+      <c r="G71" s="5" t="n"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -3686,12 +3702,12 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>4.3.1</t>
+          <t>2.11.11</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Boiler room roof ventilators and wall shutters</t>
+          <t>Glass wall</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -3700,16 +3716,12 @@
         </is>
       </c>
       <c r="E72" s="13" t="n">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Przeździak</t>
-        </is>
-      </c>
+        <v>75045.3</v>
+      </c>
+      <c r="G72" s="5" t="n"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -3719,12 +3731,12 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>4.3.2</t>
+          <t>2.11.12</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>HVAC for the technological buildings</t>
+          <t>Plastering</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -3733,14 +3745,14 @@
         </is>
       </c>
       <c r="E73" s="13" t="n">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>3107033</v>
+        <v>1241084.64</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Przeździak</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -3752,12 +3764,12 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>4.3.3</t>
+          <t>2.11.13</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HVAC for the other buildings </t>
+          <t>Carpet / polyamide</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3766,16 +3778,12 @@
         </is>
       </c>
       <c r="E74" s="13" t="n">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>1548256</v>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Przeździak</t>
-        </is>
-      </c>
+        <v>87497.52</v>
+      </c>
+      <c r="G74" s="5" t="n"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
@@ -3785,12 +3793,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>2.11.1</t>
+          <t>2.11.14</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Painting</t>
+          <t>Wall and column protection up to 2.5 m + hydrophobic protection</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -3802,13 +3810,9 @@
         <v>46234</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>669442.8</v>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>186490.48</v>
+      </c>
+      <c r="G75" s="5" t="n"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
@@ -3818,12 +3822,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>2.11.10</t>
+          <t>2.11.2</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Plasterboard wall, sandwich panel wall</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -3835,9 +3839,13 @@
         <v>46234</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>39026.75</v>
-      </c>
-      <c r="G76" s="5" t="n"/>
+        <v>631074</v>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
@@ -3847,12 +3855,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>2.11.11</t>
+          <t>2.11.3</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Glass wall</t>
+          <t>Tiles</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -3864,9 +3872,13 @@
         <v>46234</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>75045.3</v>
-      </c>
-      <c r="G77" s="5" t="n"/>
+        <v>498448.22</v>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -3876,12 +3888,12 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>2.11.12</t>
+          <t>2.11.4</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Plastering</t>
+          <t>Raised floor</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -3893,7 +3905,7 @@
         <v>46234</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>1241084.64</v>
+        <v>621907.75</v>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
@@ -3909,24 +3921,24 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>2.11.13</t>
+          <t>2.11.5</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Carpet / polyamide</t>
+          <t>Concrete floor + screed</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E79" s="13" t="n">
         <v>46234</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>87497.52</v>
+        <v>610629.23</v>
       </c>
       <c r="G79" s="5" t="n"/>
     </row>
@@ -3938,12 +3950,12 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>2.11.14</t>
+          <t>2.11.5.4</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Wall and column protection up to 2.5 m + hydrophobic protection</t>
+          <t>Concrete flooring and screed with insulation</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -3955,7 +3967,7 @@
         <v>46234</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>186490.48</v>
+        <v>0</v>
       </c>
       <c r="G80" s="5" t="n"/>
     </row>
@@ -3967,12 +3979,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>2.11.2</t>
+          <t>2.11.6</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Microcement floor</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3984,13 +3996,9 @@
         <v>46234</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>631074</v>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>133705.44</v>
+      </c>
+      <c r="G81" s="5" t="n"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
@@ -4000,12 +4008,12 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>2.11.3</t>
+          <t>2.11.7</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Tiles</t>
+          <t>Resin floor</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -4017,7 +4025,7 @@
         <v>46234</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>498448.22</v>
+        <v>655174.75</v>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
@@ -4033,12 +4041,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>2.11.4</t>
+          <t>2.11.8</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Raised floor</t>
+          <t>Suspended ceilings</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -4050,13 +4058,9 @@
         <v>46234</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>621907.75</v>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>220670.05</v>
+      </c>
+      <c r="G83" s="5" t="n"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
@@ -4066,24 +4070,24 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>2.11.5</t>
+          <t>2.11.9</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Concrete floor + screed</t>
+          <t>Segmented sliding wall</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E84" s="13" t="n">
         <v>46234</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>610629.23</v>
+        <v>65014.1</v>
       </c>
       <c r="G84" s="5" t="n"/>
     </row>
@@ -4095,26 +4099,30 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>2.11.5.4</t>
+          <t>2.12.1</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Concrete flooring and screed with insulation</t>
+          <t>Passenger and good elevator</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E85" s="13" t="n">
         <v>46234</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="5" t="n"/>
+        <v>415350</v>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Izabela Malarecka</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
@@ -4124,26 +4132,30 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>2.11.6</t>
+          <t>2.12.2</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Microcement floor</t>
+          <t>Passenger elevator</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E86" s="13" t="n">
         <v>46234</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>133705.44</v>
-      </c>
-      <c r="G86" s="5" t="n"/>
+        <v>98643.60000000001</v>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>Izabela Malarecka</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
@@ -4153,12 +4165,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>2.11.7</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Resin floor</t>
+          <t>Weigh bridge</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -4170,11 +4182,11 @@
         <v>46234</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>655174.75</v>
+        <v>551900</v>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -4186,12 +4198,12 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>2.11.8</t>
+          <t>3.4.2</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Suspended ceilings</t>
+          <t>DCS System</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -4203,9 +4215,13 @@
         <v>46234</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>220670.05</v>
-      </c>
-      <c r="G88" s="5" t="n"/>
+        <v>2752000</v>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>Roger Gołombek</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
@@ -4215,12 +4231,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>2.11.9</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Segmented sliding wall</t>
+          <t>Radioactivity detector</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -4232,7 +4248,7 @@
         <v>46234</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>65014.1</v>
+        <v>185000</v>
       </c>
       <c r="G89" s="5" t="n"/>
     </row>
@@ -4244,28 +4260,28 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>2.12.1</t>
+          <t>5.10.6</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Passenger and good elevator</t>
+          <t>Chemical dossing for thermal cycle and district heating</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E90" s="13" t="n">
         <v>46234</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>415350</v>
+        <v>550000</v>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Izabela Malarecka</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -4277,28 +4293,28 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>2.12.2</t>
+          <t>5.13.9</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Passenger elevator</t>
+          <t>Grate cooling system</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E91" s="13" t="n">
         <v>46234</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>98643.60000000001</v>
+        <v>731000</v>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Izabela Malarecka</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -4310,12 +4326,12 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>5.14.2</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Weigh bridge</t>
+          <t>Mechanical installation of technological equipment</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -4327,7 +4343,7 @@
         <v>46234</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>551900</v>
+        <v>1500000</v>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
@@ -4343,12 +4359,12 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>3.4.2</t>
+          <t>5.3.4</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>DCS System</t>
+          <t>Primary / secondary air ducts + Flue gas recirculation ducts + Auxiliary burners ducts + Supporting structures</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -4360,11 +4376,11 @@
         <v>46234</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>2752000</v>
+        <v>2502500</v>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -4376,12 +4392,12 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>5.3.5</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Radioactivity detector</t>
+          <t>Fire curtain for primary air opening</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -4393,9 +4409,13 @@
         <v>46234</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>185000</v>
-      </c>
-      <c r="G94" s="5" t="n"/>
+        <v>100000</v>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Przeździak</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
@@ -4405,12 +4425,12 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>5.10.6</t>
+          <t>5.3.8</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Chemical dossing for thermal cycle and district heating</t>
+          <t>Camera for furnace monitoring</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -4422,13 +4442,9 @@
         <v>46234</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>550000</v>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>51600</v>
+      </c>
+      <c r="G95" s="5" t="n"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
@@ -4438,12 +4454,12 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>5.13.9</t>
+          <t>5.4.6</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Grate cooling system</t>
+          <t>Compensator between boiler and ECO</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -4455,13 +4471,9 @@
         <v>46234</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>731000</v>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>129000</v>
+      </c>
+      <c r="G96" s="5" t="n"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
@@ -4471,12 +4483,12 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>5.14.2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Mechanical installation of technological equipment</t>
+          <t>Refractory</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -4488,166 +4500,9 @@
         <v>46234</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>1500000</v>
+        <v>3993000</v>
       </c>
       <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>5.3.4</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>Primary / secondary air ducts + Flue gas recirculation ducts + Auxiliary burners ducts + Supporting structures</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E98" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F98" s="6" t="n">
-        <v>2502500</v>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>5.3.5</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>Fire curtain for primary air opening</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E99" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F99" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Przeździak</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>5.3.8</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>Camera for furnace monitoring</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E100" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F100" s="6" t="n">
-        <v>51600</v>
-      </c>
-      <c r="G100" s="5" t="n"/>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>5.4.6</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>Compensator between boiler and ECO</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E101" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F101" s="6" t="n">
-        <v>129000</v>
-      </c>
-      <c r="G101" s="5" t="n"/>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>Refractory</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E102" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F102" s="6" t="n">
-        <v>3993000</v>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
         <is>
           <t>Magdalena Białorucka</t>
         </is>
@@ -7823,16 +7678,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -10749,156 +10604,6 @@
       </c>
       <c r="G97" s="5">
         <f>'10_Source_Orders_3M'!G97</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="5">
-        <f>'10_Source_Orders_3M'!A98</f>
-        <v/>
-      </c>
-      <c r="B98" s="5">
-        <f>'10_Source_Orders_3M'!B98</f>
-        <v/>
-      </c>
-      <c r="C98" s="5">
-        <f>'10_Source_Orders_3M'!C98</f>
-        <v/>
-      </c>
-      <c r="D98" s="5">
-        <f>'10_Source_Orders_3M'!D98</f>
-        <v/>
-      </c>
-      <c r="E98" s="13">
-        <f>'10_Source_Orders_3M'!E98</f>
-        <v/>
-      </c>
-      <c r="F98" s="6">
-        <f>'10_Source_Orders_3M'!F98</f>
-        <v/>
-      </c>
-      <c r="G98" s="5">
-        <f>'10_Source_Orders_3M'!G98</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="5">
-        <f>'10_Source_Orders_3M'!A99</f>
-        <v/>
-      </c>
-      <c r="B99" s="5">
-        <f>'10_Source_Orders_3M'!B99</f>
-        <v/>
-      </c>
-      <c r="C99" s="5">
-        <f>'10_Source_Orders_3M'!C99</f>
-        <v/>
-      </c>
-      <c r="D99" s="5">
-        <f>'10_Source_Orders_3M'!D99</f>
-        <v/>
-      </c>
-      <c r="E99" s="13">
-        <f>'10_Source_Orders_3M'!E99</f>
-        <v/>
-      </c>
-      <c r="F99" s="6">
-        <f>'10_Source_Orders_3M'!F99</f>
-        <v/>
-      </c>
-      <c r="G99" s="5">
-        <f>'10_Source_Orders_3M'!G99</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="5">
-        <f>'10_Source_Orders_3M'!A100</f>
-        <v/>
-      </c>
-      <c r="B100" s="5">
-        <f>'10_Source_Orders_3M'!B100</f>
-        <v/>
-      </c>
-      <c r="C100" s="5">
-        <f>'10_Source_Orders_3M'!C100</f>
-        <v/>
-      </c>
-      <c r="D100" s="5">
-        <f>'10_Source_Orders_3M'!D100</f>
-        <v/>
-      </c>
-      <c r="E100" s="13">
-        <f>'10_Source_Orders_3M'!E100</f>
-        <v/>
-      </c>
-      <c r="F100" s="6">
-        <f>'10_Source_Orders_3M'!F100</f>
-        <v/>
-      </c>
-      <c r="G100" s="5">
-        <f>'10_Source_Orders_3M'!G100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="5">
-        <f>'10_Source_Orders_3M'!A101</f>
-        <v/>
-      </c>
-      <c r="B101" s="5">
-        <f>'10_Source_Orders_3M'!B101</f>
-        <v/>
-      </c>
-      <c r="C101" s="5">
-        <f>'10_Source_Orders_3M'!C101</f>
-        <v/>
-      </c>
-      <c r="D101" s="5">
-        <f>'10_Source_Orders_3M'!D101</f>
-        <v/>
-      </c>
-      <c r="E101" s="13">
-        <f>'10_Source_Orders_3M'!E101</f>
-        <v/>
-      </c>
-      <c r="F101" s="6">
-        <f>'10_Source_Orders_3M'!F101</f>
-        <v/>
-      </c>
-      <c r="G101" s="5">
-        <f>'10_Source_Orders_3M'!G101</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="5">
-        <f>'10_Source_Orders_3M'!A102</f>
-        <v/>
-      </c>
-      <c r="B102" s="5">
-        <f>'10_Source_Orders_3M'!B102</f>
-        <v/>
-      </c>
-      <c r="C102" s="5">
-        <f>'10_Source_Orders_3M'!C102</f>
-        <v/>
-      </c>
-      <c r="D102" s="5">
-        <f>'10_Source_Orders_3M'!D102</f>
-        <v/>
-      </c>
-      <c r="E102" s="13">
-        <f>'10_Source_Orders_3M'!E102</f>
-        <v/>
-      </c>
-      <c r="F102" s="6">
-        <f>'10_Source_Orders_3M'!F102</f>
-        <v/>
-      </c>
-      <c r="G102" s="5">
-        <f>'10_Source_Orders_3M'!G102</f>
         <v/>
       </c>
     </row>

--- a/docs/reports/WTE_Dashboard_Report.xlsx
+++ b/docs/reports/WTE_Dashboard_Report.xlsx
@@ -825,7 +825,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generato: 2026-05-14 16:40</t>
+          <t>Generato: 2026-05-15 13:43</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1431,7 +1431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>8.2.11.1</t>
+          <t>1.2.7.1</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>TV ECd_33</t>
+          <t>Preparation of an application for an integrated permit, together with all necessary documents.</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="E2" s="13" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>11980</v>
+        <v>113000</v>
       </c>
       <c r="G2" s="5" t="n"/>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.5</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Temporary Traffic Management ECd_34</t>
+          <t>Foundation works</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="E3" s="13" t="n">
-        <v>46064</v>
+        <v>46068</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="G3" s="5" t="n"/>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>1.2.7.1</t>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Preparation of an application for an integrated permit, together with all necessary documents.</t>
+          <t>Diaphragm wall 100 cm thick and 6 adjacent barrettes</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1560,12 +1560,16 @@
         </is>
       </c>
       <c r="E4" s="13" t="n">
-        <v>46066</v>
+        <v>46068</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>113000</v>
-      </c>
-      <c r="G4" s="5" t="n"/>
+        <v>3176000</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Jank Szczubiał</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -1575,12 +1579,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.1.2</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Foundation works</t>
+          <t>Slotted wall 100 cm thick and 6 berets</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1592,9 +1596,13 @@
         <v>46068</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n"/>
+        <v>1124000</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Jank Szczubiał</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -1604,12 +1612,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2.1.1</t>
+          <t>8.1.5</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Diaphragm wall 100 cm thick and 6 adjacent barrettes</t>
+          <t>Stationary Cranes</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1621,11 +1629,11 @@
         <v>46068</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>3176000</v>
+        <v>0</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Jank Szczubiał</t>
+          <t>Damian Gadowski</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1645,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2.1.2</t>
+          <t>8.1.5.1</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Slotted wall 100 cm thick and 6 berets</t>
+          <t>Stationary tower crane + self-erecting crane</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1654,11 +1662,11 @@
         <v>46068</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1124000</v>
+        <v>1170200</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Jank Szczubiał</t>
+          <t>Damian Gadowski</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1678,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>8.1.5</t>
+          <t>8.2.1.1</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Stationary Cranes</t>
+          <t>Office Space or Container Rental - Consortium's facility ECd_20</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1687,11 +1695,11 @@
         <v>46068</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0</v>
+        <v>821840</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Damian Gadowski</t>
+          <t>Urszula Szwarc</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1711,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>8.1.5.1</t>
+          <t>8.2.8.1</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Stationary tower crane + self-erecting crane</t>
+          <t>Cleaning services ECd_35</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1717,16 +1725,12 @@
         </is>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1170200</v>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Damian Gadowski</t>
-        </is>
-      </c>
+        <v>178200</v>
+      </c>
+      <c r="G9" s="5" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -1736,12 +1740,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>8.2.1.1</t>
+          <t>8.5.2.2</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Office Space or Container Rental - Consortium's facility ECd_20</t>
+          <t>Office kitchen furniture  ECd_36</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1750,16 +1754,12 @@
         </is>
       </c>
       <c r="E10" s="13" t="n">
-        <v>46068</v>
+        <v>46070</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>821840</v>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Urszula Szwarc</t>
-        </is>
-      </c>
+        <v>13414.64</v>
+      </c>
+      <c r="G10" s="5" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>8.2.8.1</t>
+          <t>8.5.1</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Cleaning services ECd_35</t>
+          <t>Internet Connection ECd_37</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="E11" s="13" t="n">
-        <v>46069</v>
+        <v>46073</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>178200</v>
+        <v>27350</v>
       </c>
       <c r="G11" s="5" t="n"/>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>8.5.2.2</t>
+          <t>8.1.3.3</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Office kitchen furniture  ECd_36</t>
+          <t>Open order - sanitary industry assortment ECd_39</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="E12" s="13" t="n">
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>13414.64</v>
+        <v>30000</v>
       </c>
       <c r="G12" s="5" t="n"/>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>8.5.1</t>
+          <t>8.1.3.4</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Internet Connection ECd_37</t>
+          <t>Open order - sanitary industry assortment ECd_40</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="E13" s="13" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>27350</v>
+        <v>30000</v>
       </c>
       <c r="G13" s="5" t="n"/>
     </row>
@@ -1856,26 +1856,30 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>8.1.3.3</t>
+          <t>5.4.1</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Open order - sanitary industry assortment ECd_39</t>
+          <t>Boiler - pressure parts</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E14" s="13" t="n">
-        <v>46077</v>
+        <v>46081</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G14" s="5" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Roger Gołombek</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1885,26 +1889,30 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>8.1.3.4</t>
+          <t>5.4.1.1</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Open order - sanitary industry assortment ECd_40</t>
+          <t>Boiler - pressure parts</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E15" s="13" t="n">
-        <v>46077</v>
+        <v>46081</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G15" s="5" t="n"/>
+        <v>45990000</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Roger Gołombek</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1914,30 +1922,26 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>8.4.1.1</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Boiler - pressure parts</t>
+          <t>Personal Occupational Health and Safety Equipment ECd_43</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E16" s="13" t="n">
-        <v>46081</v>
+        <v>46090</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
+        <v>30000</v>
+      </c>
+      <c r="G16" s="5" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1947,30 +1951,26 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>5.4.1.1</t>
+          <t>8.3.1.2</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Boiler - pressure parts</t>
+          <t>Generator rental ECd_44</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E17" s="13" t="n">
-        <v>46081</v>
+        <v>46096</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
+        <v>23904</v>
+      </c>
+      <c r="G17" s="5" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>8.4.1.1</t>
+          <t>8.7.1.6</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Personal Occupational Health and Safety Equipment ECd_43</t>
+          <t>Purchase of road signs ECd_42</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="E18" s="13" t="n">
-        <v>46090</v>
+        <v>46096</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="G18" s="5" t="n"/>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>8.3.1.2</t>
+          <t>8.7.1.7</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Generator rental ECd_44</t>
+          <t>Purchase of rubble for the construction of storage yards and work platforms ECd_45</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -2026,7 +2026,7 @@
         <v>46096</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>23904</v>
+        <v>83200</v>
       </c>
       <c r="G19" s="5" t="n"/>
     </row>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.6</t>
+          <t>2.11.5.3</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Purchase of road signs ECd_42</t>
+          <t>Concrete slab installation on the ground</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2052,12 +2052,16 @@
         </is>
       </c>
       <c r="E20" s="13" t="n">
-        <v>46096</v>
+        <v>46106</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G20" s="5" t="n"/>
+        <v>1735392.78</v>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Agnieszka Zając</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -2067,12 +2071,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.7</t>
+          <t>2.14.2.2</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Purchase of rubble for the construction of storage yards and work platforms ECd_45</t>
+          <t>External road - aggregate delivery ECd_46</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -2081,12 +2085,16 @@
         </is>
       </c>
       <c r="E21" s="13" t="n">
-        <v>46096</v>
+        <v>46106</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>83200</v>
-      </c>
-      <c r="G21" s="5" t="n"/>
+        <v>134400</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Agnieszka Zając</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -2096,12 +2104,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2.11.5.3</t>
+          <t>2.4.1</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Concrete slab installation on the ground</t>
+          <t>Insulation - work</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2113,7 +2121,7 @@
         <v>46106</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1735392.78</v>
+        <v>733045.25</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
@@ -2129,12 +2137,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2.14.2.2</t>
+          <t>2.5.1.3</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>External road - aggregate delivery ECd_46</t>
+          <t>Construction of reinforced concrete foundations and underground structures</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2146,7 +2154,7 @@
         <v>46106</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>134400</v>
+        <v>5276959.37</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
@@ -2162,12 +2170,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2.4.1</t>
+          <t>2.5.2.1</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Insulation - work</t>
+          <t>Reinforced concrete structure of the above-ground part of the B1 building - delivery and assembly of prefabricated elements</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -2179,11 +2187,11 @@
         <v>46106</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>733045.25</v>
+        <v>16616880</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Jan Szczubiał</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2203,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2.5.1.3</t>
+          <t>2.5.2.2.3</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Construction of reinforced concrete foundations and underground structures</t>
+          <t>Reinforced concrete structure of the above-ground part of the B3 building - delivery and assembly of prefabricated elements</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2212,11 +2220,11 @@
         <v>46106</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>5276959.37</v>
+        <v>2115950</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Jan Szczubiał</t>
         </is>
       </c>
     </row>
@@ -2228,12 +2236,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.1</t>
+          <t>2.5.2.2.4</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the B1 building - delivery and assembly of prefabricated elements</t>
+          <t>Reinforced concrete structure of the above-ground part of the other buildings</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -2245,7 +2253,7 @@
         <v>46106</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>16616880</v>
+        <v>708072.75</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
@@ -2261,12 +2269,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.2.3</t>
+          <t>2.6.2.1</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the B3 building - delivery and assembly of prefabricated elements</t>
+          <t>Precast reinforced concrete structure of facility B3 (change from steel structure compared to the acquisition stage)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2278,11 +2286,11 @@
         <v>46106</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>2115950</v>
+        <v>1004390</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Jan Szczubiał</t>
+          <t>Robert Klimczak</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2302,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.2.4</t>
+          <t>2.6.3.1</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the other buildings</t>
+          <t>Precast reinforced concrete structure of facility B4 (change from steel structure compared to the acquisition stage)</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2311,11 +2319,11 @@
         <v>46106</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>708072.75</v>
+        <v>246780</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Jan Szczubiał</t>
+          <t>Robert Klimczak</t>
         </is>
       </c>
     </row>
@@ -2327,28 +2335,28 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2.6.2.1</t>
+          <t>5.10.2</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Precast reinforced concrete structure of facility B3 (change from steel structure compared to the acquisition stage)</t>
+          <t>Auxiliary crane and hoists for the maintenance of the steam turbine</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E29" s="13" t="n">
-        <v>46106</v>
+        <v>46115</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1004390</v>
+        <v>499000</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Robert Klimczak</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2360,28 +2368,28 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2.6.3.1</t>
+          <t>5.2.1</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Precast reinforced concrete structure of facility B4 (change from steel structure compared to the acquisition stage)</t>
+          <t>Overhead crane, grab and operator seat + Spare Grab</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E30" s="13" t="n">
-        <v>46106</v>
+        <v>46115</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>246780</v>
+        <v>8701000</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Robert Klimczak</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2393,12 +2401,12 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>5.10.2</t>
+          <t>2.14.2.1</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary crane and hoists for the maintenance of the steam turbine</t>
+          <t>External road- sub-base construction</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -2407,14 +2415,14 @@
         </is>
       </c>
       <c r="E31" s="13" t="n">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>499000</v>
+        <v>250640</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Agnieszka Zając</t>
         </is>
       </c>
     </row>
@@ -2426,12 +2434,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>5.2.1</t>
+          <t>8.3.1.1</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Overhead crane, grab and operator seat + Spare Grab</t>
+          <t>Electricity Costs</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2440,16 +2448,12 @@
         </is>
       </c>
       <c r="E32" s="13" t="n">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>8701000</v>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="G32" s="5" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -2459,12 +2463,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2.14.2.1</t>
+          <t>8.7.1.4</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>External road- sub-base construction</t>
+          <t>Construction of aggregate squares</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2476,7 +2480,7 @@
         <v>46122</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>250640</v>
+        <v>124700</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
@@ -2492,12 +2496,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8.3.1.1</t>
+          <t>8.8.4</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Electricity Costs</t>
+          <t>Removing collisions related to site preparation and construction</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2509,71 +2513,71 @@
         <v>46122</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G34" s="5" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.4</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Construction of aggregate squares</t>
+          <t>Brick walls</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E35" s="13" t="n">
-        <v>46122</v>
+        <v>46173</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>124700</v>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>Agnieszka Zając</t>
-        </is>
-      </c>
+        <v>687451.25</v>
+      </c>
+      <c r="G35" s="5" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>8.8.4</t>
+          <t>3.4.3</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Removing collisions related to site preparation and construction</t>
+          <t>Emission monitoring system (CEMS)</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E36" s="13" t="n">
-        <v>46122</v>
+        <v>46173</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G36" s="5" t="n"/>
+        <v>1960000</v>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Radosław Zdancewicz</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -2583,12 +2587,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>1.2.6</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Piping and ducts design</t>
+          <t>Deodorization system</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2597,12 +2601,16 @@
         </is>
       </c>
       <c r="E37" s="13" t="n">
-        <v>46157</v>
+        <v>46173</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="G37" s="5" t="n"/>
+        <v>1009700</v>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Stanisław Rucki</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -2612,26 +2620,30 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>1.2.6.2</t>
+          <t>4.2.1</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Piping design</t>
+          <t>Fire detection and alarm system</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E38" s="13" t="n">
-        <v>46157</v>
+        <v>46173</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="5" t="n"/>
+        <v>2211870</v>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
@@ -2641,28 +2653,28 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>5.10.12</t>
+          <t>4.2.10</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Stabilising pumps 2 x 100%, network pumps 3 x 50%, condensate pumps 2 x 100%, feed water pumps 3 pcs., cooling pumps</t>
+          <t>Smoke extraction from waste bunker and tipping hall</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E39" s="13" t="n">
-        <v>46157</v>
+        <v>46173</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>5517325</v>
+        <v>1178293</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2674,28 +2686,28 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>5.10.3</t>
+          <t>4.2.2</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Air cooled condenser</t>
+          <t>Firefighting water tank</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E40" s="13" t="n">
-        <v>46157</v>
+        <v>46173</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>9000000</v>
+        <v>275700</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2707,28 +2719,28 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>5.7.4</t>
+          <t>4.2.3</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Fly ash silos</t>
+          <t>Firefighting water pumping</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E41" s="13" t="n">
-        <v>46157</v>
+        <v>46173</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>2000000</v>
+        <v>715920</v>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2740,26 +2752,30 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>4.2.4</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Brick walls</t>
+          <t>Firefighting water external distribution, hoses, sprinklers</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E42" s="13" t="n">
         <v>46173</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>687451.25</v>
-      </c>
-      <c r="G42" s="5" t="n"/>
+        <v>821016</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -2769,28 +2785,28 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>3.4.3</t>
+          <t>4.2.5</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Emission monitoring system (CEMS)</t>
+          <t>Installation of internal hydrants in buildings B1 and B2</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E43" s="13" t="n">
         <v>46173</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>1960000</v>
+        <v>240990</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Radosław Zdancewicz</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2802,28 +2818,28 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.2.6</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Deodorization system</t>
+          <t>Wireless radio controller system type WRC, gun control</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E44" s="13" t="n">
         <v>46173</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>1009700</v>
+        <v>45500</v>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2835,12 +2851,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>4.2.7</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Fire detection and alarm system</t>
+          <t>Firefighting water external distribution, hoses, sprinklers</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2852,7 +2868,7 @@
         <v>46173</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>2211870</v>
+        <v>542750</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
@@ -2868,12 +2884,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>4.2.10</t>
+          <t>4.2.8</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Smoke extraction from waste bunker and tipping hall</t>
+          <t>Dry bunker sprinkler system. Installation of water and foam cannons in the bunker hall, and assembly of the valve sub-control unit.</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2885,7 +2901,7 @@
         <v>46173</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1178293</v>
+        <v>1925350</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
@@ -2901,12 +2917,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>4.2.2</t>
+          <t>4.2.9</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water tank</t>
+          <t>Natural gas (if any) and ammonia detection system</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2918,7 +2934,7 @@
         <v>46173</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>275700</v>
+        <v>285000</v>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
@@ -2934,28 +2950,28 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>4.2.3</t>
+          <t>5.10.13.5</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water pumping</t>
+          <t>Control valves</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E48" s="13" t="n">
         <v>46173</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>715920</v>
+        <v>700000</v>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -2967,30 +2983,26 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>4.2.4</t>
+          <t>5.2.2</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water external distribution, hoses, sprinklers</t>
+          <t>Trapdoors for grab maintenance</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E49" s="13" t="n">
         <v>46173</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>821016</v>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>81600</v>
+      </c>
+      <c r="G49" s="5" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
@@ -3000,30 +3012,26 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>4.2.5</t>
+          <t>5.3.6</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Installation of internal hydrants in buildings B1 and B2</t>
+          <t>Primary &amp; secondary air dampers</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E50" s="13" t="n">
         <v>46173</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>240990</v>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>220000</v>
+      </c>
+      <c r="G50" s="5" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -3033,30 +3041,26 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>4.2.6</t>
+          <t>5.3.7</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Wireless radio controller system type WRC, gun control</t>
+          <t>Flue gas recirculation dampers</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E51" s="13" t="n">
         <v>46173</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>45500</v>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>40000</v>
+      </c>
+      <c r="G51" s="5" t="n"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -3066,28 +3070,28 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>4.2.7</t>
+          <t>5.10.8</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water external distribution, hoses, sprinklers</t>
+          <t>Cooler tank, condensate tank</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E52" s="13" t="n">
-        <v>46173</v>
+        <v>46188</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>542750</v>
+        <v>1000000</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -3099,28 +3103,28 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>4.2.8</t>
+          <t>5.13.4</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Dry bunker sprinkler system. Installation of water and foam cannons in the bunker hall, and assembly of the valve sub-control unit.</t>
+          <t>Auxiliary fuel pumps (light oil/diesel oil), demi water pumps, other water pumps</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E53" s="13" t="n">
-        <v>46173</v>
+        <v>46188</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1925350</v>
+        <v>3337500</v>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -3132,30 +3136,26 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>4.2.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Natural gas (if any) and ammonia detection system</t>
+          <t>Notification Bodies</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E54" s="13" t="n">
-        <v>46173</v>
+        <v>46201</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>285000</v>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>350000</v>
+      </c>
+      <c r="G54" s="5" t="n"/>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>5.10.13.5</t>
+          <t>5.10.11</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Control valves</t>
+          <t>Heat exchangers 2 pcs., LP pre-heater, external economizer</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3179,14 +3179,14 @@
         </is>
       </c>
       <c r="E55" s="13" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>700000</v>
+        <v>3242866</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -3198,12 +3198,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>5.2.2</t>
+          <t>5.13.3</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Trapdoors for grab maintenance</t>
+          <t>Light oil unloading installation with TDT documentation approval</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="E56" s="13" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>81600</v>
+        <v>200000</v>
       </c>
       <c r="G56" s="5" t="n"/>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>5.3.6</t>
+          <t>5.4.4</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Primary &amp; secondary air dampers</t>
+          <t>Sampling system</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -3241,12 +3241,16 @@
         </is>
       </c>
       <c r="E57" s="13" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>220000</v>
-      </c>
-      <c r="G57" s="5" t="n"/>
+        <v>1010500</v>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -3256,12 +3260,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>5.3.7</t>
+          <t>5.4.5</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Flue gas recirculation dampers</t>
+          <t>Chemical dosing for the boiler</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -3270,12 +3274,16 @@
         </is>
       </c>
       <c r="E58" s="13" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="G58" s="5" t="n"/>
+        <v>223600</v>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
@@ -3285,12 +3293,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>5.10.8</t>
+          <t>5.7.1</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Cooler tank, condensate tank</t>
+          <t>SNCR DeNOx system including silo, pumps</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -3299,14 +3307,14 @@
         </is>
       </c>
       <c r="E59" s="13" t="n">
-        <v>46188</v>
+        <v>46203</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1000000</v>
+        <v>1090000</v>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -3318,12 +3326,12 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>5.13.4</t>
+          <t>4.3.1</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary fuel pumps (light oil/diesel oil), demi water pumps, other water pumps</t>
+          <t>Boiler room roof ventilators and wall shutters</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -3332,14 +3340,14 @@
         </is>
       </c>
       <c r="E60" s="13" t="n">
-        <v>46188</v>
+        <v>46218</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>3337500</v>
+        <v>1500000</v>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Magdalena Przeździak</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3359,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Notification Bodies</t>
+          <t>HVAC for the technological buildings</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -3365,12 +3373,16 @@
         </is>
       </c>
       <c r="E61" s="13" t="n">
-        <v>46201</v>
+        <v>46218</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>350000</v>
-      </c>
-      <c r="G61" s="5" t="n"/>
+        <v>3107033</v>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Przeździak</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -3380,12 +3392,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>5.10.11</t>
+          <t>4.3.3</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Heat exchangers 2 pcs., LP pre-heater, external economizer</t>
+          <t xml:space="preserve">HVAC for the other buildings </t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -3394,14 +3406,14 @@
         </is>
       </c>
       <c r="E62" s="13" t="n">
-        <v>46203</v>
+        <v>46218</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>3242866</v>
+        <v>1548256</v>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Magdalena Przeździak</t>
         </is>
       </c>
     </row>
@@ -3413,12 +3425,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>5.13.3</t>
+          <t>2.11.1</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Light oil unloading installation with TDT documentation approval</t>
+          <t>Painting</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -3427,12 +3439,16 @@
         </is>
       </c>
       <c r="E63" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G63" s="5" t="n"/>
+        <v>669442.8</v>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
@@ -3442,12 +3458,12 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>5.4.4</t>
+          <t>2.11.10</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Sampling system</t>
+          <t>Plasterboard wall, sandwich panel wall</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3456,16 +3472,12 @@
         </is>
       </c>
       <c r="E64" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>1010500</v>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>39026.75</v>
+      </c>
+      <c r="G64" s="5" t="n"/>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
@@ -3475,12 +3487,12 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>5.4.5</t>
+          <t>2.11.11</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Chemical dosing for the boiler</t>
+          <t>Glass wall</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -3489,16 +3501,12 @@
         </is>
       </c>
       <c r="E65" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>223600</v>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>75045.3</v>
+      </c>
+      <c r="G65" s="5" t="n"/>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
@@ -3508,12 +3516,12 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>5.7.1</t>
+          <t>2.11.12</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>SNCR DeNOx system including silo, pumps</t>
+          <t>Plastering</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -3522,10 +3530,10 @@
         </is>
       </c>
       <c r="E66" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>1090000</v>
+        <v>1241084.64</v>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
@@ -3541,12 +3549,12 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>4.3.1</t>
+          <t>2.11.13</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Boiler room roof ventilators and wall shutters</t>
+          <t>Carpet / polyamide</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -3555,16 +3563,12 @@
         </is>
       </c>
       <c r="E67" s="13" t="n">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Przeździak</t>
-        </is>
-      </c>
+        <v>87497.52</v>
+      </c>
+      <c r="G67" s="5" t="n"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
@@ -3574,12 +3578,12 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>4.3.2</t>
+          <t>2.11.14</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>HVAC for the technological buildings</t>
+          <t>Wall and column protection up to 2.5 m + hydrophobic protection</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -3588,16 +3592,12 @@
         </is>
       </c>
       <c r="E68" s="13" t="n">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>3107033</v>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Przeździak</t>
-        </is>
-      </c>
+        <v>186490.48</v>
+      </c>
+      <c r="G68" s="5" t="n"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>4.3.3</t>
+          <t>2.11.2</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HVAC for the other buildings </t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -3621,14 +3621,14 @@
         </is>
       </c>
       <c r="E69" s="13" t="n">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1548256</v>
+        <v>631074</v>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Przeździak</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -3640,12 +3640,12 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>2.11.1</t>
+          <t>2.11.3</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Painting</t>
+          <t>Tiles</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -3657,7 +3657,7 @@
         <v>46234</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>669442.8</v>
+        <v>498448.22</v>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
@@ -3673,12 +3673,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>2.11.10</t>
+          <t>2.11.4</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Plasterboard wall, sandwich panel wall</t>
+          <t>Raised floor</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -3690,9 +3690,13 @@
         <v>46234</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>39026.75</v>
-      </c>
-      <c r="G71" s="5" t="n"/>
+        <v>621907.75</v>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -3702,24 +3706,24 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>2.11.11</t>
+          <t>2.11.5</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Glass wall</t>
+          <t>Concrete floor + screed</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E72" s="13" t="n">
         <v>46234</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>75045.3</v>
+        <v>610629.23</v>
       </c>
       <c r="G72" s="5" t="n"/>
     </row>
@@ -3731,12 +3735,12 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>2.11.12</t>
+          <t>2.11.5.4</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Plastering</t>
+          <t>Concrete flooring and screed with insulation</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -3748,13 +3752,9 @@
         <v>46234</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1241084.64</v>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G73" s="5" t="n"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>2.11.13</t>
+          <t>2.11.6</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Carpet / polyamide</t>
+          <t>Microcement floor</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3781,7 +3781,7 @@
         <v>46234</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>87497.52</v>
+        <v>133705.44</v>
       </c>
       <c r="G74" s="5" t="n"/>
     </row>
@@ -3793,12 +3793,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>2.11.14</t>
+          <t>2.11.7</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Wall and column protection up to 2.5 m + hydrophobic protection</t>
+          <t>Resin floor</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -3810,9 +3810,13 @@
         <v>46234</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>186490.48</v>
-      </c>
-      <c r="G75" s="5" t="n"/>
+        <v>655174.75</v>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
@@ -3822,12 +3826,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>2.11.2</t>
+          <t>2.11.8</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Suspended ceilings</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -3839,13 +3843,9 @@
         <v>46234</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>631074</v>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>220670.05</v>
+      </c>
+      <c r="G76" s="5" t="n"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>2.11.3</t>
+          <t>2.11.9</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Tiles</t>
+          <t>Segmented sliding wall</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -3872,13 +3872,9 @@
         <v>46234</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>498448.22</v>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>65014.1</v>
+      </c>
+      <c r="G77" s="5" t="n"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -3888,28 +3884,28 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>2.11.4</t>
+          <t>2.12.1</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Raised floor</t>
+          <t>Passenger and good elevator</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E78" s="13" t="n">
         <v>46234</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>621907.75</v>
+        <v>415350</v>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Izabela Malarecka</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3917,12 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>2.11.5</t>
+          <t>2.12.2</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Concrete floor + screed</t>
+          <t>Passenger elevator</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -3938,9 +3934,13 @@
         <v>46234</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>610629.23</v>
-      </c>
-      <c r="G79" s="5" t="n"/>
+        <v>98643.60000000001</v>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Izabela Malarecka</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>2.11.5.4</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Concrete flooring and screed with insulation</t>
+          <t>Weigh bridge</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -3967,9 +3967,13 @@
         <v>46234</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="5" t="n"/>
+        <v>551900</v>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>Stanisław Rucki</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
@@ -3979,12 +3983,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>2.11.6</t>
+          <t>3.4.2</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Microcement floor</t>
+          <t>DCS System</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3996,9 +4000,13 @@
         <v>46234</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>133705.44</v>
-      </c>
-      <c r="G81" s="5" t="n"/>
+        <v>2752000</v>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Roger Gołombek</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
@@ -4008,12 +4016,12 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>2.11.7</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Resin floor</t>
+          <t>Radioactivity detector</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -4025,13 +4033,9 @@
         <v>46234</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>655174.75</v>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>185000</v>
+      </c>
+      <c r="G82" s="5" t="n"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
@@ -4041,12 +4045,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>2.11.8</t>
+          <t>5.10.6</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Suspended ceilings</t>
+          <t>Chemical dossing for thermal cycle and district heating</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -4058,9 +4062,13 @@
         <v>46234</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>220670.05</v>
-      </c>
-      <c r="G83" s="5" t="n"/>
+        <v>550000</v>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
@@ -4070,12 +4078,12 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>2.11.9</t>
+          <t>5.13.9</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Segmented sliding wall</t>
+          <t>Grate cooling system</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -4087,9 +4095,13 @@
         <v>46234</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>65014.1</v>
-      </c>
-      <c r="G84" s="5" t="n"/>
+        <v>731000</v>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
@@ -4099,28 +4111,28 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>2.12.1</t>
+          <t>5.14.2</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Passenger and good elevator</t>
+          <t>Mechanical installation of technological equipment</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E85" s="13" t="n">
         <v>46234</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>415350</v>
+        <v>1500000</v>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Izabela Malarecka</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -4132,28 +4144,28 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>2.12.2</t>
+          <t>5.3.4</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Passenger elevator</t>
+          <t>Primary / secondary air ducts + Flue gas recirculation ducts + Auxiliary burners ducts + Supporting structures</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E86" s="13" t="n">
         <v>46234</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>98643.60000000001</v>
+        <v>2502500</v>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Izabela Malarecka</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4177,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>5.3.5</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Weigh bridge</t>
+          <t>Fire curtain for primary air opening</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -4182,11 +4194,11 @@
         <v>46234</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>551900</v>
+        <v>100000</v>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Magdalena Przeździak</t>
         </is>
       </c>
     </row>
@@ -4198,12 +4210,12 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>3.4.2</t>
+          <t>5.3.8</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>DCS System</t>
+          <t>Camera for furnace monitoring</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -4215,13 +4227,9 @@
         <v>46234</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>2752000</v>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
+        <v>51600</v>
+      </c>
+      <c r="G88" s="5" t="n"/>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
@@ -4231,12 +4239,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>5.4.6</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Radioactivity detector</t>
+          <t>Compensator between boiler and ECO</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -4248,7 +4256,7 @@
         <v>46234</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>185000</v>
+        <v>129000</v>
       </c>
       <c r="G89" s="5" t="n"/>
     </row>
@@ -4260,12 +4268,12 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>5.10.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Chemical dossing for thermal cycle and district heating</t>
+          <t>Refractory</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -4277,7 +4285,7 @@
         <v>46234</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>550000</v>
+        <v>3993000</v>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
@@ -4293,12 +4301,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>5.13.9</t>
+          <t>5.10.10</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Grate cooling system</t>
+          <t>Water tank 100 m3</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -4307,10 +4315,10 @@
         </is>
       </c>
       <c r="E91" s="13" t="n">
-        <v>46234</v>
+        <v>46249</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>731000</v>
+        <v>200000</v>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
@@ -4326,12 +4334,12 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>5.14.2</t>
+          <t>5.10.7</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Mechanical installation of technological equipment</t>
+          <t>Main cooler</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -4340,171 +4348,14 @@
         </is>
       </c>
       <c r="E92" s="13" t="n">
-        <v>46234</v>
+        <v>46249</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>1500000</v>
+        <v>2000000</v>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>5.3.4</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>Primary / secondary air ducts + Flue gas recirculation ducts + Auxiliary burners ducts + Supporting structures</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E93" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F93" s="6" t="n">
-        <v>2502500</v>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>5.3.5</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>Fire curtain for primary air opening</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E94" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F94" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Przeździak</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>5.3.8</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>Camera for furnace monitoring</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E95" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F95" s="6" t="n">
-        <v>51600</v>
-      </c>
-      <c r="G95" s="5" t="n"/>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>5.4.6</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>Compensator between boiler and ECO</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E96" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F96" s="6" t="n">
-        <v>129000</v>
-      </c>
-      <c r="G96" s="5" t="n"/>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>Refractory</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E97" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F97" s="6" t="n">
-        <v>3993000</v>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -10454,156 +10305,6 @@
       </c>
       <c r="G92" s="5">
         <f>'10_Source_Orders_3M'!G92</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="5">
-        <f>'10_Source_Orders_3M'!A93</f>
-        <v/>
-      </c>
-      <c r="B93" s="5">
-        <f>'10_Source_Orders_3M'!B93</f>
-        <v/>
-      </c>
-      <c r="C93" s="5">
-        <f>'10_Source_Orders_3M'!C93</f>
-        <v/>
-      </c>
-      <c r="D93" s="5">
-        <f>'10_Source_Orders_3M'!D93</f>
-        <v/>
-      </c>
-      <c r="E93" s="13">
-        <f>'10_Source_Orders_3M'!E93</f>
-        <v/>
-      </c>
-      <c r="F93" s="6">
-        <f>'10_Source_Orders_3M'!F93</f>
-        <v/>
-      </c>
-      <c r="G93" s="5">
-        <f>'10_Source_Orders_3M'!G93</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="5">
-        <f>'10_Source_Orders_3M'!A94</f>
-        <v/>
-      </c>
-      <c r="B94" s="5">
-        <f>'10_Source_Orders_3M'!B94</f>
-        <v/>
-      </c>
-      <c r="C94" s="5">
-        <f>'10_Source_Orders_3M'!C94</f>
-        <v/>
-      </c>
-      <c r="D94" s="5">
-        <f>'10_Source_Orders_3M'!D94</f>
-        <v/>
-      </c>
-      <c r="E94" s="13">
-        <f>'10_Source_Orders_3M'!E94</f>
-        <v/>
-      </c>
-      <c r="F94" s="6">
-        <f>'10_Source_Orders_3M'!F94</f>
-        <v/>
-      </c>
-      <c r="G94" s="5">
-        <f>'10_Source_Orders_3M'!G94</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="5">
-        <f>'10_Source_Orders_3M'!A95</f>
-        <v/>
-      </c>
-      <c r="B95" s="5">
-        <f>'10_Source_Orders_3M'!B95</f>
-        <v/>
-      </c>
-      <c r="C95" s="5">
-        <f>'10_Source_Orders_3M'!C95</f>
-        <v/>
-      </c>
-      <c r="D95" s="5">
-        <f>'10_Source_Orders_3M'!D95</f>
-        <v/>
-      </c>
-      <c r="E95" s="13">
-        <f>'10_Source_Orders_3M'!E95</f>
-        <v/>
-      </c>
-      <c r="F95" s="6">
-        <f>'10_Source_Orders_3M'!F95</f>
-        <v/>
-      </c>
-      <c r="G95" s="5">
-        <f>'10_Source_Orders_3M'!G95</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="5">
-        <f>'10_Source_Orders_3M'!A96</f>
-        <v/>
-      </c>
-      <c r="B96" s="5">
-        <f>'10_Source_Orders_3M'!B96</f>
-        <v/>
-      </c>
-      <c r="C96" s="5">
-        <f>'10_Source_Orders_3M'!C96</f>
-        <v/>
-      </c>
-      <c r="D96" s="5">
-        <f>'10_Source_Orders_3M'!D96</f>
-        <v/>
-      </c>
-      <c r="E96" s="13">
-        <f>'10_Source_Orders_3M'!E96</f>
-        <v/>
-      </c>
-      <c r="F96" s="6">
-        <f>'10_Source_Orders_3M'!F96</f>
-        <v/>
-      </c>
-      <c r="G96" s="5">
-        <f>'10_Source_Orders_3M'!G96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="5">
-        <f>'10_Source_Orders_3M'!A97</f>
-        <v/>
-      </c>
-      <c r="B97" s="5">
-        <f>'10_Source_Orders_3M'!B97</f>
-        <v/>
-      </c>
-      <c r="C97" s="5">
-        <f>'10_Source_Orders_3M'!C97</f>
-        <v/>
-      </c>
-      <c r="D97" s="5">
-        <f>'10_Source_Orders_3M'!D97</f>
-        <v/>
-      </c>
-      <c r="E97" s="13">
-        <f>'10_Source_Orders_3M'!E97</f>
-        <v/>
-      </c>
-      <c r="F97" s="6">
-        <f>'10_Source_Orders_3M'!F97</f>
-        <v/>
-      </c>
-      <c r="G97" s="5">
-        <f>'10_Source_Orders_3M'!G97</f>
         <v/>
       </c>
     </row>

--- a/docs/reports/WTE_Dashboard_Report.xlsx
+++ b/docs/reports/WTE_Dashboard_Report.xlsx
@@ -825,7 +825,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generato: 2026-05-15 13:43</t>
+          <t>Generato: 2026-05-15 16:27</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="N6" s="4" t="n">
-        <v>501457852.99</v>
+        <v>501457853.02</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>40358716.72</v>
+        <v>40036817.27</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="N14" s="4" t="n">
-        <v>63170895.14</v>
+        <v>63492794.56</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>218667759.04</v>
+        <v>275231609.49</v>
       </c>
       <c r="D9" s="11">
         <f>IFERROR(C9/SUM($C$9:$C$11),0)</f>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>114149861.7</v>
+        <v>106116312.26</v>
       </c>
       <c r="D10" s="11">
         <f>IFERROR(C10/SUM($C$9:$C$11),0)</f>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>187206431.16</v>
+        <v>138676130.15</v>
       </c>
       <c r="D11" s="11">
         <f>IFERROR(C11/SUM($C$9:$C$11),0)</f>
@@ -1431,7 +1431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1440,7 +1440,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -1856,30 +1856,26 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>1.2.2</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Boiler - pressure parts</t>
+          <t>Detailed design: boiler support steel structure and equipment support structures</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E14" s="13" t="n">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
+        <v>943000</v>
+      </c>
+      <c r="G14" s="5" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1889,30 +1885,26 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>5.4.1.1</t>
+          <t>8.4.1.1</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Boiler - pressure parts</t>
+          <t>Personal Occupational Health and Safety Equipment ECd_43</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E15" s="13" t="n">
-        <v>46081</v>
+        <v>46090</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
+        <v>30000</v>
+      </c>
+      <c r="G15" s="5" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1922,12 +1914,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>8.4.1.1</t>
+          <t>8.3.1.2</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Personal Occupational Health and Safety Equipment ECd_43</t>
+          <t>Generator rental ECd_44</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1936,10 +1928,10 @@
         </is>
       </c>
       <c r="E16" s="13" t="n">
-        <v>46090</v>
+        <v>46096</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>30000</v>
+        <v>23904</v>
       </c>
       <c r="G16" s="5" t="n"/>
     </row>
@@ -1951,12 +1943,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>8.3.1.2</t>
+          <t>8.7.1.6</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Generator rental ECd_44</t>
+          <t>Purchase of road signs ECd_42</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1968,7 +1960,7 @@
         <v>46096</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>23904</v>
+        <v>2000</v>
       </c>
       <c r="G17" s="5" t="n"/>
     </row>
@@ -1980,12 +1972,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.6</t>
+          <t>8.7.1.7</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Purchase of road signs ECd_42</t>
+          <t>Purchase of rubble for the construction of storage yards and work platforms ECd_45</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1997,7 +1989,7 @@
         <v>46096</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>2000</v>
+        <v>83200</v>
       </c>
       <c r="G18" s="5" t="n"/>
     </row>
@@ -2009,12 +2001,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.7</t>
+          <t>2.11.5.3</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Purchase of rubble for the construction of storage yards and work platforms ECd_45</t>
+          <t>Concrete slab installation on the ground</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -2023,12 +2015,16 @@
         </is>
       </c>
       <c r="E19" s="13" t="n">
-        <v>46096</v>
+        <v>46106</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>83200</v>
-      </c>
-      <c r="G19" s="5" t="n"/>
+        <v>1735392.78</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Agnieszka Zając</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -2038,12 +2034,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2.11.5.3</t>
+          <t>2.14.2.2</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Concrete slab installation on the ground</t>
+          <t>External road - aggregate delivery ECd_46</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2055,7 +2051,7 @@
         <v>46106</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1735392.78</v>
+        <v>134400</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
@@ -2071,12 +2067,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2.14.2.2</t>
+          <t>2.4.1</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>External road - aggregate delivery ECd_46</t>
+          <t>Insulation - work</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -2088,7 +2084,7 @@
         <v>46106</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>134400</v>
+        <v>733045.25</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
@@ -2104,12 +2100,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2.4.1</t>
+          <t>2.5.1.3</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Insulation - work</t>
+          <t>Construction of reinforced concrete foundations and underground structures</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2121,7 +2117,7 @@
         <v>46106</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>733045.25</v>
+        <v>5276959.37</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
@@ -2137,12 +2133,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2.5.1.3</t>
+          <t>2.5.2.1</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Construction of reinforced concrete foundations and underground structures</t>
+          <t>Reinforced concrete structure of the above-ground part of the B1 building - delivery and assembly of prefabricated elements</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2154,11 +2150,11 @@
         <v>46106</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>5276959.37</v>
+        <v>16616880</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Jan Szczubiał</t>
         </is>
       </c>
     </row>
@@ -2170,12 +2166,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.1</t>
+          <t>2.5.2.2.3</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the B1 building - delivery and assembly of prefabricated elements</t>
+          <t>Reinforced concrete structure of the above-ground part of the B3 building - delivery and assembly of prefabricated elements</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -2187,7 +2183,7 @@
         <v>46106</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>16616880</v>
+        <v>2115950</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
@@ -2203,12 +2199,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.2.3</t>
+          <t>2.5.2.2.4</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the B3 building - delivery and assembly of prefabricated elements</t>
+          <t>Reinforced concrete structure of the above-ground part of the other buildings</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2220,7 +2216,7 @@
         <v>46106</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>2115950</v>
+        <v>708072.75</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
@@ -2236,12 +2232,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.2.4</t>
+          <t>2.6.2.1</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the other buildings</t>
+          <t>Precast reinforced concrete structure of facility B3 (change from steel structure compared to the acquisition stage)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -2253,11 +2249,11 @@
         <v>46106</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>708072.75</v>
+        <v>1004390</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Jan Szczubiał</t>
+          <t>Robert Klimczak</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2265,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2.6.2.1</t>
+          <t>2.6.3.1</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Precast reinforced concrete structure of facility B3 (change from steel structure compared to the acquisition stage)</t>
+          <t>Precast reinforced concrete structure of facility B4 (change from steel structure compared to the acquisition stage)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2286,7 +2282,7 @@
         <v>46106</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1004390</v>
+        <v>246780</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
@@ -2302,12 +2298,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2.6.3.1</t>
+          <t>2.14.2.1</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Precast reinforced concrete structure of facility B4 (change from steel structure compared to the acquisition stage)</t>
+          <t>External road- sub-base construction</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2316,14 +2312,14 @@
         </is>
       </c>
       <c r="E28" s="13" t="n">
-        <v>46106</v>
+        <v>46122</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>246780</v>
+        <v>250640</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Robert Klimczak</t>
+          <t>Agnieszka Zając</t>
         </is>
       </c>
     </row>
@@ -2335,30 +2331,26 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>5.10.2</t>
+          <t>8.3.1.1</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary crane and hoists for the maintenance of the steam turbine</t>
+          <t>Electricity Costs</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E29" s="13" t="n">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>499000</v>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="G29" s="5" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -2368,28 +2360,28 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>5.2.1</t>
+          <t>8.7.1.4</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Overhead crane, grab and operator seat + Spare Grab</t>
+          <t>Construction of aggregate squares</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E30" s="13" t="n">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>8701000</v>
+        <v>124700</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Agnieszka Zając</t>
         </is>
       </c>
     </row>
@@ -2401,30 +2393,26 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2.14.2.1</t>
+          <t>8.8.4</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>External road- sub-base construction</t>
+          <t>Removing collisions related to site preparation and construction</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E31" s="13" t="n">
         <v>46122</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>250640</v>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>Agnieszka Zając</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -2434,24 +2422,24 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>8.3.1.1</t>
+          <t>8.8.4.1</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Electricity Costs</t>
+          <t>Removal of existing reinforced concrete foundations in the vicinity of Building B2</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E32" s="13" t="n">
         <v>46122</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G32" s="5" t="n"/>
     </row>
@@ -2463,28 +2451,28 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.4</t>
+          <t>5.10.2</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Construction of aggregate squares</t>
+          <t>Auxiliary crane and hoists for the maintenance of the steam turbine</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E33" s="13" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>124700</v>
+        <v>499000</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2496,664 +2484,648 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8.8.4</t>
+          <t>5.2.1</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Removing collisions related to site preparation and construction</t>
+          <t>Overhead crane, grab and operator seat + Spare Grab</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E34" s="13" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G34" s="5" t="n"/>
+        <v>8701000</v>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Brick walls</t>
+          <t>Stack</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E35" s="13" t="n">
-        <v>46173</v>
+        <v>46127</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>687451.25</v>
-      </c>
-      <c r="G35" s="5" t="n"/>
+        <v>1498200</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>3.4.3</t>
+          <t>5.4.1.1</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Emission monitoring system (CEMS)</t>
+          <t>Boiler - pressure parts</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E36" s="13" t="n">
-        <v>46173</v>
+        <v>46127</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>1960000</v>
+        <v>45990000</v>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Radosław Zdancewicz</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>8.3.5</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Deodorization system</t>
+          <t>Construction Waste Removal  ECd_38</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E37" s="13" t="n">
-        <v>46173</v>
+        <v>46127</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1009700</v>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
+        <v>290720</v>
+      </c>
+      <c r="G37" s="5" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Fire detection and alarm system</t>
+          <t>Drainage</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E38" s="13" t="n">
-        <v>46173</v>
+        <v>46129</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>2211870</v>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>4.2.10</t>
+          <t>2.3.1</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Smoke extraction from waste bunker and tipping hall</t>
+          <t>Rental of an drainage pump ECd_49</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E39" s="13" t="n">
-        <v>46173</v>
+        <v>46129</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1178293</v>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>4600</v>
+      </c>
+      <c r="G39" s="5" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>4.2.2</t>
+          <t>2.3.2</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water tank</t>
+          <t xml:space="preserve">Mobilization, installation and leasing of a wellpoint system including pumps ECd_50 </t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E40" s="13" t="n">
-        <v>46173</v>
+        <v>46129</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>275700</v>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>70000</v>
+      </c>
+      <c r="G40" s="5" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>4.2.3</t>
+          <t>1.2.4</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water pumping</t>
+          <t xml:space="preserve">Electrical &amp; I/C detailed design </t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E41" s="13" t="n">
-        <v>46173</v>
+        <v>46134</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>715920</v>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>1620000</v>
+      </c>
+      <c r="G41" s="5" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>4.2.4</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water external distribution, hoses, sprinklers</t>
+          <t>Delivery and installation of electrical equipment</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E42" s="13" t="n">
-        <v>46173</v>
+        <v>46134</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>821016</v>
+        <v>0</v>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Radosław Zdancewicz</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>4.2.5</t>
+          <t>3.1.1.1</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Installation of internal hydrants in buildings B1 and B2</t>
+          <t>Delivery and installation of electrical equipment</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E43" s="13" t="n">
-        <v>46173</v>
+        <v>46134</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>240990</v>
+        <v>27750000</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Radosław Zdancewicz</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>4.2.6</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Wireless radio controller system type WRC, gun control</t>
+          <t>Teletechnical installations</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E44" s="13" t="n">
-        <v>46173</v>
+        <v>46134</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>45500</v>
+        <v>1750000</v>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Radosław Zdancewicz</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>4.2.7</t>
+          <t>3.4.1</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water external distribution, hoses, sprinklers</t>
+          <t>Automation system and instrumentation, communication networks and control room devices</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E45" s="13" t="n">
-        <v>46173</v>
+        <v>46134</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>542750</v>
+        <v>0</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Radosław Zdancewicz</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>4.2.8</t>
+          <t>3.4.1.1</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Dry bunker sprinkler system. Installation of water and foam cannons in the bunker hall, and assembly of the valve sub-control unit.</t>
+          <t>Automation system and instrumentation, communication networks and control room devices</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E46" s="13" t="n">
-        <v>46173</v>
+        <v>46134</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1925350</v>
+        <v>6280000</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Radosław Zdancewicz</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>4.2.9</t>
+          <t>6.4.1</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Natural gas (if any) and ammonia detection system</t>
+          <t>Extension of the guarantee and warranty period to 48 months for electrical, technical and I&amp;C works</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E47" s="13" t="n">
-        <v>46173</v>
+        <v>46134</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>285000</v>
+        <v>350000</v>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Radosław Zdancewicz</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>5.10.13.5</t>
+          <t>5.10.1</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Control valves</t>
+          <t>Steam turbine - gear box - generator. Including accessories: oil system, coolers, insulation, pipes and valves, control panel, protection panel, synchro system etc.</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E48" s="13" t="n">
-        <v>46173</v>
+        <v>46137</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Magdalena Białorucka / Stanisław Rucki</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>5.2.2</t>
+          <t>5.8.1</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Trapdoors for grab maintenance</t>
+          <t>Chain conveyor under grate + Bottom ash extractor + Vibrating table / bulk screen</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E49" s="13" t="n">
-        <v>46173</v>
+        <v>46137</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>81600</v>
-      </c>
-      <c r="G49" s="5" t="n"/>
+        <v>1462000</v>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Stanisław Rucki</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>5.3.6</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Primary &amp; secondary air dampers</t>
+          <t>Insulation – supply – Hydrostop ECd_51</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E50" s="13" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>220000</v>
+        <v>31352</v>
       </c>
       <c r="G50" s="5" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>5.3.7</t>
+          <t>2.4.3</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Flue gas recirculation dampers</t>
+          <t>Insulation – supply – foil, compound ECd_14</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E51" s="13" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>40000</v>
+        <v>27600</v>
       </c>
       <c r="G51" s="5" t="n"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>5.10.8</t>
+          <t>8.1.1.1</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Cooler tank, condensate tank</t>
+          <t>Purchase of temporary stairs ECd_48</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E52" s="13" t="n">
-        <v>46188</v>
+        <v>46142</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
+        <v>17530</v>
+      </c>
+      <c r="G52" s="5" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>5.13.4</t>
+          <t>8.1.1.2</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary fuel pumps (light oil/diesel oil), demi water pumps, other water pumps</t>
+          <t>Meals ECd_53</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E53" s="13" t="n">
-        <v>46188</v>
+        <v>46142</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3337500</v>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
+        <v>5711</v>
+      </c>
+      <c r="G53" s="5" t="n"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Next orders 3 months</t>
+          <t>Closed last 3 months</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.7.1.8</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Notification Bodies</t>
+          <t>Installation of road markings and traffic signs ECd_52</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E54" s="13" t="n">
-        <v>46201</v>
+        <v>46142</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>350000</v>
+        <v>920</v>
       </c>
       <c r="G54" s="5" t="n"/>
     </row>
@@ -3165,30 +3137,22 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>5.10.11</t>
+          <t>5.10.13.6</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Heat exchangers 2 pcs., LP pre-heater, external economizer</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
+          <t>Bypass</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n"/>
       <c r="E55" s="13" t="n">
-        <v>46203</v>
+        <v>46158</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>3242866</v>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="n"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
@@ -3198,26 +3162,30 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>5.13.3</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Light oil unloading installation with TDT documentation approval</t>
+          <t>Burners including fans</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>negotiation</t>
         </is>
       </c>
       <c r="E56" s="13" t="n">
-        <v>46203</v>
+        <v>46158</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G56" s="5" t="n"/>
+        <v>1062800</v>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Stanisław Rucki</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
@@ -3227,12 +3195,12 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>5.4.4</t>
+          <t>5.13.7</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Sampling system</t>
+          <t>Demi water system including storage tank 100m3 and piping</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -3241,10 +3209,10 @@
         </is>
       </c>
       <c r="E57" s="13" t="n">
-        <v>46203</v>
+        <v>46169</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1010500</v>
+        <v>3010000</v>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
@@ -3260,12 +3228,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>5.4.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Chemical dosing for the boiler</t>
+          <t>Brick walls</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -3274,16 +3242,12 @@
         </is>
       </c>
       <c r="E58" s="13" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>223600</v>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>687451.25</v>
+      </c>
+      <c r="G58" s="5" t="n"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
@@ -3293,12 +3257,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>5.7.1</t>
+          <t>5.2.2</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>SNCR DeNOx system including silo, pumps</t>
+          <t>Trapdoors for grab maintenance</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -3307,16 +3271,12 @@
         </is>
       </c>
       <c r="E59" s="13" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>81600</v>
+      </c>
+      <c r="G59" s="5" t="n"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
@@ -3326,30 +3286,26 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>4.3.1</t>
+          <t>1.2.6.1</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Boiler room roof ventilators and wall shutters</t>
+          <t>Ducts design</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E60" s="13" t="n">
-        <v>46218</v>
+        <v>46174</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Przeździak</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="n"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
@@ -3359,12 +3315,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>4.3.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>HVAC for the technological buildings</t>
+          <t xml:space="preserve">Explosion hazard assessment </t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -3373,16 +3329,12 @@
         </is>
       </c>
       <c r="E61" s="13" t="n">
-        <v>46218</v>
+        <v>46174</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3107033</v>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Przeździak</t>
-        </is>
-      </c>
+        <v>120000</v>
+      </c>
+      <c r="G61" s="5" t="n"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -3392,28 +3344,28 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>4.3.3</t>
+          <t>5.10.4</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HVAC for the other buildings </t>
+          <t>Feed water tank and Deaerator</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>negotiation</t>
         </is>
       </c>
       <c r="E62" s="13" t="n">
-        <v>46218</v>
+        <v>46174</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>1548256</v>
+        <v>1000000</v>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Przeździak</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -3425,12 +3377,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>2.11.1</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Painting</t>
+          <t>Bottom ash / slag valorization</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -3439,14 +3391,14 @@
         </is>
       </c>
       <c r="E63" s="13" t="n">
-        <v>46234</v>
+        <v>46175</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>669442.8</v>
+        <v>8271000</v>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3410,12 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>2.11.10</t>
+          <t>5.8.2</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Plasterboard wall, sandwich panel wall</t>
+          <t>Belt conveyors</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3472,12 +3424,16 @@
         </is>
       </c>
       <c r="E64" s="13" t="n">
-        <v>46234</v>
+        <v>46176</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>39026.75</v>
-      </c>
-      <c r="G64" s="5" t="n"/>
+        <v>2347800</v>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Stanisław Rucki</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
@@ -3487,26 +3443,30 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>2.11.11</t>
+          <t>5.10.3</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Glass wall</t>
+          <t>Air cooled condenser</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E65" s="13" t="n">
-        <v>46234</v>
+        <v>46178</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>75045.3</v>
-      </c>
-      <c r="G65" s="5" t="n"/>
+        <v>9000000</v>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Roger Gołombek</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
@@ -3516,28 +3476,28 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>2.11.12</t>
+          <t>2.5.2.3</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Plastering</t>
+          <t>Supply of reinforcing steel</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E66" s="13" t="n">
-        <v>46234</v>
+        <v>46181</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>1241084.64</v>
+        <v>386500</v>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Agnieszka Zając</t>
         </is>
       </c>
     </row>
@@ -3549,26 +3509,30 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2.11.13</t>
+          <t>5.13.2</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Carpet / polyamide</t>
+          <t>Auxiliary fuel tank (light oil/diesel oil)</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E67" s="13" t="n">
-        <v>46234</v>
+        <v>46189</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>87497.52</v>
-      </c>
-      <c r="G67" s="5" t="n"/>
+        <v>200000</v>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
@@ -3578,12 +3542,12 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>2.11.14</t>
+          <t>2.8.1</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Wall and column protection up to 2.5 m + hydrophobic protection</t>
+          <t>Parapet</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -3592,12 +3556,16 @@
         </is>
       </c>
       <c r="E68" s="13" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>186490.48</v>
-      </c>
-      <c r="G68" s="5" t="n"/>
+        <v>82476</v>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Joanna Sawicka</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -3607,12 +3575,12 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>2.11.2</t>
+          <t>2.8.10</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Soffit lining</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -3621,14 +3589,14 @@
         </is>
       </c>
       <c r="E69" s="13" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>631074</v>
+        <v>308662.24</v>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Joanna Sawicka</t>
         </is>
       </c>
     </row>
@@ -3640,12 +3608,12 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>2.11.3</t>
+          <t>2.8.11</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Tiles</t>
+          <t>Scaffolding</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -3654,14 +3622,14 @@
         </is>
       </c>
       <c r="E70" s="13" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>498448.22</v>
+        <v>77076</v>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Joanna Sawicka</t>
         </is>
       </c>
     </row>
@@ -3673,12 +3641,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>2.11.4</t>
+          <t>2.8.12</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Raised floor</t>
+          <t>Safety system</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -3687,14 +3655,14 @@
         </is>
       </c>
       <c r="E71" s="13" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>621907.75</v>
+        <v>150018.35</v>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Joanna Sawicka</t>
         </is>
       </c>
     </row>
@@ -3706,26 +3674,30 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>2.11.5</t>
+          <t>2.8.13</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Concrete floor + screed</t>
+          <t>Shutters</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E72" s="13" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>610629.23</v>
-      </c>
-      <c r="G72" s="5" t="n"/>
+        <v>107600.56</v>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Joanna Sawicka</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -3735,12 +3707,12 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>2.11.5.4</t>
+          <t>2.8.2</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Concrete flooring and screed with insulation</t>
+          <t>Steel-aluminum canopy</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -3749,12 +3721,16 @@
         </is>
       </c>
       <c r="E73" s="13" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="5" t="n"/>
+        <v>120922.87</v>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Joanna Sawicka</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -3764,12 +3740,12 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>2.11.6</t>
+          <t>2.8.3</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Microcement floor</t>
+          <t>Aluminum-glass facade</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3778,12 +3754,16 @@
         </is>
       </c>
       <c r="E74" s="13" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>133705.44</v>
-      </c>
-      <c r="G74" s="5" t="n"/>
+        <v>296487.48</v>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Joanna Sawicka</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
@@ -3793,12 +3773,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>2.11.7</t>
+          <t>2.8.4</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Resin floor</t>
+          <t xml:space="preserve">ETICS </t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -3807,14 +3787,14 @@
         </is>
       </c>
       <c r="E75" s="13" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>655174.75</v>
+        <v>122038.26</v>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Joanna Sawicka</t>
         </is>
       </c>
     </row>
@@ -3826,12 +3806,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>2.11.8</t>
+          <t>2.8.5</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Suspended ceilings</t>
+          <t>Flashings</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -3840,12 +3820,16 @@
         </is>
       </c>
       <c r="E76" s="13" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>220670.05</v>
-      </c>
-      <c r="G76" s="5" t="n"/>
+        <v>366598.98</v>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Joanna Sawicka</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
@@ -3855,12 +3839,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>2.11.9</t>
+          <t>2.8.6</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Segmented sliding wall</t>
+          <t>Sheet metal cladding</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -3869,12 +3853,16 @@
         </is>
       </c>
       <c r="E77" s="13" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>65014.1</v>
-      </c>
-      <c r="G77" s="5" t="n"/>
+        <v>1172886.87</v>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Joanna Sawicka</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -3884,12 +3872,12 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>2.12.1</t>
+          <t>2.8.7</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Passenger and good elevator</t>
+          <t>Sandwich panel cladding</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -3898,14 +3886,14 @@
         </is>
       </c>
       <c r="E78" s="13" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>415350</v>
+        <v>5792279.88</v>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Izabela Malarecka</t>
+          <t>Joanna Sawicka</t>
         </is>
       </c>
     </row>
@@ -3917,28 +3905,28 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>2.12.2</t>
+          <t>2.8.8</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Passenger elevator</t>
+          <t>Fiber cement panel cladding</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E79" s="13" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>98643.60000000001</v>
+        <v>241170.5</v>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Izabela Malarecka</t>
+          <t>Joanna Sawicka</t>
         </is>
       </c>
     </row>
@@ -3950,12 +3938,12 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.8.9</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Weigh bridge</t>
+          <t>Substructures</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -3964,14 +3952,14 @@
         </is>
       </c>
       <c r="E80" s="13" t="n">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>551900</v>
+        <v>419580</v>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Joanna Sawicka</t>
         </is>
       </c>
     </row>
@@ -3983,12 +3971,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>3.4.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>DCS System</t>
+          <t>Notification Bodies</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3997,16 +3985,12 @@
         </is>
       </c>
       <c r="E81" s="13" t="n">
-        <v>46234</v>
+        <v>46201</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>2752000</v>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
+        <v>350000</v>
+      </c>
+      <c r="G81" s="5" t="n"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
@@ -4016,24 +4000,24 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>2.5.1.4</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Radioactivity detector</t>
+          <t>Execution of pre-wall insulation</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>negotiation</t>
         </is>
       </c>
       <c r="E82" s="13" t="n">
-        <v>46234</v>
+        <v>46201</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>185000</v>
+        <v>500000</v>
       </c>
       <c r="G82" s="5" t="n"/>
     </row>
@@ -4045,28 +4029,28 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>5.10.6</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Chemical dossing for thermal cycle and district heating</t>
+          <t>Fly ash extraction system for the boiler and conveyors</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E83" s="13" t="n">
-        <v>46234</v>
+        <v>46202</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>550000</v>
+        <v>4260000</v>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4062,12 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>5.13.9</t>
+          <t>1.2.6.2</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Grate cooling system</t>
+          <t>Piping design</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -4092,16 +4076,12 @@
         </is>
       </c>
       <c r="E84" s="13" t="n">
-        <v>46234</v>
+        <v>46205</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>731000</v>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G84" s="5" t="n"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
@@ -4111,12 +4091,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>5.14.2</t>
+          <t>5.7.1</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Mechanical installation of technological equipment</t>
+          <t>SNCR DeNOx system including silo, pumps</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -4125,14 +4105,14 @@
         </is>
       </c>
       <c r="E85" s="13" t="n">
-        <v>46234</v>
+        <v>46205</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1500000</v>
+        <v>1090000</v>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4124,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>5.3.4</t>
+          <t>4.3.6</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Primary / secondary air ducts + Flue gas recirculation ducts + Auxiliary burners ducts + Supporting structures</t>
+          <t>Emergency showers and eye washers</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -4158,14 +4138,14 @@
         </is>
       </c>
       <c r="E86" s="13" t="n">
-        <v>46234</v>
+        <v>46212</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>2502500</v>
+        <v>10000</v>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Magdalena Przeździak</t>
         </is>
       </c>
     </row>
@@ -4177,12 +4157,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>5.3.5</t>
+          <t>5.10.11</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Fire curtain for primary air opening</t>
+          <t>Heat exchangers 2 pcs., LP pre-heater, external economizer</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -4191,14 +4171,14 @@
         </is>
       </c>
       <c r="E87" s="13" t="n">
-        <v>46234</v>
+        <v>46215</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>100000</v>
+        <v>3242866</v>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Przeździak</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -4210,12 +4190,12 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>5.3.8</t>
+          <t>1.2.3</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Camera for furnace monitoring</t>
+          <t>Detailed design: fire-fighting system</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -4224,10 +4204,10 @@
         </is>
       </c>
       <c r="E88" s="13" t="n">
-        <v>46234</v>
+        <v>46218</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>51600</v>
+        <v>260000</v>
       </c>
       <c r="G88" s="5" t="n"/>
     </row>
@@ -4239,12 +4219,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>5.4.6</t>
+          <t>4.3.1</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Compensator between boiler and ECO</t>
+          <t>Boiler room roof ventilators and wall shutters</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -4253,12 +4233,16 @@
         </is>
       </c>
       <c r="E89" s="13" t="n">
-        <v>46234</v>
+        <v>46218</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>129000</v>
-      </c>
-      <c r="G89" s="5" t="n"/>
+        <v>1500000</v>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Przeździak</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
@@ -4268,12 +4252,12 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Refractory</t>
+          <t>HVAC for the technological buildings</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -4282,14 +4266,14 @@
         </is>
       </c>
       <c r="E90" s="13" t="n">
-        <v>46234</v>
+        <v>46218</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>3993000</v>
+        <v>3107033</v>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Magdalena Przeździak</t>
         </is>
       </c>
     </row>
@@ -4301,12 +4285,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>5.10.10</t>
+          <t>4.3.3</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Water tank 100 m3</t>
+          <t xml:space="preserve">HVAC for the other buildings </t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -4315,14 +4299,14 @@
         </is>
       </c>
       <c r="E91" s="13" t="n">
-        <v>46249</v>
+        <v>46218</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>200000</v>
+        <v>1548256</v>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Magdalena Przeździak</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4318,12 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>5.10.7</t>
+          <t>3.4.3</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Main cooler</t>
+          <t>Emission monitoring system (CEMS)</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -4348,14 +4332,1059 @@
         </is>
       </c>
       <c r="E92" s="13" t="n">
-        <v>46249</v>
+        <v>46219</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>2000000</v>
+        <v>1960000</v>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
+          <t>Radosław Zdancewicz</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Deodorization system</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>enquiry</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="n">
+        <v>46219</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>1009700</v>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Stanisław Rucki</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>5.13.3</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Light oil unloading installation with TDT documentation approval</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="n">
+        <v>46222</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G94" s="5" t="n"/>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>5.10.12</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Stabilising pumps 2 x 100%, network pumps 3 x 50%, condensate pumps 2 x 100%, feed water pumps 3 pcs., cooling pumps</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>enquiry</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="n">
+        <v>46231</v>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>5517325</v>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>Stanisław Rucki</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>5.13.4</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Auxiliary fuel pumps (light oil/diesel oil), demi water pumps, other water pumps</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="n">
+        <v>46231</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>3337500</v>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Stanisław Rucki</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>2.11.1</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Painting</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E97" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>669442.8</v>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>2.11.10</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Plasterboard wall, sandwich panel wall</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E98" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>39026.75</v>
+      </c>
+      <c r="G98" s="5" t="n"/>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>2.11.11</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Glass wall</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>75045.3</v>
+      </c>
+      <c r="G99" s="5" t="n"/>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>2.11.12</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Plastering</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E100" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>1241084.64</v>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>2.11.13</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Carpet / polyamide</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>87497.52</v>
+      </c>
+      <c r="G101" s="5" t="n"/>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>2.11.14</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Wall and column protection up to 2.5 m + hydrophobic protection</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E102" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>186490.48</v>
+      </c>
+      <c r="G102" s="5" t="n"/>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>2.11.2</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E103" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>631074</v>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>2.11.3</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Tiles</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E104" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F104" s="6" t="n">
+        <v>498448.22</v>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>2.11.4</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Raised floor</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F105" s="6" t="n">
+        <v>621907.75</v>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>2.11.5</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Concrete floor + screed</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>enquiry</t>
+        </is>
+      </c>
+      <c r="E106" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F106" s="6" t="n">
+        <v>610629.23</v>
+      </c>
+      <c r="G106" s="5" t="n"/>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>2.11.5.4</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Concrete flooring and screed with insulation</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F107" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="5" t="n"/>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>2.11.6</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Microcement floor</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F108" s="6" t="n">
+        <v>133705.44</v>
+      </c>
+      <c r="G108" s="5" t="n"/>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>2.11.7</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Resin floor</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F109" s="6" t="n">
+        <v>655174.75</v>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>2.11.8</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Suspended ceilings</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E110" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F110" s="6" t="n">
+        <v>220670.05</v>
+      </c>
+      <c r="G110" s="5" t="n"/>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>2.11.9</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Segmented sliding wall</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v>65014.1</v>
+      </c>
+      <c r="G111" s="5" t="n"/>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>2.12.1</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Passenger and good elevator</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>enquiry</t>
+        </is>
+      </c>
+      <c r="E112" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F112" s="6" t="n">
+        <v>415350</v>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>Izabela Malarecka</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>2.12.2</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>enquiry</t>
+        </is>
+      </c>
+      <c r="E113" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F113" s="6" t="n">
+        <v>98643.60000000001</v>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Izabela Malarecka</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Weigh bridge</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E114" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F114" s="6" t="n">
+        <v>551900</v>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>Stanisław Rucki</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>5.14.2</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Mechanical installation of technological equipment</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F115" s="6" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>Stanisław Rucki</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>5.4.6</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Compensator between boiler and ECO</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E116" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F116" s="6" t="n">
+        <v>129000</v>
+      </c>
+      <c r="G116" s="5" t="n"/>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>Refractory</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E117" s="13" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F117" s="6" t="n">
+        <v>3993000</v>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>4.2.2</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Firefighting water tank</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>enquiry</t>
+        </is>
+      </c>
+      <c r="E118" s="13" t="n">
+        <v>46235</v>
+      </c>
+      <c r="F118" s="6" t="n">
+        <v>275700</v>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>5.13.1</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Compressors 2 x 50% + 1 x 50%</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E119" s="13" t="n">
+        <v>46235</v>
+      </c>
+      <c r="F119" s="6" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
           <t>Roger Gołombek</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>4.3.5</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Sanitary water, connection to source, storage, pumping, underground and external distribution</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E120" s="13" t="n">
+        <v>46236</v>
+      </c>
+      <c r="F120" s="6" t="n">
+        <v>637613</v>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Przeździak</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>4.3.7</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Sanitary waste water collection, treatment and connection to discharge point</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E121" s="13" t="n">
+        <v>46236</v>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v>624272</v>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Przeździak</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>4.3.8</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Waste water collection and connection to discharge point</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E122" s="13" t="n">
+        <v>46236</v>
+      </c>
+      <c r="F122" s="6" t="n">
+        <v>200969</v>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Przeździak</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>4.3.9</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Rain water and snowmelt collection, treatment and connection to discharge point</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="n">
+        <v>46236</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>3359643</v>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Przeździak</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>5.13.9</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Grate cooling system</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="n">
+        <v>46236</v>
+      </c>
+      <c r="F124" s="6" t="n">
+        <v>731000</v>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Next orders 3 months</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>2.6.4</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Steel structure of the staircase in the B1.4 facility (change from the reinforced concrete structure in relation to the acquisition stage)</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="n">
+        <v>46237</v>
+      </c>
+      <c r="F125" s="6" t="n">
+        <v>470146.23</v>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>Robert Klimczak</t>
         </is>
       </c>
     </row>
@@ -4539,10 +5568,10 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>6635951.36</v>
+        <v>6583222.55</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6635951.36</v>
+        <v>6583222.55</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>6199140</v>
@@ -4570,10 +5599,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>9407183.25</v>
+        <v>9354454.439999999</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>16043134.61</v>
+        <v>15937676.99</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>1209845.03</v>
@@ -4601,16 +5630,16 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>28559502.41</v>
+        <v>15217247.88</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>44602637.02</v>
+        <v>31154924.87</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>7794586.93</v>
+        <v>4914057.77</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>15203571.96</v>
+        <v>12323042.8</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0</v>
@@ -4632,16 +5661,16 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>41783746.29</v>
+        <v>17664420.45</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>86386383.31</v>
+        <v>48819345.32</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>12423640.08</v>
+        <v>6224860.47</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>27627212.04</v>
+        <v>18547903.27</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>0</v>
@@ -4663,16 +5692,16 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>41368003.68</v>
+        <v>32610741.4</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>127754386.99</v>
+        <v>81430086.72</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>11336449.17</v>
+        <v>3080461.27</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>38963661.21</v>
+        <v>21628364.54</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0</v>
@@ -4694,16 +5723,16 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>39534317.53</v>
+        <v>25126114.16</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>167288704.52</v>
+        <v>106556200.88</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>13624888.02</v>
+        <v>10298268.2</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>52588549.23</v>
+        <v>31926632.74</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>0</v>
@@ -4729,16 +5758,16 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>38328272.54</v>
+        <v>50027765.79</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>205616977.06</v>
+        <v>156583966.67</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>14910518.13</v>
+        <v>24920618.49</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>67499067.36</v>
+        <v>56847251.23</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>0</v>
@@ -4760,16 +5789,16 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>37965906.53</v>
+        <v>44614937.25</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>243582883.59</v>
+        <v>201198903.92</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>15028245.62</v>
+        <v>11044595.67</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>82527312.98</v>
+        <v>67891846.90000001</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>0</v>
@@ -4791,16 +5820,16 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>28948793.89</v>
+        <v>31388394.81</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>272531677.48</v>
+        <v>232587298.73</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>24539477.12</v>
+        <v>12651060.25</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>107066790.1</v>
+        <v>80542907.15000001</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>0</v>
@@ -4822,16 +5851,16 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>29770985.24</v>
+        <v>28927011.96</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>302302662.72</v>
+        <v>261514310.69</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>31216463.12</v>
+        <v>16840968.47</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>138283253.22</v>
+        <v>97383875.62</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>0</v>
@@ -4853,16 +5882,16 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>24376568.36</v>
+        <v>26801511.96</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>326679231.08</v>
+        <v>288315822.65</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>27608192.85</v>
+        <v>21259070.9</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>165891446.07</v>
+        <v>118642946.52</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>0</v>
@@ -4884,16 +5913,16 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>42520040.63</v>
+        <v>23020290.23</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>369199271.71</v>
+        <v>311336112.88</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>26540967.3</v>
+        <v>17153971.64</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>192432413.37</v>
+        <v>135796918.16</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>0</v>
@@ -4915,16 +5944,16 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>28741079.3</v>
+        <v>19232675.49</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>397940351.01</v>
+        <v>330568788.37</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>28846792.41</v>
+        <v>19773194.85</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>221279205.78</v>
+        <v>155570113.01</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0</v>
@@ -4946,16 +5975,16 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>15761646.89</v>
+        <v>19092679.12</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>413701997.9</v>
+        <v>349661467.49</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>27022580.63</v>
+        <v>24861930.4</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>248301786.41</v>
+        <v>180432043.41</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>0</v>
@@ -4977,16 +6006,16 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>15778129.71</v>
+        <v>48251591.24</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>429480127.61</v>
+        <v>397913058.73</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>28325747.31</v>
+        <v>27968549.5</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>276627533.72</v>
+        <v>208400592.91</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>0</v>
@@ -5008,16 +6037,16 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>16128129.72</v>
+        <v>16687397.24</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>445608257.33</v>
+        <v>414600455.97</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>35039986.08</v>
+        <v>35342841.76</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>311667519.8</v>
+        <v>243743434.67</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>0</v>
@@ -5039,16 +6068,16 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>14020660.87</v>
+        <v>14237428.39</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>459628918.2</v>
+        <v>428837884.36</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>33822381.41</v>
+        <v>30823036.89</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>345489901.21</v>
+        <v>274566471.56</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>0</v>
@@ -5070,16 +6099,16 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>6947735.9</v>
+        <v>7430822.59</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>466576654.1</v>
+        <v>436268706.95</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>25897922.24</v>
+        <v>32016185.06</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>371387823.45</v>
+        <v>306582656.62</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>0</v>
@@ -5101,16 +6130,16 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>6947735.91</v>
+        <v>7430822.59</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>473524390.01</v>
+        <v>443699529.54</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>28095849.06</v>
+        <v>26848740.97</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>399483672.51</v>
+        <v>333431397.59</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>0</v>
@@ -5132,16 +6161,16 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>5529097.01</v>
+        <v>9132146.75</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>479053487.02</v>
+        <v>452831676.29</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>20736784.02</v>
+        <v>23300575.32</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>420220456.53</v>
+        <v>356731972.91</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>0</v>
@@ -5163,16 +6192,16 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>5529097.02</v>
+        <v>9132146.76</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>484582584.04</v>
+        <v>461963823.05</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>17315684.93</v>
+        <v>17197990.11</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>437536141.46</v>
+        <v>373929963.02</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>0</v>
@@ -5194,16 +6223,16 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>5529097.02</v>
+        <v>9132146.75</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>490111681.06</v>
+        <v>471095969.8</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>15763709.59</v>
+        <v>22446419.55</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>453299851.05</v>
+        <v>396376382.57</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>0</v>
@@ -5225,16 +6254,16 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>4469340.79</v>
+        <v>8530301.029999999</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>494581021.85</v>
+        <v>479626270.83</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>12623620.61</v>
+        <v>10601806.85</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>465923471.66</v>
+        <v>406978189.42</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>0</v>
@@ -5256,16 +6285,16 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>2567186.04</v>
+        <v>6894099.11</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>497148207.89</v>
+        <v>486520369.94</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>10976891.07</v>
+        <v>8350089.78</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>476900362.73</v>
+        <v>415328279.2</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>0</v>
@@ -5287,16 +6316,16 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>2479892.4</v>
+        <v>5164130.92</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>499628100.29</v>
+        <v>491684500.86</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>11889923.67</v>
+        <v>24637776.5</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>488790286.4</v>
+        <v>439966055.7</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>0</v>
@@ -5318,16 +6347,16 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>3399175.86</v>
+        <v>5049870.1</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>503027276.15</v>
+        <v>496734370.96</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0</v>
+        <v>5817816.96</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>488790286.4</v>
+        <v>445783872.66</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>0</v>
@@ -5349,16 +6378,16 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>3277266.16</v>
+        <v>3301596.76</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>506304542.31</v>
+        <v>500035967.72</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>1910542.1</v>
+        <v>3279069.24</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>490700828.5</v>
+        <v>449062941.9</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>0</v>
@@ -5380,16 +6409,16 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>3277266.16</v>
+        <v>3301596.75</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>509581808.47</v>
+        <v>503337564.47</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>2167008.58</v>
+        <v>2859802.38</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>492867837.08</v>
+        <v>451922744.28</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>0</v>
@@ -5411,16 +6440,16 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>3261355.05</v>
+        <v>3285685.65</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>512843163.52</v>
+        <v>506623250.12</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>758299.79</v>
+        <v>308626.93</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>493626136.87</v>
+        <v>452231371.21</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>0</v>
@@ -5442,16 +6471,16 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>3261355.04</v>
+        <v>3285685.64</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>516104518.56</v>
+        <v>509908935.76</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>3740876.04</v>
+        <v>3335488.44</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>497367012.91</v>
+        <v>455566859.65</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>0</v>
@@ -5473,16 +6502,16 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>3261355.05</v>
+        <v>3285685.65</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>519365873.61</v>
+        <v>513194621.41</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>1069040.53</v>
+        <v>966685.08</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>498436053.44</v>
+        <v>456533544.73</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
@@ -5507,13 +6536,13 @@
         <v>0</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>519365873.61</v>
+        <v>513194621.41</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>454545.46</v>
+        <v>0</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>498890598.9</v>
+        <v>456533544.73</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>0</v>
@@ -5538,13 +6567,13 @@
         <v>0</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>519365873.61</v>
+        <v>513194621.41</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>454545.45</v>
+        <v>0</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>499345144.35</v>
+        <v>456533544.73</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
@@ -5569,13 +6598,13 @@
         <v>0</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>519365873.61</v>
+        <v>513194621.41</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>628545.46</v>
+        <v>174000</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>499973689.81</v>
+        <v>456707544.73</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>0</v>
@@ -5600,13 +6629,13 @@
         <v>0</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>519365873.61</v>
+        <v>513194621.41</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>499973689.81</v>
+        <v>456707544.73</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -5631,13 +6660,13 @@
         <v>0</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>519365873.61</v>
+        <v>513194621.41</v>
       </c>
       <c r="E45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>499973689.81</v>
+        <v>456707544.73</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>0</v>
@@ -5662,13 +6691,13 @@
         <v>0</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>519365873.61</v>
+        <v>513194621.41</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>0</v>
+        <v>44750308.29</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>499973689.81</v>
+        <v>501457853.02</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>0</v>
@@ -7529,16 +8558,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -10305,6 +11334,996 @@
       </c>
       <c r="G92" s="5">
         <f>'10_Source_Orders_3M'!G92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="5">
+        <f>'10_Source_Orders_3M'!A93</f>
+        <v/>
+      </c>
+      <c r="B93" s="5">
+        <f>'10_Source_Orders_3M'!B93</f>
+        <v/>
+      </c>
+      <c r="C93" s="5">
+        <f>'10_Source_Orders_3M'!C93</f>
+        <v/>
+      </c>
+      <c r="D93" s="5">
+        <f>'10_Source_Orders_3M'!D93</f>
+        <v/>
+      </c>
+      <c r="E93" s="13">
+        <f>'10_Source_Orders_3M'!E93</f>
+        <v/>
+      </c>
+      <c r="F93" s="6">
+        <f>'10_Source_Orders_3M'!F93</f>
+        <v/>
+      </c>
+      <c r="G93" s="5">
+        <f>'10_Source_Orders_3M'!G93</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="5">
+        <f>'10_Source_Orders_3M'!A94</f>
+        <v/>
+      </c>
+      <c r="B94" s="5">
+        <f>'10_Source_Orders_3M'!B94</f>
+        <v/>
+      </c>
+      <c r="C94" s="5">
+        <f>'10_Source_Orders_3M'!C94</f>
+        <v/>
+      </c>
+      <c r="D94" s="5">
+        <f>'10_Source_Orders_3M'!D94</f>
+        <v/>
+      </c>
+      <c r="E94" s="13">
+        <f>'10_Source_Orders_3M'!E94</f>
+        <v/>
+      </c>
+      <c r="F94" s="6">
+        <f>'10_Source_Orders_3M'!F94</f>
+        <v/>
+      </c>
+      <c r="G94" s="5">
+        <f>'10_Source_Orders_3M'!G94</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="5">
+        <f>'10_Source_Orders_3M'!A95</f>
+        <v/>
+      </c>
+      <c r="B95" s="5">
+        <f>'10_Source_Orders_3M'!B95</f>
+        <v/>
+      </c>
+      <c r="C95" s="5">
+        <f>'10_Source_Orders_3M'!C95</f>
+        <v/>
+      </c>
+      <c r="D95" s="5">
+        <f>'10_Source_Orders_3M'!D95</f>
+        <v/>
+      </c>
+      <c r="E95" s="13">
+        <f>'10_Source_Orders_3M'!E95</f>
+        <v/>
+      </c>
+      <c r="F95" s="6">
+        <f>'10_Source_Orders_3M'!F95</f>
+        <v/>
+      </c>
+      <c r="G95" s="5">
+        <f>'10_Source_Orders_3M'!G95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="5">
+        <f>'10_Source_Orders_3M'!A96</f>
+        <v/>
+      </c>
+      <c r="B96" s="5">
+        <f>'10_Source_Orders_3M'!B96</f>
+        <v/>
+      </c>
+      <c r="C96" s="5">
+        <f>'10_Source_Orders_3M'!C96</f>
+        <v/>
+      </c>
+      <c r="D96" s="5">
+        <f>'10_Source_Orders_3M'!D96</f>
+        <v/>
+      </c>
+      <c r="E96" s="13">
+        <f>'10_Source_Orders_3M'!E96</f>
+        <v/>
+      </c>
+      <c r="F96" s="6">
+        <f>'10_Source_Orders_3M'!F96</f>
+        <v/>
+      </c>
+      <c r="G96" s="5">
+        <f>'10_Source_Orders_3M'!G96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="5">
+        <f>'10_Source_Orders_3M'!A97</f>
+        <v/>
+      </c>
+      <c r="B97" s="5">
+        <f>'10_Source_Orders_3M'!B97</f>
+        <v/>
+      </c>
+      <c r="C97" s="5">
+        <f>'10_Source_Orders_3M'!C97</f>
+        <v/>
+      </c>
+      <c r="D97" s="5">
+        <f>'10_Source_Orders_3M'!D97</f>
+        <v/>
+      </c>
+      <c r="E97" s="13">
+        <f>'10_Source_Orders_3M'!E97</f>
+        <v/>
+      </c>
+      <c r="F97" s="6">
+        <f>'10_Source_Orders_3M'!F97</f>
+        <v/>
+      </c>
+      <c r="G97" s="5">
+        <f>'10_Source_Orders_3M'!G97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="5">
+        <f>'10_Source_Orders_3M'!A98</f>
+        <v/>
+      </c>
+      <c r="B98" s="5">
+        <f>'10_Source_Orders_3M'!B98</f>
+        <v/>
+      </c>
+      <c r="C98" s="5">
+        <f>'10_Source_Orders_3M'!C98</f>
+        <v/>
+      </c>
+      <c r="D98" s="5">
+        <f>'10_Source_Orders_3M'!D98</f>
+        <v/>
+      </c>
+      <c r="E98" s="13">
+        <f>'10_Source_Orders_3M'!E98</f>
+        <v/>
+      </c>
+      <c r="F98" s="6">
+        <f>'10_Source_Orders_3M'!F98</f>
+        <v/>
+      </c>
+      <c r="G98" s="5">
+        <f>'10_Source_Orders_3M'!G98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="5">
+        <f>'10_Source_Orders_3M'!A99</f>
+        <v/>
+      </c>
+      <c r="B99" s="5">
+        <f>'10_Source_Orders_3M'!B99</f>
+        <v/>
+      </c>
+      <c r="C99" s="5">
+        <f>'10_Source_Orders_3M'!C99</f>
+        <v/>
+      </c>
+      <c r="D99" s="5">
+        <f>'10_Source_Orders_3M'!D99</f>
+        <v/>
+      </c>
+      <c r="E99" s="13">
+        <f>'10_Source_Orders_3M'!E99</f>
+        <v/>
+      </c>
+      <c r="F99" s="6">
+        <f>'10_Source_Orders_3M'!F99</f>
+        <v/>
+      </c>
+      <c r="G99" s="5">
+        <f>'10_Source_Orders_3M'!G99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="5">
+        <f>'10_Source_Orders_3M'!A100</f>
+        <v/>
+      </c>
+      <c r="B100" s="5">
+        <f>'10_Source_Orders_3M'!B100</f>
+        <v/>
+      </c>
+      <c r="C100" s="5">
+        <f>'10_Source_Orders_3M'!C100</f>
+        <v/>
+      </c>
+      <c r="D100" s="5">
+        <f>'10_Source_Orders_3M'!D100</f>
+        <v/>
+      </c>
+      <c r="E100" s="13">
+        <f>'10_Source_Orders_3M'!E100</f>
+        <v/>
+      </c>
+      <c r="F100" s="6">
+        <f>'10_Source_Orders_3M'!F100</f>
+        <v/>
+      </c>
+      <c r="G100" s="5">
+        <f>'10_Source_Orders_3M'!G100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="5">
+        <f>'10_Source_Orders_3M'!A101</f>
+        <v/>
+      </c>
+      <c r="B101" s="5">
+        <f>'10_Source_Orders_3M'!B101</f>
+        <v/>
+      </c>
+      <c r="C101" s="5">
+        <f>'10_Source_Orders_3M'!C101</f>
+        <v/>
+      </c>
+      <c r="D101" s="5">
+        <f>'10_Source_Orders_3M'!D101</f>
+        <v/>
+      </c>
+      <c r="E101" s="13">
+        <f>'10_Source_Orders_3M'!E101</f>
+        <v/>
+      </c>
+      <c r="F101" s="6">
+        <f>'10_Source_Orders_3M'!F101</f>
+        <v/>
+      </c>
+      <c r="G101" s="5">
+        <f>'10_Source_Orders_3M'!G101</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="5">
+        <f>'10_Source_Orders_3M'!A102</f>
+        <v/>
+      </c>
+      <c r="B102" s="5">
+        <f>'10_Source_Orders_3M'!B102</f>
+        <v/>
+      </c>
+      <c r="C102" s="5">
+        <f>'10_Source_Orders_3M'!C102</f>
+        <v/>
+      </c>
+      <c r="D102" s="5">
+        <f>'10_Source_Orders_3M'!D102</f>
+        <v/>
+      </c>
+      <c r="E102" s="13">
+        <f>'10_Source_Orders_3M'!E102</f>
+        <v/>
+      </c>
+      <c r="F102" s="6">
+        <f>'10_Source_Orders_3M'!F102</f>
+        <v/>
+      </c>
+      <c r="G102" s="5">
+        <f>'10_Source_Orders_3M'!G102</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="5">
+        <f>'10_Source_Orders_3M'!A103</f>
+        <v/>
+      </c>
+      <c r="B103" s="5">
+        <f>'10_Source_Orders_3M'!B103</f>
+        <v/>
+      </c>
+      <c r="C103" s="5">
+        <f>'10_Source_Orders_3M'!C103</f>
+        <v/>
+      </c>
+      <c r="D103" s="5">
+        <f>'10_Source_Orders_3M'!D103</f>
+        <v/>
+      </c>
+      <c r="E103" s="13">
+        <f>'10_Source_Orders_3M'!E103</f>
+        <v/>
+      </c>
+      <c r="F103" s="6">
+        <f>'10_Source_Orders_3M'!F103</f>
+        <v/>
+      </c>
+      <c r="G103" s="5">
+        <f>'10_Source_Orders_3M'!G103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="5">
+        <f>'10_Source_Orders_3M'!A104</f>
+        <v/>
+      </c>
+      <c r="B104" s="5">
+        <f>'10_Source_Orders_3M'!B104</f>
+        <v/>
+      </c>
+      <c r="C104" s="5">
+        <f>'10_Source_Orders_3M'!C104</f>
+        <v/>
+      </c>
+      <c r="D104" s="5">
+        <f>'10_Source_Orders_3M'!D104</f>
+        <v/>
+      </c>
+      <c r="E104" s="13">
+        <f>'10_Source_Orders_3M'!E104</f>
+        <v/>
+      </c>
+      <c r="F104" s="6">
+        <f>'10_Source_Orders_3M'!F104</f>
+        <v/>
+      </c>
+      <c r="G104" s="5">
+        <f>'10_Source_Orders_3M'!G104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="5">
+        <f>'10_Source_Orders_3M'!A105</f>
+        <v/>
+      </c>
+      <c r="B105" s="5">
+        <f>'10_Source_Orders_3M'!B105</f>
+        <v/>
+      </c>
+      <c r="C105" s="5">
+        <f>'10_Source_Orders_3M'!C105</f>
+        <v/>
+      </c>
+      <c r="D105" s="5">
+        <f>'10_Source_Orders_3M'!D105</f>
+        <v/>
+      </c>
+      <c r="E105" s="13">
+        <f>'10_Source_Orders_3M'!E105</f>
+        <v/>
+      </c>
+      <c r="F105" s="6">
+        <f>'10_Source_Orders_3M'!F105</f>
+        <v/>
+      </c>
+      <c r="G105" s="5">
+        <f>'10_Source_Orders_3M'!G105</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="5">
+        <f>'10_Source_Orders_3M'!A106</f>
+        <v/>
+      </c>
+      <c r="B106" s="5">
+        <f>'10_Source_Orders_3M'!B106</f>
+        <v/>
+      </c>
+      <c r="C106" s="5">
+        <f>'10_Source_Orders_3M'!C106</f>
+        <v/>
+      </c>
+      <c r="D106" s="5">
+        <f>'10_Source_Orders_3M'!D106</f>
+        <v/>
+      </c>
+      <c r="E106" s="13">
+        <f>'10_Source_Orders_3M'!E106</f>
+        <v/>
+      </c>
+      <c r="F106" s="6">
+        <f>'10_Source_Orders_3M'!F106</f>
+        <v/>
+      </c>
+      <c r="G106" s="5">
+        <f>'10_Source_Orders_3M'!G106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="5">
+        <f>'10_Source_Orders_3M'!A107</f>
+        <v/>
+      </c>
+      <c r="B107" s="5">
+        <f>'10_Source_Orders_3M'!B107</f>
+        <v/>
+      </c>
+      <c r="C107" s="5">
+        <f>'10_Source_Orders_3M'!C107</f>
+        <v/>
+      </c>
+      <c r="D107" s="5">
+        <f>'10_Source_Orders_3M'!D107</f>
+        <v/>
+      </c>
+      <c r="E107" s="13">
+        <f>'10_Source_Orders_3M'!E107</f>
+        <v/>
+      </c>
+      <c r="F107" s="6">
+        <f>'10_Source_Orders_3M'!F107</f>
+        <v/>
+      </c>
+      <c r="G107" s="5">
+        <f>'10_Source_Orders_3M'!G107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="5">
+        <f>'10_Source_Orders_3M'!A108</f>
+        <v/>
+      </c>
+      <c r="B108" s="5">
+        <f>'10_Source_Orders_3M'!B108</f>
+        <v/>
+      </c>
+      <c r="C108" s="5">
+        <f>'10_Source_Orders_3M'!C108</f>
+        <v/>
+      </c>
+      <c r="D108" s="5">
+        <f>'10_Source_Orders_3M'!D108</f>
+        <v/>
+      </c>
+      <c r="E108" s="13">
+        <f>'10_Source_Orders_3M'!E108</f>
+        <v/>
+      </c>
+      <c r="F108" s="6">
+        <f>'10_Source_Orders_3M'!F108</f>
+        <v/>
+      </c>
+      <c r="G108" s="5">
+        <f>'10_Source_Orders_3M'!G108</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="5">
+        <f>'10_Source_Orders_3M'!A109</f>
+        <v/>
+      </c>
+      <c r="B109" s="5">
+        <f>'10_Source_Orders_3M'!B109</f>
+        <v/>
+      </c>
+      <c r="C109" s="5">
+        <f>'10_Source_Orders_3M'!C109</f>
+        <v/>
+      </c>
+      <c r="D109" s="5">
+        <f>'10_Source_Orders_3M'!D109</f>
+        <v/>
+      </c>
+      <c r="E109" s="13">
+        <f>'10_Source_Orders_3M'!E109</f>
+        <v/>
+      </c>
+      <c r="F109" s="6">
+        <f>'10_Source_Orders_3M'!F109</f>
+        <v/>
+      </c>
+      <c r="G109" s="5">
+        <f>'10_Source_Orders_3M'!G109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="5">
+        <f>'10_Source_Orders_3M'!A110</f>
+        <v/>
+      </c>
+      <c r="B110" s="5">
+        <f>'10_Source_Orders_3M'!B110</f>
+        <v/>
+      </c>
+      <c r="C110" s="5">
+        <f>'10_Source_Orders_3M'!C110</f>
+        <v/>
+      </c>
+      <c r="D110" s="5">
+        <f>'10_Source_Orders_3M'!D110</f>
+        <v/>
+      </c>
+      <c r="E110" s="13">
+        <f>'10_Source_Orders_3M'!E110</f>
+        <v/>
+      </c>
+      <c r="F110" s="6">
+        <f>'10_Source_Orders_3M'!F110</f>
+        <v/>
+      </c>
+      <c r="G110" s="5">
+        <f>'10_Source_Orders_3M'!G110</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="5">
+        <f>'10_Source_Orders_3M'!A111</f>
+        <v/>
+      </c>
+      <c r="B111" s="5">
+        <f>'10_Source_Orders_3M'!B111</f>
+        <v/>
+      </c>
+      <c r="C111" s="5">
+        <f>'10_Source_Orders_3M'!C111</f>
+        <v/>
+      </c>
+      <c r="D111" s="5">
+        <f>'10_Source_Orders_3M'!D111</f>
+        <v/>
+      </c>
+      <c r="E111" s="13">
+        <f>'10_Source_Orders_3M'!E111</f>
+        <v/>
+      </c>
+      <c r="F111" s="6">
+        <f>'10_Source_Orders_3M'!F111</f>
+        <v/>
+      </c>
+      <c r="G111" s="5">
+        <f>'10_Source_Orders_3M'!G111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="5">
+        <f>'10_Source_Orders_3M'!A112</f>
+        <v/>
+      </c>
+      <c r="B112" s="5">
+        <f>'10_Source_Orders_3M'!B112</f>
+        <v/>
+      </c>
+      <c r="C112" s="5">
+        <f>'10_Source_Orders_3M'!C112</f>
+        <v/>
+      </c>
+      <c r="D112" s="5">
+        <f>'10_Source_Orders_3M'!D112</f>
+        <v/>
+      </c>
+      <c r="E112" s="13">
+        <f>'10_Source_Orders_3M'!E112</f>
+        <v/>
+      </c>
+      <c r="F112" s="6">
+        <f>'10_Source_Orders_3M'!F112</f>
+        <v/>
+      </c>
+      <c r="G112" s="5">
+        <f>'10_Source_Orders_3M'!G112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="5">
+        <f>'10_Source_Orders_3M'!A113</f>
+        <v/>
+      </c>
+      <c r="B113" s="5">
+        <f>'10_Source_Orders_3M'!B113</f>
+        <v/>
+      </c>
+      <c r="C113" s="5">
+        <f>'10_Source_Orders_3M'!C113</f>
+        <v/>
+      </c>
+      <c r="D113" s="5">
+        <f>'10_Source_Orders_3M'!D113</f>
+        <v/>
+      </c>
+      <c r="E113" s="13">
+        <f>'10_Source_Orders_3M'!E113</f>
+        <v/>
+      </c>
+      <c r="F113" s="6">
+        <f>'10_Source_Orders_3M'!F113</f>
+        <v/>
+      </c>
+      <c r="G113" s="5">
+        <f>'10_Source_Orders_3M'!G113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="5">
+        <f>'10_Source_Orders_3M'!A114</f>
+        <v/>
+      </c>
+      <c r="B114" s="5">
+        <f>'10_Source_Orders_3M'!B114</f>
+        <v/>
+      </c>
+      <c r="C114" s="5">
+        <f>'10_Source_Orders_3M'!C114</f>
+        <v/>
+      </c>
+      <c r="D114" s="5">
+        <f>'10_Source_Orders_3M'!D114</f>
+        <v/>
+      </c>
+      <c r="E114" s="13">
+        <f>'10_Source_Orders_3M'!E114</f>
+        <v/>
+      </c>
+      <c r="F114" s="6">
+        <f>'10_Source_Orders_3M'!F114</f>
+        <v/>
+      </c>
+      <c r="G114" s="5">
+        <f>'10_Source_Orders_3M'!G114</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="5">
+        <f>'10_Source_Orders_3M'!A115</f>
+        <v/>
+      </c>
+      <c r="B115" s="5">
+        <f>'10_Source_Orders_3M'!B115</f>
+        <v/>
+      </c>
+      <c r="C115" s="5">
+        <f>'10_Source_Orders_3M'!C115</f>
+        <v/>
+      </c>
+      <c r="D115" s="5">
+        <f>'10_Source_Orders_3M'!D115</f>
+        <v/>
+      </c>
+      <c r="E115" s="13">
+        <f>'10_Source_Orders_3M'!E115</f>
+        <v/>
+      </c>
+      <c r="F115" s="6">
+        <f>'10_Source_Orders_3M'!F115</f>
+        <v/>
+      </c>
+      <c r="G115" s="5">
+        <f>'10_Source_Orders_3M'!G115</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="5">
+        <f>'10_Source_Orders_3M'!A116</f>
+        <v/>
+      </c>
+      <c r="B116" s="5">
+        <f>'10_Source_Orders_3M'!B116</f>
+        <v/>
+      </c>
+      <c r="C116" s="5">
+        <f>'10_Source_Orders_3M'!C116</f>
+        <v/>
+      </c>
+      <c r="D116" s="5">
+        <f>'10_Source_Orders_3M'!D116</f>
+        <v/>
+      </c>
+      <c r="E116" s="13">
+        <f>'10_Source_Orders_3M'!E116</f>
+        <v/>
+      </c>
+      <c r="F116" s="6">
+        <f>'10_Source_Orders_3M'!F116</f>
+        <v/>
+      </c>
+      <c r="G116" s="5">
+        <f>'10_Source_Orders_3M'!G116</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="5">
+        <f>'10_Source_Orders_3M'!A117</f>
+        <v/>
+      </c>
+      <c r="B117" s="5">
+        <f>'10_Source_Orders_3M'!B117</f>
+        <v/>
+      </c>
+      <c r="C117" s="5">
+        <f>'10_Source_Orders_3M'!C117</f>
+        <v/>
+      </c>
+      <c r="D117" s="5">
+        <f>'10_Source_Orders_3M'!D117</f>
+        <v/>
+      </c>
+      <c r="E117" s="13">
+        <f>'10_Source_Orders_3M'!E117</f>
+        <v/>
+      </c>
+      <c r="F117" s="6">
+        <f>'10_Source_Orders_3M'!F117</f>
+        <v/>
+      </c>
+      <c r="G117" s="5">
+        <f>'10_Source_Orders_3M'!G117</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="5">
+        <f>'10_Source_Orders_3M'!A118</f>
+        <v/>
+      </c>
+      <c r="B118" s="5">
+        <f>'10_Source_Orders_3M'!B118</f>
+        <v/>
+      </c>
+      <c r="C118" s="5">
+        <f>'10_Source_Orders_3M'!C118</f>
+        <v/>
+      </c>
+      <c r="D118" s="5">
+        <f>'10_Source_Orders_3M'!D118</f>
+        <v/>
+      </c>
+      <c r="E118" s="13">
+        <f>'10_Source_Orders_3M'!E118</f>
+        <v/>
+      </c>
+      <c r="F118" s="6">
+        <f>'10_Source_Orders_3M'!F118</f>
+        <v/>
+      </c>
+      <c r="G118" s="5">
+        <f>'10_Source_Orders_3M'!G118</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="5">
+        <f>'10_Source_Orders_3M'!A119</f>
+        <v/>
+      </c>
+      <c r="B119" s="5">
+        <f>'10_Source_Orders_3M'!B119</f>
+        <v/>
+      </c>
+      <c r="C119" s="5">
+        <f>'10_Source_Orders_3M'!C119</f>
+        <v/>
+      </c>
+      <c r="D119" s="5">
+        <f>'10_Source_Orders_3M'!D119</f>
+        <v/>
+      </c>
+      <c r="E119" s="13">
+        <f>'10_Source_Orders_3M'!E119</f>
+        <v/>
+      </c>
+      <c r="F119" s="6">
+        <f>'10_Source_Orders_3M'!F119</f>
+        <v/>
+      </c>
+      <c r="G119" s="5">
+        <f>'10_Source_Orders_3M'!G119</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="5">
+        <f>'10_Source_Orders_3M'!A120</f>
+        <v/>
+      </c>
+      <c r="B120" s="5">
+        <f>'10_Source_Orders_3M'!B120</f>
+        <v/>
+      </c>
+      <c r="C120" s="5">
+        <f>'10_Source_Orders_3M'!C120</f>
+        <v/>
+      </c>
+      <c r="D120" s="5">
+        <f>'10_Source_Orders_3M'!D120</f>
+        <v/>
+      </c>
+      <c r="E120" s="13">
+        <f>'10_Source_Orders_3M'!E120</f>
+        <v/>
+      </c>
+      <c r="F120" s="6">
+        <f>'10_Source_Orders_3M'!F120</f>
+        <v/>
+      </c>
+      <c r="G120" s="5">
+        <f>'10_Source_Orders_3M'!G120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="5">
+        <f>'10_Source_Orders_3M'!A121</f>
+        <v/>
+      </c>
+      <c r="B121" s="5">
+        <f>'10_Source_Orders_3M'!B121</f>
+        <v/>
+      </c>
+      <c r="C121" s="5">
+        <f>'10_Source_Orders_3M'!C121</f>
+        <v/>
+      </c>
+      <c r="D121" s="5">
+        <f>'10_Source_Orders_3M'!D121</f>
+        <v/>
+      </c>
+      <c r="E121" s="13">
+        <f>'10_Source_Orders_3M'!E121</f>
+        <v/>
+      </c>
+      <c r="F121" s="6">
+        <f>'10_Source_Orders_3M'!F121</f>
+        <v/>
+      </c>
+      <c r="G121" s="5">
+        <f>'10_Source_Orders_3M'!G121</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="5">
+        <f>'10_Source_Orders_3M'!A122</f>
+        <v/>
+      </c>
+      <c r="B122" s="5">
+        <f>'10_Source_Orders_3M'!B122</f>
+        <v/>
+      </c>
+      <c r="C122" s="5">
+        <f>'10_Source_Orders_3M'!C122</f>
+        <v/>
+      </c>
+      <c r="D122" s="5">
+        <f>'10_Source_Orders_3M'!D122</f>
+        <v/>
+      </c>
+      <c r="E122" s="13">
+        <f>'10_Source_Orders_3M'!E122</f>
+        <v/>
+      </c>
+      <c r="F122" s="6">
+        <f>'10_Source_Orders_3M'!F122</f>
+        <v/>
+      </c>
+      <c r="G122" s="5">
+        <f>'10_Source_Orders_3M'!G122</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="5">
+        <f>'10_Source_Orders_3M'!A123</f>
+        <v/>
+      </c>
+      <c r="B123" s="5">
+        <f>'10_Source_Orders_3M'!B123</f>
+        <v/>
+      </c>
+      <c r="C123" s="5">
+        <f>'10_Source_Orders_3M'!C123</f>
+        <v/>
+      </c>
+      <c r="D123" s="5">
+        <f>'10_Source_Orders_3M'!D123</f>
+        <v/>
+      </c>
+      <c r="E123" s="13">
+        <f>'10_Source_Orders_3M'!E123</f>
+        <v/>
+      </c>
+      <c r="F123" s="6">
+        <f>'10_Source_Orders_3M'!F123</f>
+        <v/>
+      </c>
+      <c r="G123" s="5">
+        <f>'10_Source_Orders_3M'!G123</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="5">
+        <f>'10_Source_Orders_3M'!A124</f>
+        <v/>
+      </c>
+      <c r="B124" s="5">
+        <f>'10_Source_Orders_3M'!B124</f>
+        <v/>
+      </c>
+      <c r="C124" s="5">
+        <f>'10_Source_Orders_3M'!C124</f>
+        <v/>
+      </c>
+      <c r="D124" s="5">
+        <f>'10_Source_Orders_3M'!D124</f>
+        <v/>
+      </c>
+      <c r="E124" s="13">
+        <f>'10_Source_Orders_3M'!E124</f>
+        <v/>
+      </c>
+      <c r="F124" s="6">
+        <f>'10_Source_Orders_3M'!F124</f>
+        <v/>
+      </c>
+      <c r="G124" s="5">
+        <f>'10_Source_Orders_3M'!G124</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="5">
+        <f>'10_Source_Orders_3M'!A125</f>
+        <v/>
+      </c>
+      <c r="B125" s="5">
+        <f>'10_Source_Orders_3M'!B125</f>
+        <v/>
+      </c>
+      <c r="C125" s="5">
+        <f>'10_Source_Orders_3M'!C125</f>
+        <v/>
+      </c>
+      <c r="D125" s="5">
+        <f>'10_Source_Orders_3M'!D125</f>
+        <v/>
+      </c>
+      <c r="E125" s="13">
+        <f>'10_Source_Orders_3M'!E125</f>
+        <v/>
+      </c>
+      <c r="F125" s="6">
+        <f>'10_Source_Orders_3M'!F125</f>
+        <v/>
+      </c>
+      <c r="G125" s="5">
+        <f>'10_Source_Orders_3M'!G125</f>
         <v/>
       </c>
     </row>
@@ -11897,7 +13916,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
@@ -12045,7 +14064,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>501457852.9912034</v>
+        <v>501457853.0157034</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -12167,7 +14186,7 @@
         <v>30550000</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>27169999.9970502</v>
+        <v>27170000.00460673</v>
       </c>
       <c r="G12" s="6">
         <f>F12-E12</f>
@@ -12209,7 +14228,7 @@
         <v>113409768</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>108109766.991854</v>
+        <v>108109767.0078188</v>
       </c>
       <c r="G13" s="6">
         <f>F13-E13</f>
@@ -12262,11 +14281,11 @@
         <v/>
       </c>
       <c r="I14" s="5" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>I143 / AB143</t>
+          <t>I149 / AB149</t>
         </is>
       </c>
     </row>
@@ -12304,11 +14323,11 @@
         <v/>
       </c>
       <c r="I15" s="5" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>I160 / AB160</t>
+          <t>I166 / AB166</t>
         </is>
       </c>
     </row>
@@ -12335,7 +14354,7 @@
         <v>293798902</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>258666645.9991515</v>
+        <v>258666645.9970825</v>
       </c>
       <c r="G16" s="6">
         <f>F16-E16</f>
@@ -12346,11 +14365,11 @@
         <v/>
       </c>
       <c r="I16" s="5" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>I185 / AB185</t>
+          <t>I191 / AB191</t>
         </is>
       </c>
     </row>
@@ -12388,18 +14407,18 @@
         <v/>
       </c>
       <c r="I17" s="5" t="n">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>I257 / AB257</t>
+          <t>I265 / AB265</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Direct cost / root budget group</t>
+          <t>Financial summary / WBS 1-17</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -12430,18 +14449,18 @@
         <v/>
       </c>
       <c r="I18" s="5" t="n">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>I276 / AB276</t>
+          <t>I284 / AB284</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Direct cost / root budget group</t>
+          <t>Financial summary / WBS 1-17</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
@@ -12468,11 +14487,11 @@
         <v/>
       </c>
       <c r="I19" s="5" t="n">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>I279 / AB279</t>
+          <t>I287 / AB287</t>
         </is>
       </c>
     </row>
@@ -12495,7 +14514,7 @@
         <v>505757853</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>501457852.9912035</v>
+        <v>501457853.0157036</v>
       </c>
       <c r="G20" s="6">
         <f>F20-E20</f>
@@ -12506,11 +14525,11 @@
         <v/>
       </c>
       <c r="I20" s="5" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>I283 / AB283</t>
+          <t>I291 / AB291</t>
         </is>
       </c>
     </row>
@@ -12548,11 +14567,11 @@
         <v/>
       </c>
       <c r="I21" s="5" t="n">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>I290 / AB290</t>
+          <t>I298 / AB298</t>
         </is>
       </c>
     </row>
@@ -12579,7 +14598,7 @@
         <v>546148867.15</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>563915104.8630807</v>
+        <v>563593205.4394034</v>
       </c>
       <c r="G22" s="6">
         <f>F22-E22</f>
@@ -12590,11 +14609,11 @@
         <v/>
       </c>
       <c r="I22" s="5" t="n">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>I428 / AB428</t>
+          <t>I440 / AB440</t>
         </is>
       </c>
     </row>
@@ -12617,7 +14636,7 @@
         <v>85237132.84999999</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>63170895.14</v>
+        <v>63492794.56</v>
       </c>
       <c r="G23" s="6">
         <f>F23-E23</f>
@@ -12628,11 +14647,11 @@
         <v/>
       </c>
       <c r="I23" s="5" t="n">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>I429 / AB429</t>
+          <t>I441 / AB441</t>
         </is>
       </c>
     </row>
@@ -12655,7 +14674,7 @@
         <v>0.1560694125299533</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.1120219951464821</v>
+        <v>0.1126571327461233</v>
       </c>
       <c r="G24" s="6">
         <f>F24-E24</f>
@@ -12666,11 +14685,11 @@
         <v/>
       </c>
       <c r="I24" s="5" t="n">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>I430 / AB430</t>
+          <t>I442 / AB442</t>
         </is>
       </c>
     </row>
@@ -12704,11 +14723,11 @@
         <v/>
       </c>
       <c r="I25" s="5" t="n">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>I440 / AB440</t>
+          <t>I452 / AB452</t>
         </is>
       </c>
     </row>
@@ -12742,11 +14761,11 @@
         <v/>
       </c>
       <c r="I26" s="5" t="n">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>I441 / AB441</t>
+          <t>I453 / AB453</t>
         </is>
       </c>
     </row>
@@ -12785,11 +14804,11 @@
         <v/>
       </c>
       <c r="I27" s="5" t="n">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>I442 / AB442</t>
+          <t>I454 / AB454</t>
         </is>
       </c>
     </row>
@@ -12823,11 +14842,11 @@
         <v/>
       </c>
       <c r="I28" s="5" t="n">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>I445 / AB445</t>
+          <t>I457 / AB457</t>
         </is>
       </c>
     </row>
@@ -12850,7 +14869,7 @@
         <v>85237132.84999999</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>63170895.14</v>
+        <v>63492794.56</v>
       </c>
       <c r="G29" s="6">
         <f>F29-E29</f>
@@ -12861,11 +14880,11 @@
         <v/>
       </c>
       <c r="I29" s="5" t="n">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>I446 / AB446</t>
+          <t>I458 / AB458</t>
         </is>
       </c>
     </row>
@@ -12892,7 +14911,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>63170895.14</v>
+        <v>63492794.56</v>
       </c>
       <c r="G30" s="6">
         <f>F30-E30</f>
@@ -12903,11 +14922,11 @@
         <v/>
       </c>
       <c r="I30" s="5" t="n">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>I447 / AB447</t>
+          <t>I459 / AB459</t>
         </is>
       </c>
     </row>
@@ -12930,7 +14949,7 @@
         <v>45080960.4</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>31178096.01959363</v>
+        <v>31178095.3777719</v>
       </c>
       <c r="G31" s="6">
         <f>F31-E31</f>
@@ -12941,11 +14960,11 @@
         <v/>
       </c>
       <c r="I31" s="5" t="n">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>I463 / AB463</t>
+          <t>I475 / AB475</t>
         </is>
       </c>
     </row>
@@ -12968,7 +14987,7 @@
         <v>40156172.45</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>31992799.12040637</v>
+        <v>32314699.18222811</v>
       </c>
       <c r="G32" s="6">
         <f>F32-E32</f>
@@ -12979,11 +14998,11 @@
         <v/>
       </c>
       <c r="I32" s="5" t="n">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>I465 / AB465</t>
+          <t>I477 / AB477</t>
         </is>
       </c>
     </row>
@@ -13006,7 +15025,7 @@
         <v>0.06360003619022277</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.05101820024750411</v>
+        <v>0.05153152706682673</v>
       </c>
       <c r="G33" s="6">
         <f>F33-E33</f>
@@ -13017,11 +15036,11 @@
         <v/>
       </c>
       <c r="I33" s="5" t="n">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>I466 / AB466</t>
+          <t>I478 / AB478</t>
         </is>
       </c>
     </row>
@@ -13044,7 +15063,7 @@
         <v>40156172.45</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>54091334.27040637</v>
+        <v>54413234.33222811</v>
       </c>
       <c r="G34" s="6">
         <f>F34-E34</f>
@@ -13055,11 +15074,11 @@
         <v/>
       </c>
       <c r="I34" s="5" t="n">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>I468 / AB468</t>
+          <t>I480 / AB480</t>
         </is>
       </c>
     </row>
@@ -13082,7 +15101,7 @@
         <v>0.06360003619022277</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.08625823933305218</v>
+        <v>0.08677156615237482</v>
       </c>
       <c r="G35" s="6">
         <f>F35-E35</f>
@@ -13093,11 +15112,11 @@
         <v/>
       </c>
       <c r="I35" s="5" t="n">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>I469 / AB469</t>
+          <t>I481 / AB481</t>
         </is>
       </c>
     </row>
@@ -13131,11 +15150,11 @@
         <v/>
       </c>
       <c r="I36" s="5" t="n">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>I476 / AB476</t>
+          <t>I488 / AB488</t>
         </is>
       </c>
     </row>
@@ -13169,11 +15188,11 @@
         <v/>
       </c>
       <c r="I37" s="5" t="n">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>I477 / AB477</t>
+          <t>I489 / AB489</t>
         </is>
       </c>
     </row>
@@ -13347,7 +15366,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>5765471.942780515</v>
+        <v>6224860.46888889</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -13369,7 +15388,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>6905734.093098548</v>
+        <v>3080461.270952381</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
@@ -13391,7 +15410,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>8873827.146967065</v>
+        <v>10298268.19915018</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
@@ -13413,7 +15432,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>10285632.29324826</v>
+        <v>24920618.49075124</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -13435,7 +15454,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>10740381.93769237</v>
+        <v>11044595.67496808</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -13457,7 +15476,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>11563023.0631719</v>
+        <v>12651060.24080475</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -13479,7 +15498,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>16961088.66094667</v>
+        <v>16840968.47857952</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
@@ -13501,7 +15520,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>20646901.92593019</v>
+        <v>21259070.9007059</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
@@ -13523,7 +15542,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>16967267.57127333</v>
+        <v>17153971.63890618</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
@@ -13545,7 +15564,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>19654432.33260666</v>
+        <v>19773194.85023951</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
@@ -13567,7 +15586,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>27037107.25342266</v>
+        <v>24861930.3932784</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
@@ -13589,7 +15608,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>31052003.95498933</v>
+        <v>27968549.50484506</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
@@ -13611,7 +15630,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>37364643.97098334</v>
+        <v>35342841.76083907</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
@@ -13633,7 +15652,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>32844839.10125062</v>
+        <v>30823036.89110636</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
@@ -13655,7 +15674,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>34135803.94847285</v>
+        <v>32016185.05832859</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
@@ -13677,7 +15696,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>28870543.17699507</v>
+        <v>26848740.96685081</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
@@ -13699,7 +15718,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>25137377.52638055</v>
+        <v>23300575.31623628</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
@@ -13721,7 +15740,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>19034792.32649231</v>
+        <v>17197990.11634805</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
@@ -13743,7 +15762,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>24283221.76122564</v>
+        <v>22446419.55108138</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
@@ -13765,7 +15784,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>12421394.06224786</v>
+        <v>10601806.8521036</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
@@ -13787,7 +15806,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>10204106.98265897</v>
+        <v>8350089.772514713</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
@@ -13809,7 +15828,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>18501734.79064787</v>
+        <v>24637776.5005036</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
@@ -14073,7 +16092,7 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>42828572.34</v>
+        <v>44750308.29</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>

--- a/docs/reports/WTE_Dashboard_Report.xlsx
+++ b/docs/reports/WTE_Dashboard_Report.xlsx
@@ -828,7 +828,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generato: 2026-05-20 11:03</t>
+          <t>Generato: 2026-05-22 12:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1459,7 +1459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>8.5.2.2</t>
+          <t>8.5.1</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Office kitchen furniture  ECd_36</t>
+          <t>Internet Connection ECd_37</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="E2" s="13" t="n">
-        <v>46070</v>
+        <v>46073</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>13414.64</v>
+        <v>27350</v>
       </c>
       <c r="G2" s="5" t="n"/>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>8.5.1</t>
+          <t>8.1.3.3</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Internet Connection ECd_37</t>
+          <t>Open order - sanitary industry assortment ECd_39</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="E3" s="13" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>27350</v>
+        <v>30000</v>
       </c>
       <c r="G3" s="5" t="n"/>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>8.1.3.3</t>
+          <t>8.1.3.4</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Open order - sanitary industry assortment ECd_39</t>
+          <t>Open order - sanitary industry assortment ECd_40</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8.1.3.4</t>
+          <t>1.2.2</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Open order - sanitary industry assortment ECd_40</t>
+          <t>Detailed design: boiler support steel structure and equipment support structures</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="E5" s="13" t="n">
-        <v>46077</v>
+        <v>46080</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>30000</v>
+        <v>943000</v>
       </c>
       <c r="G5" s="5" t="n"/>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>8.4.1.1</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Detailed design: boiler support steel structure and equipment support structures</t>
+          <t>Personal Occupational Health and Safety Equipment ECd_43</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="E6" s="13" t="n">
-        <v>46080</v>
+        <v>46090</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>943000</v>
+        <v>30000</v>
       </c>
       <c r="G6" s="5" t="n"/>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>8.4.1.1</t>
+          <t>8.3.1.2</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Personal Occupational Health and Safety Equipment ECd_43</t>
+          <t>Generator rental ECd_44</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="E7" s="13" t="n">
-        <v>46090</v>
+        <v>46096</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>30000</v>
+        <v>23904</v>
       </c>
       <c r="G7" s="5" t="n"/>
     </row>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>8.3.1.2</t>
+          <t>8.7.1.6</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Generator rental ECd_44</t>
+          <t>Purchase of road signs ECd_42</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1707,7 +1707,7 @@
         <v>46096</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>23904</v>
+        <v>2000</v>
       </c>
       <c r="G8" s="5" t="n"/>
     </row>
@@ -1719,12 +1719,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.6</t>
+          <t>8.7.1.7</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Purchase of road signs ECd_42</t>
+          <t>Purchase of rubble for the construction of storage yards and work platforms ECd_45</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1736,7 +1736,7 @@
         <v>46096</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2000</v>
+        <v>83200</v>
       </c>
       <c r="G9" s="5" t="n"/>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.7</t>
+          <t>2.11.5.3</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Purchase of rubble for the construction of storage yards and work platforms ECd_45</t>
+          <t>Concrete slab installation on the ground</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1762,12 +1762,16 @@
         </is>
       </c>
       <c r="E10" s="13" t="n">
-        <v>46096</v>
+        <v>46106</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>83200</v>
-      </c>
-      <c r="G10" s="5" t="n"/>
+        <v>1735392.78</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Agnieszka Zając</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1777,12 +1781,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2.11.5.3</t>
+          <t>2.14.2.2</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Concrete slab installation on the ground</t>
+          <t>External road - aggregate delivery ECd_46</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1794,7 +1798,7 @@
         <v>46106</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1735392.78</v>
+        <v>134400</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
@@ -1810,12 +1814,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2.14.2.2</t>
+          <t>2.4.1</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>External road - aggregate delivery ECd_46</t>
+          <t>Insulation - work</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1827,7 +1831,7 @@
         <v>46106</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>134400</v>
+        <v>733045.25</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
@@ -1843,12 +1847,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2.4.1</t>
+          <t>2.5.1.3</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Insulation - work</t>
+          <t>Construction of reinforced concrete foundations and underground structures</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1860,7 +1864,7 @@
         <v>46106</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>733045.25</v>
+        <v>5276959.37</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
@@ -1876,12 +1880,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2.5.1.3</t>
+          <t>2.5.2.1</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Construction of reinforced concrete foundations and underground structures</t>
+          <t>Reinforced concrete structure of the above-ground part of the B1 building - delivery and assembly of prefabricated elements</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1893,11 +1897,11 @@
         <v>46106</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>5276959.37</v>
+        <v>16616880</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Jan Szczubiał</t>
         </is>
       </c>
     </row>
@@ -1909,12 +1913,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.1</t>
+          <t>2.5.2.2.3</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the B1 building - delivery and assembly of prefabricated elements</t>
+          <t>Reinforced concrete structure of the above-ground part of the B3 building - delivery and assembly of prefabricated elements</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1926,7 +1930,7 @@
         <v>46106</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>16616880</v>
+        <v>2115950</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
@@ -1942,12 +1946,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.2.3</t>
+          <t>2.5.2.2.4</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the B3 building - delivery and assembly of prefabricated elements</t>
+          <t>Reinforced concrete structure of the above-ground part of the other buildings</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1959,7 +1963,7 @@
         <v>46106</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>2115950</v>
+        <v>708072.75</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
@@ -1975,12 +1979,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.2.4</t>
+          <t>2.6.2.1</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the other buildings</t>
+          <t>Precast reinforced concrete structure of facility B3 (change from steel structure compared to the acquisition stage)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1992,11 +1996,11 @@
         <v>46106</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>708072.75</v>
+        <v>1004390</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Jan Szczubiał</t>
+          <t>Robert Klimczak</t>
         </is>
       </c>
     </row>
@@ -2008,12 +2012,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2.6.2.1</t>
+          <t>2.6.3.1</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Precast reinforced concrete structure of facility B3 (change from steel structure compared to the acquisition stage)</t>
+          <t>Precast reinforced concrete structure of facility B4 (change from steel structure compared to the acquisition stage)</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -2025,7 +2029,7 @@
         <v>46106</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1004390</v>
+        <v>246780</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
@@ -2041,12 +2045,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2.6.3.1</t>
+          <t>2.14.2.1</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Precast reinforced concrete structure of facility B4 (change from steel structure compared to the acquisition stage)</t>
+          <t>External road- sub-base construction</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -2055,14 +2059,14 @@
         </is>
       </c>
       <c r="E19" s="13" t="n">
-        <v>46106</v>
+        <v>46122</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>246780</v>
+        <v>250640</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Robert Klimczak</t>
+          <t>Agnieszka Zając</t>
         </is>
       </c>
     </row>
@@ -2074,12 +2078,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2.14.2.1</t>
+          <t>8.3.1.1</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>External road- sub-base construction</t>
+          <t>Electricity Costs</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2091,13 +2095,9 @@
         <v>46122</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>250640</v>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Agnieszka Zając</t>
-        </is>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="G20" s="5" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>8.3.1.1</t>
+          <t>8.7.1.4</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Electricity Costs</t>
+          <t>Construction of aggregate squares</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -2124,9 +2124,13 @@
         <v>46122</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G21" s="5" t="n"/>
+        <v>124700</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Agnieszka Zając</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -2136,12 +2140,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.4</t>
+          <t>8.8.4</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Construction of aggregate squares</t>
+          <t>Removing collisions related to site preparation and construction</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2153,13 +2157,9 @@
         <v>46122</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>124700</v>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Agnieszka Zając</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>8.8.4</t>
+          <t>8.8.4.1</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Removing collisions related to site preparation and construction</t>
+          <t>Removal of existing reinforced concrete foundations in the vicinity of Building B2</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2186,7 +2186,7 @@
         <v>46122</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G23" s="5" t="n"/>
     </row>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>8.8.4.1</t>
+          <t>5.10.2</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Removal of existing reinforced concrete foundations in the vicinity of Building B2</t>
+          <t>Auxiliary crane and hoists for the maintenance of the steam turbine</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -2212,12 +2212,16 @@
         </is>
       </c>
       <c r="E24" s="13" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G24" s="5" t="n"/>
+        <v>499000</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -2227,12 +2231,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>5.10.2</t>
+          <t>5.2.1</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary crane and hoists for the maintenance of the steam turbine</t>
+          <t>Overhead crane, grab and operator seat + Spare Grab</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2244,7 +2248,7 @@
         <v>46125</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>499000</v>
+        <v>8701000</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
@@ -2260,12 +2264,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>5.2.1</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Overhead crane, grab and operator seat + Spare Grab</t>
+          <t>Stack</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -2274,10 +2278,10 @@
         </is>
       </c>
       <c r="E26" s="13" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>8701000</v>
+        <v>1498200</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
@@ -2293,12 +2297,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.4.1.1</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Stack</t>
+          <t>Boiler - pressure parts</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2310,11 +2314,11 @@
         <v>46127</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1498200</v>
+        <v>45990000</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2330,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>5.4.1.1</t>
+          <t>8.3.5</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Boiler - pressure parts</t>
+          <t>Construction Waste Removal  ECd_38</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2343,13 +2347,9 @@
         <v>46127</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
+        <v>290720</v>
+      </c>
+      <c r="G28" s="5" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>8.3.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Construction Waste Removal  ECd_38</t>
+          <t>Drainage</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="E29" s="13" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>290720</v>
+        <v>0</v>
       </c>
       <c r="G29" s="5" t="n"/>
     </row>
@@ -2388,12 +2388,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.3.1</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Drainage</t>
+          <t>Rental of an drainage pump ECd_49</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2405,7 +2405,7 @@
         <v>46129</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="G30" s="5" t="n"/>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>2.3.2</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Rental of an drainage pump ECd_49</t>
+          <t xml:space="preserve">Mobilization, installation and leasing of a wellpoint system including pumps ECd_50 </t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -2434,7 +2434,7 @@
         <v>46129</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>4600</v>
+        <v>70000</v>
       </c>
       <c r="G31" s="5" t="n"/>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>1.2.4</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobilization, installation and leasing of a wellpoint system including pumps ECd_50 </t>
+          <t xml:space="preserve">Electrical &amp; I/C detailed design </t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="E32" s="13" t="n">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>70000</v>
+        <v>1620000</v>
       </c>
       <c r="G32" s="5" t="n"/>
     </row>
@@ -2475,12 +2475,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical &amp; I/C detailed design </t>
+          <t>Delivery and installation of electrical equipment</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2492,9 +2492,13 @@
         <v>46134</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1620000</v>
-      </c>
-      <c r="G33" s="5" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Radosław Zdancewicz</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -2504,7 +2508,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>3.1.1</t>
+          <t>3.1.1.1</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -2521,7 +2525,7 @@
         <v>46134</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0</v>
+        <v>27750000</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -2537,12 +2541,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>3.1.1.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Delivery and installation of electrical equipment</t>
+          <t>Teletechnical installations</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2554,7 +2558,7 @@
         <v>46134</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>27750000</v>
+        <v>1750000</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
@@ -2570,12 +2574,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.4.1</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Teletechnical installations</t>
+          <t>Automation system and instrumentation, communication networks and control room devices</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2587,7 +2591,7 @@
         <v>46134</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>1750000</v>
+        <v>0</v>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
@@ -2603,7 +2607,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>3.4.1</t>
+          <t>3.4.1.1</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2620,7 +2624,7 @@
         <v>46134</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0</v>
+        <v>6280000</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
@@ -2636,12 +2640,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>3.4.1.1</t>
+          <t>6.4.1</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Automation system and instrumentation, communication networks and control room devices</t>
+          <t>Extension of the guarantee and warranty period to 48 months for electrical, technical and I&amp;C works</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2653,7 +2657,7 @@
         <v>46134</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>6280000</v>
+        <v>350000</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
@@ -2669,28 +2673,28 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>6.4.1</t>
+          <t>5.10.1</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Extension of the guarantee and warranty period to 48 months for electrical, technical and I&amp;C works</t>
+          <t>Steam turbine - gear box - generator. Including accessories: oil system, coolers, insulation, pipes and valves, control panel, protection panel, synchro system etc.</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E39" s="13" t="n">
-        <v>46134</v>
+        <v>46137</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Radosław Zdancewicz</t>
+          <t>Magdalena Białorucka / Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -2702,12 +2706,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>5.10.1</t>
+          <t>5.8.1</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Steam turbine - gear box - generator. Including accessories: oil system, coolers, insulation, pipes and valves, control panel, protection panel, synchro system etc.</t>
+          <t>Chain conveyor under grate + Bottom ash extractor + Vibrating table / bulk screen</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2719,11 +2723,11 @@
         <v>46137</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0</v>
+        <v>1462000</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka / Stanisław Rucki</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -2735,30 +2739,26 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>5.8.1</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Chain conveyor under grate + Bottom ash extractor + Vibrating table / bulk screen</t>
+          <t>Insulation – supply – Hydrostop ECd_51</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E41" s="13" t="n">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1462000</v>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
+        <v>31352</v>
+      </c>
+      <c r="G41" s="5" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
@@ -2768,12 +2768,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>2.4.2</t>
+          <t>2.4.3</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Insulation – supply – Hydrostop ECd_51</t>
+          <t>Insulation – supply – foil, compound ECd_14</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -2785,7 +2785,7 @@
         <v>46142</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>31352</v>
+        <v>27600</v>
       </c>
       <c r="G42" s="5" t="n"/>
     </row>
@@ -2797,12 +2797,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2.4.3</t>
+          <t>8.1.1.1</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Insulation – supply – foil, compound ECd_14</t>
+          <t>Purchase of temporary stairs ECd_48</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2814,7 +2814,7 @@
         <v>46142</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>27600</v>
+        <v>17530</v>
       </c>
       <c r="G43" s="5" t="n"/>
     </row>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>8.1.1.1</t>
+          <t>8.1.1.2</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Purchase of temporary stairs ECd_48</t>
+          <t>Meals ECd_53</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2843,7 +2843,7 @@
         <v>46142</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>17530</v>
+        <v>5711</v>
       </c>
       <c r="G44" s="5" t="n"/>
     </row>
@@ -2855,12 +2855,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>8.1.1.2</t>
+          <t>8.7.1.8</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Meals ECd_53</t>
+          <t>Installation of road markings and traffic signs ECd_52</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2872,38 +2872,42 @@
         <v>46142</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5711</v>
+        <v>920</v>
       </c>
       <c r="G45" s="5" t="n"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.8</t>
+          <t>5.13.7</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Installation of road markings and traffic signs ECd_52</t>
+          <t>Demi water system including storage tank 100m3 and piping</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E46" s="13" t="n">
-        <v>46142</v>
+        <v>46169</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>920</v>
-      </c>
-      <c r="G46" s="5" t="n"/>
+        <v>3010000</v>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -2913,12 +2917,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>5.13.7</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Demi water system including storage tank 100m3 and piping</t>
+          <t>Brick walls</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2927,16 +2931,12 @@
         </is>
       </c>
       <c r="E47" s="13" t="n">
-        <v>46169</v>
+        <v>46173</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>3010000</v>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>687451.25</v>
+      </c>
+      <c r="G47" s="5" t="n"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>5.2.2</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Brick walls</t>
+          <t>Trapdoors for grab maintenance</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2963,7 +2963,7 @@
         <v>46173</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>687451.25</v>
+        <v>81600</v>
       </c>
       <c r="G48" s="5" t="n"/>
     </row>
@@ -2975,24 +2975,24 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>5.2.2</t>
+          <t>1.2.6.1</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Trapdoors for grab maintenance</t>
+          <t>Ducts design</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E49" s="13" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>81600</v>
+        <v>0</v>
       </c>
       <c r="G49" s="5" t="n"/>
     </row>
@@ -3004,24 +3004,24 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>1.2.6.1</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Ducts design</t>
+          <t xml:space="preserve">Explosion hazard assessment </t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E50" s="13" t="n">
         <v>46174</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="G50" s="5" t="n"/>
     </row>
@@ -3033,26 +3033,30 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>5.10.4</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explosion hazard assessment </t>
+          <t>Feed water tank and Deaerator</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>negotiation</t>
         </is>
       </c>
       <c r="E51" s="13" t="n">
         <v>46174</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>120000</v>
-      </c>
-      <c r="G51" s="5" t="n"/>
+        <v>1000000</v>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -3062,28 +3066,28 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>5.10.4</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Feed water tank and Deaerator</t>
+          <t>Bottom ash / slag valorization</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>negotiation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E52" s="13" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>1000000</v>
+        <v>8271000</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -3095,12 +3099,12 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.8.2</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Bottom ash / slag valorization</t>
+          <t>Belt conveyors</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3109,14 +3113,14 @@
         </is>
       </c>
       <c r="E53" s="13" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>8271000</v>
+        <v>2347800</v>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -3128,28 +3132,28 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>5.8.2</t>
+          <t>5.10.3</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Belt conveyors</t>
+          <t>Air cooled condenser</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E54" s="13" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>2347800</v>
+        <v>9000000</v>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3165,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>5.10.3</t>
+          <t>2.5.2.3</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Air cooled condenser</t>
+          <t>Supply of reinforcing steel</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3175,14 +3179,14 @@
         </is>
       </c>
       <c r="E55" s="13" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>9000000</v>
+        <v>386500</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Agnieszka Zając</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3198,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.3</t>
+          <t>5.13.2</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Supply of reinforcing steel</t>
+          <t>Auxiliary fuel tank (light oil/diesel oil)</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -3208,14 +3212,14 @@
         </is>
       </c>
       <c r="E56" s="13" t="n">
-        <v>46181</v>
+        <v>46189</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>386500</v>
+        <v>200000</v>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -3227,28 +3231,28 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>5.13.2</t>
+          <t>2.8.1</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary fuel tank (light oil/diesel oil)</t>
+          <t>Parapet</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E57" s="13" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>200000</v>
+        <v>82476</v>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Joanna Sawicka</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3264,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>2.8.1</t>
+          <t>2.8.10</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Parapet</t>
+          <t>Soffit lining</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -3277,7 +3281,7 @@
         <v>46190</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>82476</v>
+        <v>308662.24</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
@@ -3293,12 +3297,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>2.8.10</t>
+          <t>2.8.11</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Soffit lining</t>
+          <t>Scaffolding</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -3310,7 +3314,7 @@
         <v>46190</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>308662.24</v>
+        <v>77076</v>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
@@ -3326,12 +3330,12 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>2.8.11</t>
+          <t>2.8.12</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Scaffolding</t>
+          <t>Safety system</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -3343,7 +3347,7 @@
         <v>46190</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>77076</v>
+        <v>150018.35</v>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
@@ -3359,12 +3363,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>2.8.12</t>
+          <t>2.8.13</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Safety system</t>
+          <t>Shutters</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -3376,7 +3380,7 @@
         <v>46190</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>150018.35</v>
+        <v>107600.56</v>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
@@ -3392,12 +3396,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>2.8.13</t>
+          <t>2.8.2</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Shutters</t>
+          <t>Steel-aluminum canopy</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -3409,7 +3413,7 @@
         <v>46190</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>107600.56</v>
+        <v>120922.87</v>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
@@ -3425,12 +3429,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>2.8.2</t>
+          <t>2.8.3</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Steel-aluminum canopy</t>
+          <t>Aluminum-glass facade</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -3442,7 +3446,7 @@
         <v>46190</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>120922.87</v>
+        <v>296487.48</v>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
@@ -3458,12 +3462,12 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>2.8.3</t>
+          <t>2.8.4</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Aluminum-glass facade</t>
+          <t xml:space="preserve">ETICS </t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3475,7 +3479,7 @@
         <v>46190</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>296487.48</v>
+        <v>122038.26</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
@@ -3491,12 +3495,12 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>2.8.4</t>
+          <t>2.8.5</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETICS </t>
+          <t>Flashings</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -3508,7 +3512,7 @@
         <v>46190</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>122038.26</v>
+        <v>366598.98</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
@@ -3524,12 +3528,12 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>2.8.5</t>
+          <t>2.8.6</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Flashings</t>
+          <t>Sheet metal cladding</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -3541,7 +3545,7 @@
         <v>46190</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>366598.98</v>
+        <v>1172886.87</v>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
@@ -3557,24 +3561,24 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2.8.6</t>
+          <t>2.8.7</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Sheet metal cladding</t>
+          <t>Sandwich panel cladding</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E67" s="13" t="n">
         <v>46190</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>1172886.87</v>
+        <v>5792279.88</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
@@ -3590,24 +3594,24 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>2.8.7</t>
+          <t>2.8.8</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Sandwich panel cladding</t>
+          <t>Fiber cement panel cladding</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E68" s="13" t="n">
         <v>46190</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>5792279.88</v>
+        <v>241170.5</v>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
@@ -3623,12 +3627,12 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>2.8.8</t>
+          <t>2.8.9</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Fiber cement panel cladding</t>
+          <t>Substructures</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -3640,7 +3644,7 @@
         <v>46190</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>241170.5</v>
+        <v>419580</v>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
@@ -3656,12 +3660,12 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>2.8.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Substructures</t>
+          <t>Notification Bodies</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -3670,16 +3674,12 @@
         </is>
       </c>
       <c r="E70" s="13" t="n">
-        <v>46190</v>
+        <v>46201</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>419580</v>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>Joanna Sawicka</t>
-        </is>
-      </c>
+        <v>350000</v>
+      </c>
+      <c r="G70" s="5" t="n"/>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
@@ -3689,24 +3689,24 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.5.1.4</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Notification Bodies</t>
+          <t>Execution of pre-wall insulation</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>negotiation</t>
         </is>
       </c>
       <c r="E71" s="13" t="n">
         <v>46201</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>350000</v>
+        <v>500000</v>
       </c>
       <c r="G71" s="5" t="n"/>
     </row>
@@ -3718,26 +3718,30 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>2.5.1.4</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Execution of pre-wall insulation</t>
+          <t>Fly ash extraction system for the boiler and conveyors</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>negotiation</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E72" s="13" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G72" s="5" t="n"/>
+        <v>4260000</v>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Roger Gołombek</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -3747,30 +3751,26 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>1.2.6.2</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Fly ash extraction system for the boiler and conveyors</t>
+          <t>Piping design</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E73" s="13" t="n">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>4260000</v>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G73" s="5" t="n"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>1.2.6.2</t>
+          <t>5.7.1</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Piping design</t>
+          <t>SNCR DeNOx system including silo, pumps</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3797,9 +3797,13 @@
         <v>46205</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="5" t="n"/>
+        <v>1090000</v>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
@@ -3809,12 +3813,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>5.7.1</t>
+          <t>4.3.6</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>SNCR DeNOx system including silo, pumps</t>
+          <t>Emergency showers and eye washers</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -3823,14 +3827,14 @@
         </is>
       </c>
       <c r="E75" s="13" t="n">
-        <v>46205</v>
+        <v>46212</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>1090000</v>
+        <v>10000</v>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Magdalena Przeździak</t>
         </is>
       </c>
     </row>
@@ -3842,12 +3846,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>4.3.6</t>
+          <t>5.10.11</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Emergency showers and eye washers</t>
+          <t>Heat exchangers 2 pcs., LP pre-heater, external economizer</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -3856,14 +3860,14 @@
         </is>
       </c>
       <c r="E76" s="13" t="n">
-        <v>46212</v>
+        <v>46215</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>10000</v>
+        <v>3242866</v>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Przeździak</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -3875,12 +3879,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>5.10.11</t>
+          <t>1.2.3</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Heat exchangers 2 pcs., LP pre-heater, external economizer</t>
+          <t>Detailed design: fire-fighting system</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -3889,16 +3893,12 @@
         </is>
       </c>
       <c r="E77" s="13" t="n">
-        <v>46215</v>
+        <v>46218</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>3242866</v>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
+        <v>260000</v>
+      </c>
+      <c r="G77" s="5" t="n"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>1.2.3</t>
+          <t>4.3.1</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Detailed design: fire-fighting system</t>
+          <t>Boiler room roof ventilators and wall shutters</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -3925,9 +3925,13 @@
         <v>46218</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>260000</v>
-      </c>
-      <c r="G78" s="5" t="n"/>
+        <v>1500000</v>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Przeździak</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
@@ -3937,12 +3941,12 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>4.3.1</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Boiler room roof ventilators and wall shutters</t>
+          <t>HVAC for the technological buildings</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -3954,7 +3958,7 @@
         <v>46218</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>1500000</v>
+        <v>3107033</v>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
@@ -3970,12 +3974,12 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>4.3.2</t>
+          <t>4.3.3</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>HVAC for the technological buildings</t>
+          <t xml:space="preserve">HVAC for the other buildings </t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -3987,7 +3991,7 @@
         <v>46218</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>3107033</v>
+        <v>1548256</v>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
@@ -4003,12 +4007,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>4.3.3</t>
+          <t>3.4.3</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HVAC for the other buildings </t>
+          <t>Emission monitoring system (CEMS)</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -4017,14 +4021,14 @@
         </is>
       </c>
       <c r="E81" s="13" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1548256</v>
+        <v>1960000</v>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Przeździak</t>
+          <t>Radosław Zdancewicz</t>
         </is>
       </c>
     </row>
@@ -4036,28 +4040,28 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>3.4.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Emission monitoring system (CEMS)</t>
+          <t>Deodorization system</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E82" s="13" t="n">
         <v>46219</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>1960000</v>
+        <v>1009700</v>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Radosław Zdancewicz</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -4069,30 +4073,26 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>5.13.3</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Deodorization system</t>
+          <t>Light oil unloading installation with TDT documentation approval</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E83" s="13" t="n">
-        <v>46219</v>
+        <v>46222</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>1009700</v>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
+        <v>200000</v>
+      </c>
+      <c r="G83" s="5" t="n"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
@@ -4102,26 +4102,30 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>5.13.3</t>
+          <t>5.10.12</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Light oil unloading installation with TDT documentation approval</t>
+          <t>Stabilising pumps 2 x 100%, network pumps 3 x 50%, condensate pumps 2 x 100%, feed water pumps 3 pcs., cooling pumps</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E84" s="13" t="n">
-        <v>46222</v>
+        <v>46231</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G84" s="5" t="n"/>
+        <v>5517325</v>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>Stanisław Rucki</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
@@ -4131,24 +4135,24 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>5.10.12</t>
+          <t>5.13.4</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Stabilising pumps 2 x 100%, network pumps 3 x 50%, condensate pumps 2 x 100%, feed water pumps 3 pcs., cooling pumps</t>
+          <t>Auxiliary fuel pumps (light oil/diesel oil), demi water pumps, other water pumps</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E85" s="13" t="n">
         <v>46231</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>5517325</v>
+        <v>3337500</v>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
@@ -4164,12 +4168,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>5.13.4</t>
+          <t>2.11.1</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary fuel pumps (light oil/diesel oil), demi water pumps, other water pumps</t>
+          <t>Painting</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -4178,14 +4182,14 @@
         </is>
       </c>
       <c r="E86" s="13" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>3337500</v>
+        <v>669442.8</v>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -4197,12 +4201,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>2.11.1</t>
+          <t>2.11.10</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Painting</t>
+          <t>Plasterboard wall, sandwich panel wall</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -4214,13 +4218,9 @@
         <v>46234</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>669442.8</v>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>39026.75</v>
+      </c>
+      <c r="G87" s="5" t="n"/>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>2.11.10</t>
+          <t>2.11.11</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Plasterboard wall, sandwich panel wall</t>
+          <t>Glass wall</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -4247,7 +4247,7 @@
         <v>46234</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>39026.75</v>
+        <v>75045.3</v>
       </c>
       <c r="G88" s="5" t="n"/>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>2.11.11</t>
+          <t>2.11.12</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Glass wall</t>
+          <t>Plastering</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -4276,9 +4276,13 @@
         <v>46234</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>75045.3</v>
-      </c>
-      <c r="G89" s="5" t="n"/>
+        <v>1241084.64</v>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
@@ -4288,12 +4292,12 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>2.11.12</t>
+          <t>2.11.13</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Plastering</t>
+          <t>Carpet / polyamide</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -4305,13 +4309,9 @@
         <v>46234</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>1241084.64</v>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>87497.52</v>
+      </c>
+      <c r="G90" s="5" t="n"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>2.11.13</t>
+          <t>2.11.14</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Carpet / polyamide</t>
+          <t>Wall and column protection up to 2.5 m + hydrophobic protection</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -4338,7 +4338,7 @@
         <v>46234</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>87497.52</v>
+        <v>186490.48</v>
       </c>
       <c r="G91" s="5" t="n"/>
     </row>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>2.11.14</t>
+          <t>2.11.2</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Wall and column protection up to 2.5 m + hydrophobic protection</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -4367,9 +4367,13 @@
         <v>46234</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>186490.48</v>
-      </c>
-      <c r="G92" s="5" t="n"/>
+        <v>631074</v>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
@@ -4379,12 +4383,12 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>2.11.2</t>
+          <t>2.11.3</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Tiles</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -4396,7 +4400,7 @@
         <v>46234</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>631074</v>
+        <v>498448.22</v>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
@@ -4412,12 +4416,12 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>2.11.3</t>
+          <t>2.11.4</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Tiles</t>
+          <t>Raised floor</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -4429,7 +4433,7 @@
         <v>46234</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>498448.22</v>
+        <v>621907.75</v>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
@@ -4445,30 +4449,26 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>2.11.4</t>
+          <t>2.11.5</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Raised floor</t>
+          <t>Concrete floor + screed</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E95" s="13" t="n">
         <v>46234</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>621907.75</v>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>610629.23</v>
+      </c>
+      <c r="G95" s="5" t="n"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
@@ -4478,24 +4478,24 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>2.11.5</t>
+          <t>2.11.5.4</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Concrete floor + screed</t>
+          <t>Concrete flooring and screed with insulation</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E96" s="13" t="n">
         <v>46234</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>610629.23</v>
+        <v>0</v>
       </c>
       <c r="G96" s="5" t="n"/>
     </row>
@@ -4507,12 +4507,12 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>2.11.5.4</t>
+          <t>2.11.6</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Concrete flooring and screed with insulation</t>
+          <t>Microcement floor</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -4524,7 +4524,7 @@
         <v>46234</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>0</v>
+        <v>133705.44</v>
       </c>
       <c r="G97" s="5" t="n"/>
     </row>
@@ -4536,12 +4536,12 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>2.11.6</t>
+          <t>2.11.7</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Microcement floor</t>
+          <t>Resin floor</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -4553,9 +4553,13 @@
         <v>46234</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>133705.44</v>
-      </c>
-      <c r="G98" s="5" t="n"/>
+        <v>655174.75</v>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
@@ -4565,12 +4569,12 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>2.11.7</t>
+          <t>2.11.8</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Resin floor</t>
+          <t>Suspended ceilings</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -4582,13 +4586,9 @@
         <v>46234</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>655174.75</v>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>220670.05</v>
+      </c>
+      <c r="G99" s="5" t="n"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
@@ -4598,12 +4598,12 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>2.11.8</t>
+          <t>2.11.9</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Suspended ceilings</t>
+          <t>Segmented sliding wall</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -4615,7 +4615,7 @@
         <v>46234</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>220670.05</v>
+        <v>65014.1</v>
       </c>
       <c r="G100" s="5" t="n"/>
     </row>
@@ -4627,26 +4627,30 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>2.11.9</t>
+          <t>2.12.1</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Segmented sliding wall</t>
+          <t>Passenger and good elevator</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E101" s="13" t="n">
         <v>46234</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>65014.1</v>
-      </c>
-      <c r="G101" s="5" t="n"/>
+        <v>415350</v>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>Izabela Malarecka</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
@@ -4656,12 +4660,12 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>2.12.1</t>
+          <t>2.12.2</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Passenger and good elevator</t>
+          <t>Passenger elevator</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -4673,7 +4677,7 @@
         <v>46234</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>415350</v>
+        <v>98643.60000000001</v>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
@@ -4689,28 +4693,28 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>2.12.2</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Passenger elevator</t>
+          <t>Weigh bridge</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E103" s="13" t="n">
         <v>46234</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>98643.60000000001</v>
+        <v>551900</v>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>Izabela Malarecka</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -4722,12 +4726,12 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>5.14.2</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Weigh bridge</t>
+          <t>Mechanical installation of technological equipment</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -4739,7 +4743,7 @@
         <v>46234</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>551900</v>
+        <v>1500000</v>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
@@ -4755,12 +4759,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>5.14.2</t>
+          <t>5.4.6</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Mechanical installation of technological equipment</t>
+          <t>Compensator between boiler and ECO</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -4772,13 +4776,9 @@
         <v>46234</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
+        <v>129000</v>
+      </c>
+      <c r="G105" s="5" t="n"/>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>5.4.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Compensator between boiler and ECO</t>
+          <t>Refractory</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -4805,9 +4805,13 @@
         <v>46234</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>129000</v>
-      </c>
-      <c r="G106" s="5" t="n"/>
+        <v>3993000</v>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
@@ -4817,24 +4821,24 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.2.2</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Refractory</t>
+          <t>Firefighting water tank</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E107" s="13" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>3993000</v>
+        <v>275700</v>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
@@ -4850,28 +4854,28 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>4.2.2</t>
+          <t>5.13.1</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water tank</t>
+          <t>Compressors 2 x 50% + 1 x 50%</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E108" s="13" t="n">
         <v>46235</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>275700</v>
+        <v>1500000</v>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -4883,12 +4887,12 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>5.13.1</t>
+          <t>4.3.5</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Compressors 2 x 50% + 1 x 50%</t>
+          <t>Sanitary water, connection to source, storage, pumping, underground and external distribution</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -4897,14 +4901,14 @@
         </is>
       </c>
       <c r="E109" s="13" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>1500000</v>
+        <v>637613</v>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Magdalena Przeździak</t>
         </is>
       </c>
     </row>
@@ -4916,12 +4920,12 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>4.3.5</t>
+          <t>4.3.7</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Sanitary water, connection to source, storage, pumping, underground and external distribution</t>
+          <t>Sanitary waste water collection, treatment and connection to discharge point</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -4933,7 +4937,7 @@
         <v>46236</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>637613</v>
+        <v>624272</v>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
@@ -4949,12 +4953,12 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>4.3.7</t>
+          <t>4.3.8</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Sanitary waste water collection, treatment and connection to discharge point</t>
+          <t>Waste water collection and connection to discharge point</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -4966,7 +4970,7 @@
         <v>46236</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>624272</v>
+        <v>200969</v>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
@@ -4982,12 +4986,12 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>4.3.8</t>
+          <t>4.3.9</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Waste water collection and connection to discharge point</t>
+          <t>Rain water and snowmelt collection, treatment and connection to discharge point</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -4999,7 +5003,7 @@
         <v>46236</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>200969</v>
+        <v>3359643</v>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
@@ -5015,12 +5019,12 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>4.3.9</t>
+          <t>5.13.9</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Rain water and snowmelt collection, treatment and connection to discharge point</t>
+          <t>Grate cooling system</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -5032,11 +5036,11 @@
         <v>46236</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>3359643</v>
+        <v>731000</v>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Przeździak</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5052,12 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>5.13.9</t>
+          <t>2.6.4</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Grate cooling system</t>
+          <t>Steel structure of the staircase in the B1.4 facility (change from the reinforced concrete structure in relation to the acquisition stage)</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -5062,14 +5066,14 @@
         </is>
       </c>
       <c r="E114" s="13" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>731000</v>
+        <v>470146.23</v>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Robert Klimczak</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5085,12 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>2.6.4</t>
+          <t>3.4.2</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Steel structure of the staircase in the B1.4 facility (change from the reinforced concrete structure in relation to the acquisition stage)</t>
+          <t>DCS System</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -5095,14 +5099,14 @@
         </is>
       </c>
       <c r="E115" s="13" t="n">
-        <v>46237</v>
+        <v>46250</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>470146.23</v>
+        <v>2752000</v>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>Robert Klimczak</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5118,12 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>3.4.2</t>
+          <t>5.7.4</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>DCS System</t>
+          <t>Fly ash silos</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -5131,7 +5135,7 @@
         <v>46250</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>2752000</v>
+        <v>2000000</v>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
@@ -5147,12 +5151,12 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>5.7.4</t>
+          <t>5.10.7</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Fly ash silos</t>
+          <t>Main cooler</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -5161,7 +5165,7 @@
         </is>
       </c>
       <c r="E117" s="13" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>2000000</v>
@@ -5180,12 +5184,12 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>5.10.7</t>
+          <t>5.10.8</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Main cooler</t>
+          <t>Cooler tank, condensate tank</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -5197,7 +5201,7 @@
         <v>46251</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
@@ -5213,12 +5217,12 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>5.10.8</t>
+          <t>5.13.11</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Cooler tank, condensate tank</t>
+          <t>waste water treatment</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -5230,7 +5234,7 @@
         <v>46251</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
@@ -5246,12 +5250,12 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>5.13.11</t>
+          <t>5.4.5</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>waste water treatment</t>
+          <t>Chemical dosing for the boiler</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
@@ -5263,11 +5267,11 @@
         <v>46251</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>800000</v>
+        <v>223600</v>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -5279,59 +5283,26 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>5.4.5</t>
+          <t>5.10.9</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Chemical dosing for the boiler</t>
+          <t>Water pressure stabilization system</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>negotiation</t>
         </is>
       </c>
       <c r="E121" s="13" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>223600</v>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>5.10.9</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>Water pressure stabilization system</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>negotiation</t>
-        </is>
-      </c>
-      <c r="E122" s="13" t="n">
-        <v>46252</v>
-      </c>
-      <c r="F122" s="6" t="n">
         <v>350000</v>
       </c>
-      <c r="G122" s="5" t="n"/>
+      <c r="G121" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8503,7 +8474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -12149,36 +12120,6 @@
       </c>
       <c r="G121" s="5">
         <f>'10_Source_Orders_3M'!G121</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="5">
-        <f>'10_Source_Orders_3M'!A122</f>
-        <v/>
-      </c>
-      <c r="B122" s="5">
-        <f>'10_Source_Orders_3M'!B122</f>
-        <v/>
-      </c>
-      <c r="C122" s="5">
-        <f>'10_Source_Orders_3M'!C122</f>
-        <v/>
-      </c>
-      <c r="D122" s="5">
-        <f>'10_Source_Orders_3M'!D122</f>
-        <v/>
-      </c>
-      <c r="E122" s="13">
-        <f>'10_Source_Orders_3M'!E122</f>
-        <v/>
-      </c>
-      <c r="F122" s="6">
-        <f>'10_Source_Orders_3M'!F122</f>
-        <v/>
-      </c>
-      <c r="G122" s="5">
-        <f>'10_Source_Orders_3M'!G122</f>
         <v/>
       </c>
     </row>

--- a/docs/reports/WTE_Dashboard_Report.xlsx
+++ b/docs/reports/WTE_Dashboard_Report.xlsx
@@ -828,7 +828,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generato: 2026-06-15 16:42</t>
+          <t>Generato: 2026-06-15 16:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/docs/reports/WTE_Dashboard_Report.xlsx
+++ b/docs/reports/WTE_Dashboard_Report.xlsx
@@ -828,7 +828,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generato: 2026-06-15 16:47</t>
+          <t>Generato: 2026-07-01 12:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="N6" s="4" t="n">
-        <v>501457853.03</v>
+        <v>501457853.02</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>40357633.06</v>
+        <v>40036817.27</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="N14" s="4" t="n">
-        <v>63171978.76</v>
+        <v>63492794.56</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1288,7 +1288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>300304565.67</v>
+        <v>268330424.03</v>
       </c>
       <c r="D9" s="11">
         <f>IFERROR(C9/SUM($C$9:$C$11),0)</f>
@@ -1406,14 +1406,14 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>In negoziazione</t>
+          <t>Da ordinare</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>81677402.31</v>
+        <v>233127428.99</v>
       </c>
       <c r="D10" s="11">
         <f>IFERROR(C10/SUM($C$9:$C$11),0)</f>
@@ -1421,27 +1421,6 @@
       </c>
       <c r="E10" s="11">
         <f>IFERROR(B10/SUM($B$9:$B$11),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Da ordinare</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>123361456</v>
-      </c>
-      <c r="D11" s="11">
-        <f>IFERROR(C11/SUM($C$9:$C$11),0)</f>
-        <v/>
-      </c>
-      <c r="E11" s="11">
-        <f>IFERROR(B11/SUM($B$9:$B$11),0)</f>
         <v/>
       </c>
     </row>
@@ -1459,7 +1438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1516,12 +1495,12 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.3.2</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Burners including fans</t>
+          <t>Primary and secondary air fan, Flue gas recirculation fan, ID Fan</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -1530,14 +1509,14 @@
         </is>
       </c>
       <c r="E2" s="13" t="n">
-        <v>46096</v>
+        <v>46112</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1569500</v>
+        <v>2360000</v>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -1549,26 +1528,30 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>8.3.1.2</t>
+          <t>5.3.3</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Generator rental ECd_44</t>
+          <t>Primary &amp; secondary air heat exchanger</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E3" s="13" t="n">
-        <v>46096</v>
+        <v>46112</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>23904</v>
-      </c>
-      <c r="G3" s="5" t="n"/>
+        <v>2400000</v>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Stanisław Rucki</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -1578,12 +1561,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.6</t>
+          <t>2.14.2.1</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Purchase of road signs ECd_42</t>
+          <t>External road- sub-base construction</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1592,12 +1575,16 @@
         </is>
       </c>
       <c r="E4" s="13" t="n">
-        <v>46096</v>
+        <v>46122</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G4" s="5" t="n"/>
+        <v>250640</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Agnieszka Zając</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -1607,12 +1594,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.7</t>
+          <t>8.3.1.1</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Purchase of rubble for the construction of storage yards and work platforms ECd_45</t>
+          <t>Electricity Costs</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1621,10 +1608,10 @@
         </is>
       </c>
       <c r="E5" s="13" t="n">
-        <v>46096</v>
+        <v>46122</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>83200</v>
+        <v>100000</v>
       </c>
       <c r="G5" s="5" t="n"/>
     </row>
@@ -1636,12 +1623,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>8.7.1.4</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>HAZOP study and SIL analysis</t>
+          <t>Construction of aggregate squares</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1650,12 +1637,16 @@
         </is>
       </c>
       <c r="E6" s="13" t="n">
-        <v>46102</v>
+        <v>46122</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>214974</v>
-      </c>
-      <c r="G6" s="5" t="n"/>
+        <v>124700</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Agnieszka Zając</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -1665,12 +1656,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2.11.5.3</t>
+          <t>8.8.4</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Concrete slab installation on the ground</t>
+          <t>Removing collisions related to site preparation and construction</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1679,16 +1670,12 @@
         </is>
       </c>
       <c r="E7" s="13" t="n">
-        <v>46106</v>
+        <v>46122</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1735392.78</v>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Agnieszka Zając</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -1698,12 +1685,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2.14.2.2</t>
+          <t>8.8.4.1</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">External Road </t>
+          <t>Removal of existing reinforced concrete foundations in the vicinity of Building B2</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1712,16 +1699,12 @@
         </is>
       </c>
       <c r="E8" s="13" t="n">
-        <v>46106</v>
+        <v>46122</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>134400</v>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Agnieszka Zając</t>
-        </is>
-      </c>
+        <v>50000</v>
+      </c>
+      <c r="G8" s="5" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1731,12 +1714,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2.4.1</t>
+          <t>5.10.2</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>reinforced concrete works</t>
+          <t>Auxiliary crane and hoists for the maintenance of the steam turbine</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1745,14 +1728,14 @@
         </is>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46106</v>
+        <v>46125</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>733045.25</v>
+        <v>499000</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1747,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2.5.1.3</t>
+          <t>5.2.1</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Construction of reinforced concrete foundations and underground structures</t>
+          <t>Overhead crane, grab and operator seat + Spare Grab</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1778,14 +1761,14 @@
         </is>
       </c>
       <c r="E10" s="13" t="n">
-        <v>46106</v>
+        <v>46125</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>5276959.37</v>
+        <v>8701000</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -1797,12 +1780,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.1</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the B1 building - delivery and assembly of prefabricated elements</t>
+          <t>Stack</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1811,14 +1794,14 @@
         </is>
       </c>
       <c r="E11" s="13" t="n">
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>16616880</v>
+        <v>1498200</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Jan Szczubiał</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -1830,12 +1813,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.2.3</t>
+          <t>5.4.1.1</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the B3 building - delivery and assembly of prefabricated elements</t>
+          <t>Boiler - pressure parts</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1844,14 +1827,14 @@
         </is>
       </c>
       <c r="E12" s="13" t="n">
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>2115950</v>
+        <v>45990000</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Jan Szczubiał</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1846,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.2.4</t>
+          <t>8.3.5</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Reinforced concrete structure of the above-ground part of the other buildings</t>
+          <t>Construction Waste Removal  ECd_38</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1877,16 +1860,12 @@
         </is>
       </c>
       <c r="E13" s="13" t="n">
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>708072.75</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Jan Szczubiał</t>
-        </is>
-      </c>
+        <v>290720</v>
+      </c>
+      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1896,12 +1875,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2.6.2.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Precast reinforced concrete structure of facility B3 (change from steel structure compared to the acquisition stage)</t>
+          <t>Drainage</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1910,16 +1889,12 @@
         </is>
       </c>
       <c r="E14" s="13" t="n">
-        <v>46106</v>
+        <v>46129</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1004390</v>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Robert Klimczak</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1929,12 +1904,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2.6.3.1</t>
+          <t>2.3.1</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Structure, including platforms, walkways, ladders, roofing ECR 16</t>
+          <t>Rental of an drainage pump ECd_49</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1943,16 +1918,12 @@
         </is>
       </c>
       <c r="E15" s="13" t="n">
-        <v>46106</v>
+        <v>46129</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>246780</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Robert Klimczak</t>
-        </is>
-      </c>
+        <v>4600</v>
+      </c>
+      <c r="G15" s="5" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1962,30 +1933,26 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>5.3.2</t>
+          <t>2.3.2</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Primary and secondary air fan, Flue gas recirculation fan, ID Fan</t>
+          <t xml:space="preserve">Mobilization, installation and leasing of a wellpoint system including pumps ECd_50 </t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E16" s="13" t="n">
-        <v>46112</v>
+        <v>46129</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>2360000</v>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>105000</v>
+      </c>
+      <c r="G16" s="5" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1995,30 +1962,26 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>5.3.3</t>
+          <t>1.2.4</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Primary &amp; secondary air heat exchanger</t>
+          <t xml:space="preserve">Electrical &amp; I/C detailed design </t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E17" s="13" t="n">
-        <v>46112</v>
+        <v>46134</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
+        <v>1620000</v>
+      </c>
+      <c r="G17" s="5" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -2028,12 +1991,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2.14.2.1</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Crushed aggregate</t>
+          <t>Delivery and installation of electrical equipment</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -2042,14 +2005,14 @@
         </is>
       </c>
       <c r="E18" s="13" t="n">
-        <v>46122</v>
+        <v>46134</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>250640</v>
+        <v>0</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Radosław Zdancewicz</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2024,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>8.3.1.1</t>
+          <t>3.1.1.1</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Electricity Costs</t>
+          <t>Delivery and installation of electrical equipment</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -2075,12 +2038,16 @@
         </is>
       </c>
       <c r="E19" s="13" t="n">
-        <v>46122</v>
+        <v>46134</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G19" s="5" t="n"/>
+        <v>27750000</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Radosław Zdancewicz</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -2090,12 +2057,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Construction of aggregate squares</t>
+          <t>Teletechnical installations</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2104,14 +2071,14 @@
         </is>
       </c>
       <c r="E20" s="13" t="n">
-        <v>46122</v>
+        <v>46134</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>124700</v>
+        <v>1750000</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Radosław Zdancewicz</t>
         </is>
       </c>
     </row>
@@ -2123,12 +2090,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>8.8.4</t>
+          <t>3.4.1</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Removing collisions related to site preparation and construction</t>
+          <t>Automation system and instrumentation, communication networks and control room devices</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -2137,12 +2104,16 @@
         </is>
       </c>
       <c r="E21" s="13" t="n">
-        <v>46122</v>
+        <v>46134</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="5" t="n"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Radosław Zdancewicz</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -2152,12 +2123,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>8.8.4.1</t>
+          <t>3.4.1.1</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Removal of existing reinforced concrete foundations in the vicinity of Building B2</t>
+          <t>Automation system and instrumentation, communication networks and control room devices</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2166,12 +2137,16 @@
         </is>
       </c>
       <c r="E22" s="13" t="n">
-        <v>46122</v>
+        <v>46134</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G22" s="5" t="n"/>
+        <v>6280000</v>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Radosław Zdancewicz</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -2181,12 +2156,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>5.10.2</t>
+          <t>6.4.1</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Auxiliary crane and hoists for the maintenance of the steam turbine</t>
+          <t>Extension of the guarantee and warranty period to 48 months for electrical, technical and I&amp;C works</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2195,14 +2170,14 @@
         </is>
       </c>
       <c r="E23" s="13" t="n">
-        <v>46125</v>
+        <v>46134</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>499000</v>
+        <v>350000</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Radosław Zdancewicz</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2189,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>5.2.1</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Overhead crane, grab and operator seat + Spare Grab</t>
+          <t>Insulation – supply – Hydrostop ECd_51</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -2228,16 +2203,12 @@
         </is>
       </c>
       <c r="E24" s="13" t="n">
-        <v>46125</v>
+        <v>46142</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>8701000</v>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>31352</v>
+      </c>
+      <c r="G24" s="5" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -2247,12 +2218,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>2.4.3</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Stack</t>
+          <t>Insulation – supply – foil, compound ECd_14</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2261,16 +2232,12 @@
         </is>
       </c>
       <c r="E25" s="13" t="n">
-        <v>46127</v>
+        <v>46142</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1498200</v>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>27600</v>
+      </c>
+      <c r="G25" s="5" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -2280,12 +2247,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>5.4.1.1</t>
+          <t>2.6.1.1</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>boiler</t>
+          <t>Detailed design: boiler support steel structure and equipment support structures</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -2294,14 +2261,14 @@
         </is>
       </c>
       <c r="E26" s="13" t="n">
-        <v>46127</v>
+        <v>46142</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>45990000</v>
+        <v>12745295</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Robert Klimczak</t>
         </is>
       </c>
     </row>
@@ -2313,12 +2280,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>8.3.5</t>
+          <t>2.6.5</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Construction Waste Removal  ECd_38</t>
+          <t>Gantry beams B1.2</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2327,12 +2294,16 @@
         </is>
       </c>
       <c r="E27" s="13" t="n">
-        <v>46127</v>
+        <v>46142</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>290720</v>
-      </c>
-      <c r="G27" s="5" t="n"/>
+        <v>380800</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Robert Klimczak</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -2342,12 +2313,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Drainage</t>
+          <t>Boiler - supporting structure including walkways</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2356,12 +2327,16 @@
         </is>
       </c>
       <c r="E28" s="13" t="n">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="5" t="n"/>
+        <v>6675500</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Roger Gołombek</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -2371,12 +2346,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>8.1.1.1</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Dehydration ECD 50</t>
+          <t>Purchase of temporary stairs ECd_48</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2385,10 +2360,10 @@
         </is>
       </c>
       <c r="E29" s="13" t="n">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>4600</v>
+        <v>17530</v>
       </c>
       <c r="G29" s="5" t="n"/>
     </row>
@@ -2400,12 +2375,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>8.1.1.2</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobilization, installation and leasing of a wellpoint system including pumps ECd_50 </t>
+          <t>Meals ECd_53</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2414,10 +2389,10 @@
         </is>
       </c>
       <c r="E30" s="13" t="n">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>105000</v>
+        <v>5711</v>
       </c>
       <c r="G30" s="5" t="n"/>
     </row>
@@ -2429,12 +2404,12 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>8.7.1.8</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical &amp; I/C detailed design </t>
+          <t>Installation of road markings and traffic signs ECd_52</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -2443,10 +2418,10 @@
         </is>
       </c>
       <c r="E31" s="13" t="n">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1620000</v>
+        <v>920</v>
       </c>
       <c r="G31" s="5" t="n"/>
     </row>
@@ -2458,12 +2433,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>3.1.1</t>
+          <t>1.2.6.1</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Delivery and installation of electrical equipment</t>
+          <t>Ducts design</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2472,16 +2447,12 @@
         </is>
       </c>
       <c r="E32" s="13" t="n">
-        <v>46134</v>
+        <v>46157</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>Radosław Zdancewicz</t>
-        </is>
-      </c>
+        <v>99000</v>
+      </c>
+      <c r="G32" s="5" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -2491,30 +2462,26 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>3.1.1.1</t>
+          <t>2.5.1.4</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Delivery and installation of electrical equipment</t>
+          <t>Execution of pre-wall insulation</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>PCT/approval</t>
         </is>
       </c>
       <c r="E33" s="13" t="n">
-        <v>46134</v>
+        <v>46157</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>27750000</v>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>Radosław Zdancewicz</t>
-        </is>
-      </c>
+        <v>331791.5</v>
+      </c>
+      <c r="G33" s="5" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -2524,12 +2491,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5.10.1</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Teletechnical installations</t>
+          <t>Steam turbine - gear box - generator. Including accessories: oil system, coolers, insulation, pipes and valves, control panel, protection panel, synchro system etc.</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2538,14 +2505,14 @@
         </is>
       </c>
       <c r="E34" s="13" t="n">
-        <v>46134</v>
+        <v>46173</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1750000</v>
+        <v>12979894</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Radosław Zdancewicz</t>
+          <t>Magdalena Białorucka / Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2524,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>3.4.1</t>
+          <t>5.10.4</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Automation system and instrumentation, communication networks and control room devices</t>
+          <t>Feed water tank and Deaerator</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2571,14 +2538,14 @@
         </is>
       </c>
       <c r="E35" s="13" t="n">
-        <v>46134</v>
+        <v>46173</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0</v>
+        <v>732740</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Radosław Zdancewicz</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -2590,12 +2557,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>3.4.1.1</t>
+          <t>5.10.9</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Automation system and instrumentation, communication networks and control room devices</t>
+          <t>Water pressure stabilization system</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2604,16 +2571,12 @@
         </is>
       </c>
       <c r="E36" s="13" t="n">
-        <v>46134</v>
+        <v>46173</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>6280000</v>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>Radosław Zdancewicz</t>
-        </is>
-      </c>
+        <v>350000</v>
+      </c>
+      <c r="G36" s="5" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -2623,12 +2586,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>6.4.1</t>
+          <t>5.8.1</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Extension of the guarantee and warranty period to 48 months for electrical, technical and I&amp;C works</t>
+          <t>Chain conveyor under grate + Bottom ash extractor + Vibrating table / bulk screen</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2637,378 +2600,390 @@
         </is>
       </c>
       <c r="E37" s="13" t="n">
-        <v>46134</v>
+        <v>46173</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>350000</v>
+        <v>1462000</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Radosław Zdancewicz</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>2.4.2</t>
+          <t>5.13.11</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Waterproofing</t>
+          <t>Waste Water Treatment Plant</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E38" s="13" t="n">
-        <v>46142</v>
+        <v>46213</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>31352</v>
-      </c>
-      <c r="G38" s="5" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2.4.3</t>
+          <t>4.3.1</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Foundation insulation materials</t>
+          <t>Boiler room roof ventilators and wall shutters</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E39" s="13" t="n">
-        <v>46142</v>
+        <v>46218</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>27600</v>
-      </c>
-      <c r="G39" s="5" t="n"/>
+        <v>1500000</v>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Przeździak</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>2.6.1.1</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Detailed design: boiler support steel structure and equipment support structures</t>
+          <t>HVAC for the technological buildings</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E40" s="13" t="n">
-        <v>46142</v>
+        <v>46218</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>12745295</v>
+        <v>3107033</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Robert Klimczak</t>
+          <t>Magdalena Przeździak</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2.6.5</t>
+          <t>4.3.3</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Gantry beams B1.2</t>
+          <t xml:space="preserve">HVAC for the other buildings </t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E41" s="13" t="n">
-        <v>46142</v>
+        <v>46218</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>380800</v>
+        <v>1548256</v>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Robert Klimczak</t>
+          <t>Magdalena Przeździak</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>2.11.1</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Structure, including platforms, walkways, ladders, roofing ECR 16</t>
+          <t>Painting</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E42" s="13" t="n">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>6675500</v>
+        <v>669442.8</v>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>8.1.1.1</t>
+          <t>2.11.10</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Purchase of temporary stairs ECd_48</t>
+          <t>Plasterboard wall, sandwich panel wall</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E43" s="13" t="n">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>17530</v>
+        <v>39026.75</v>
       </c>
       <c r="G43" s="5" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>8.1.1.2</t>
+          <t>2.11.11</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Meals ECd_53</t>
+          <t>Glass wall</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E44" s="13" t="n">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>5711</v>
+        <v>75045.3</v>
       </c>
       <c r="G44" s="5" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>8.7.1.8</t>
+          <t>2.11.12</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Installation of road markings and traffic signs ECd_52</t>
+          <t>Plastering</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E45" s="13" t="n">
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>920</v>
-      </c>
-      <c r="G45" s="5" t="n"/>
+        <v>1241084.64</v>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>1.2.6.1</t>
+          <t>2.11.13</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">air and flue gas ducts design </t>
+          <t>Carpet / polyamide</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E46" s="13" t="n">
-        <v>46157</v>
+        <v>46234</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>99000</v>
+        <v>87497.52</v>
       </c>
       <c r="G46" s="5" t="n"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2.5.1.4</t>
+          <t>2.11.14</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Execution of pre-wall insulation</t>
+          <t>Wall and column protection up to 2.5 m + hydrophobic protection</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>PCT/approval</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E47" s="13" t="n">
-        <v>46157</v>
+        <v>46234</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>331791.5</v>
+        <v>186490.48</v>
       </c>
       <c r="G47" s="5" t="n"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>5.10.1</t>
+          <t>2.11.2</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Steam turbine - gear box - generator. Including accessories: oil system, coolers, insulation, pipes and valves, control panel, protection panel, synchro system etc.</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E48" s="13" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>12979894</v>
+        <v>631074</v>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka / Stanisław Rucki</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>5.10.4</t>
+          <t>2.11.3</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Feed water tank and Deaerator</t>
+          <t>Tiles</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E49" s="13" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>732740</v>
+        <v>498448.22</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
@@ -3019,64 +2994,64 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>5.10.9</t>
+          <t>2.11.4</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Water pressure stabilization system</t>
+          <t>Raised floor</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E50" s="13" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>350000</v>
-      </c>
-      <c r="G50" s="5" t="n"/>
+        <v>621907.75</v>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Closed last 3 months</t>
+          <t>Next orders 3 months</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>5.8.1</t>
+          <t>2.11.5</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Chain conveyor under grate + Bottom ash extractor + Vibrating table / bulk screen</t>
+          <t>Concrete floor + screed</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E51" s="13" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1462000</v>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
+        <v>610629.23</v>
+      </c>
+      <c r="G51" s="5" t="n"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -3086,12 +3061,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.11.5.4</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Notification Bodies</t>
+          <t>Concrete flooring and screed with insulation</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -3100,10 +3075,10 @@
         </is>
       </c>
       <c r="E52" s="13" t="n">
-        <v>46201</v>
+        <v>46234</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="G52" s="5" t="n"/>
     </row>
@@ -3115,12 +3090,12 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>1.2.3</t>
+          <t>2.11.6</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Detailed design: fire-fighting system</t>
+          <t>Microcement floor</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3129,10 +3104,10 @@
         </is>
       </c>
       <c r="E53" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>260000</v>
+        <v>133705.44</v>
       </c>
       <c r="G53" s="5" t="n"/>
     </row>
@@ -3144,26 +3119,30 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>1.2.6.2</t>
+          <t>2.11.7</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Piping design</t>
+          <t>Resin floor</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E54" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="5" t="n"/>
+        <v>655174.75</v>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Magdalena Białorucka</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -3173,12 +3152,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.11.8</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Fencing</t>
+          <t>Suspended ceilings</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3187,10 +3166,10 @@
         </is>
       </c>
       <c r="E55" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0</v>
+        <v>220670.05</v>
       </c>
       <c r="G55" s="5" t="n"/>
     </row>
@@ -3202,12 +3181,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2.16.1</t>
+          <t>2.11.9</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Delivery of fences, gates and wickets</t>
+          <t>Segmented sliding wall</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -3216,16 +3195,12 @@
         </is>
       </c>
       <c r="E56" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>321394.76</v>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
+        <v>65014.1</v>
+      </c>
+      <c r="G56" s="5" t="n"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
@@ -3235,28 +3210,28 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2.16.2</t>
+          <t>2.12.1</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Installation of fences, gates and wickets</t>
+          <t>Passenger and good elevator</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>negotiation</t>
         </is>
       </c>
       <c r="E57" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>416382.29</v>
+        <v>415350</v>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Roger Gołombek</t>
+          <t>Izabela Malarecka</t>
         </is>
       </c>
     </row>
@@ -3268,28 +3243,28 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.3</t>
+          <t>2.12.2</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Supply of reinforcing steel</t>
+          <t>Passenger elevator</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>negotiation</t>
         </is>
       </c>
       <c r="E58" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>386500</v>
+        <v>98643.60000000001</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Izabela Malarecka</t>
         </is>
       </c>
     </row>
@@ -3301,28 +3276,28 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>2.5.2.4</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Supply of concrete mix with pumping service</t>
+          <t>Weigh bridge</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E59" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>718448.41</v>
+        <v>551900</v>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Agnieszka Zając</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -3334,12 +3309,12 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3.1.1.2</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Brick walls</t>
+          <t>Implementation of power supply and control for HVAC devices</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -3348,12 +3323,16 @@
         </is>
       </c>
       <c r="E60" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>687451.25</v>
-      </c>
-      <c r="G60" s="5" t="n"/>
+        <v>1700000</v>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Radosław Zdancewicz</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
@@ -3363,12 +3342,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>3.1.4</t>
+          <t>3.4.2</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Fire detection and alarm system ( electrical&amp;teletechnical part )</t>
+          <t>DCS System</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -3377,14 +3356,14 @@
         </is>
       </c>
       <c r="E61" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>980000</v>
+        <v>2752000</v>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Radosław Zdancewicz</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -3396,12 +3375,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>3.1.5</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Smoke extraction from waste bunker and tipping hall (electrical&amp;teletechnical part )</t>
+          <t>Radioactivity detector</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -3410,16 +3389,12 @@
         </is>
       </c>
       <c r="E62" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>175000</v>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>Radosław Zdancewicz</t>
-        </is>
-      </c>
+        <v>185000</v>
+      </c>
+      <c r="G62" s="5" t="n"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
@@ -3429,28 +3404,28 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>3.3.1</t>
+          <t>5.10.6</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Transformer 110 kV</t>
+          <t>Chemical dossing for thermal cycle and district heating</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>negotiation</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E63" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>2500000</v>
+        <v>550000</v>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Radosław Zdancewicz</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -3462,24 +3437,24 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>5.13.9</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Fire detection and alarm system</t>
+          <t>Grate cooling system</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E64" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>2211870</v>
+        <v>731000</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
@@ -3495,28 +3470,28 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>4.2.10</t>
+          <t>5.14.2</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Smoke extraction from waste bunker and tipping hall</t>
+          <t>Mechanical installation of technological equipment</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E65" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1178293</v>
+        <v>1500000</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -3528,12 +3503,12 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>4.2.2</t>
+          <t>5.14.3</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water tank</t>
+          <t>Devices support structures</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -3542,14 +3517,14 @@
         </is>
       </c>
       <c r="E66" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>275700</v>
+        <v>1000000</v>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Robert Klimczak</t>
         </is>
       </c>
     </row>
@@ -3561,28 +3536,28 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>4.2.3</t>
+          <t>5.3.4</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water pumping</t>
+          <t>Primary / secondary air ducts + Flue gas recirculation ducts + Auxiliary burners ducts + Supporting structures</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E67" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>715920</v>
+        <v>2502500</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Stanisław Rucki</t>
         </is>
       </c>
     </row>
@@ -3594,28 +3569,28 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>4.2.4</t>
+          <t>5.3.5</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water external distribution, hoses, sprinklers</t>
+          <t>Fire curtain for primary air opening</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E68" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>821016</v>
+        <v>100000</v>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Magdalena Przeździak</t>
         </is>
       </c>
     </row>
@@ -3627,30 +3602,26 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>4.2.5</t>
+          <t>5.3.8</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Installation of internal hydrants in buildings B1 and B2</t>
+          <t>Camera for furnace monitoring</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E69" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>240990</v>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>51600</v>
+      </c>
+      <c r="G69" s="5" t="n"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -3660,30 +3631,26 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>4.2.6</t>
+          <t>5.4.6</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Wireless radio controller system type WRC, gun control</t>
+          <t>Compensator between boiler and ECO</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E70" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>45500</v>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
+        <v>129000</v>
+      </c>
+      <c r="G70" s="5" t="n"/>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
@@ -3693,24 +3660,24 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>4.2.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Firefighting water external distribution, hoses, sprinklers</t>
+          <t>Refractory</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E71" s="13" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>542750</v>
+        <v>3993000</v>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
@@ -3726,24 +3693,24 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>4.2.8</t>
+          <t>5.10.10</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Dry bunker sprinkler system. Installation of water and foam cannons in the bunker hall, and assembly of the valve sub-control unit.</t>
+          <t>Water tank 100 m3</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E72" s="13" t="n">
-        <v>46203</v>
+        <v>46249</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>1925350</v>
+        <v>200000</v>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
@@ -3759,28 +3726,28 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>4.2.9</t>
+          <t>5.10.7</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Natural gas (if any) and ammonia detection system</t>
+          <t>Main cooler</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E73" s="13" t="n">
-        <v>46203</v>
+        <v>46249</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>285000</v>
+        <v>2000000</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -3792,30 +3759,22 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>4.3.4</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Service water storage, pumping, underground and external distribution + Sanitary facilities (toilets, showers, etc.)</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
+          <t>Doors, windows, gates and hatches</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="n"/>
       <c r="E74" s="13" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>1053444</v>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Przeździak</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G74" s="5" t="n"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
@@ -3825,12 +3784,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>4.3.5</t>
+          <t>2.9.1</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Sanitary water, connection to source, storage, pumping, underground and external distribution</t>
+          <t>Gates</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -3839,14 +3798,14 @@
         </is>
       </c>
       <c r="E75" s="13" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>637613</v>
+        <v>1169928.68</v>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Przeździak</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -3858,12 +3817,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>4.3.6</t>
+          <t>2.9.2</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Emergency showers and eye washers</t>
+          <t>Interior doors</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -3872,14 +3831,14 @@
         </is>
       </c>
       <c r="E76" s="13" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>10000</v>
+        <v>433041.85</v>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Przeździak</t>
+          <t>Izabela Malarecka</t>
         </is>
       </c>
     </row>
@@ -3891,12 +3850,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>4.3.7</t>
+          <t>2.9.3</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Sanitary waste water collection, treatment and connection to discharge point</t>
+          <t>Exterior doors</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -3905,14 +3864,14 @@
         </is>
       </c>
       <c r="E77" s="13" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>624272</v>
+        <v>164458.64</v>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Przeździak</t>
+          <t>Izabela Malarecka</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3883,12 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>4.3.8</t>
+          <t>2.9.4</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Waste water collection and connection to discharge point</t>
+          <t>Windows</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -3938,14 +3897,14 @@
         </is>
       </c>
       <c r="E78" s="13" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>200969</v>
+        <v>366535.63</v>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Przeździak</t>
+          <t>Izabela Malarecka</t>
         </is>
       </c>
     </row>
@@ -3957,12 +3916,12 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>4.3.9</t>
+          <t>2.9.5</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Rain water and snowmelt collection, treatment and connection to discharge point</t>
+          <t>Bunker windows</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -3971,14 +3930,14 @@
         </is>
       </c>
       <c r="E79" s="13" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>3359643</v>
+        <v>205428.18</v>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Przeździak</t>
+          <t>Izabela Malarecka</t>
         </is>
       </c>
     </row>
@@ -3990,28 +3949,28 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>5.10.11</t>
+          <t>2.9.6</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Heat exchangers 2 pcs., LP pre-heater, external economizer</t>
+          <t>Hatches</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E80" s="13" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>3242866</v>
+        <v>327190.64</v>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Stanisław Rucki</t>
+          <t>Magdalena Białorucka</t>
         </is>
       </c>
     </row>
@@ -4023,26 +3982,30 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>5.13.3</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Light oil unloading installation with TDT documentation approval</t>
+          <t>GPO/GPZ power supply</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E81" s="13" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G81" s="5" t="n"/>
+        <v>11010000</v>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Radosław Zdancewicz</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
@@ -4052,28 +4015,28 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>5.4.4</t>
+          <t>3.3.2</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Sampling system</t>
+          <t>GPO/GPZ power supply</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>enquiry</t>
         </is>
       </c>
       <c r="E82" s="13" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>1010500</v>
+        <v>0</v>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Radosław Zdancewicz</t>
         </is>
       </c>
     </row>
@@ -4085,12 +4048,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>5.4.5</t>
+          <t>3.4.1.2</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Chemical dosing for the boiler</t>
+          <t>Delivery of instrumentation for the boiler</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -4099,14 +4062,14 @@
         </is>
       </c>
       <c r="E83" s="13" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>223600</v>
+        <v>300000</v>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Radosław Zdancewicz</t>
         </is>
       </c>
     </row>
@@ -4118,12 +4081,12 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>5.7.1</t>
+          <t>5.10.13.2</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>SNCR DeNOx system including silo, pumps</t>
+          <t>Motorized valves</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -4132,14 +4095,14 @@
         </is>
       </c>
       <c r="E84" s="13" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>1090000</v>
+        <v>1000000</v>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -4151,28 +4114,28 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>5.13.11</t>
+          <t>5.10.13.3</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Waste Water Treatment Plant</t>
+          <t>Safety valves</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>enquiry</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="E85" s="13" t="n">
-        <v>46213</v>
+        <v>46265</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Białorucka</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4147,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>4.3.1</t>
+          <t>5.10.13.4</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Boiler room roof ventilators and wall shutters</t>
+          <t>ON/OFF valves</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -4198,14 +4161,14 @@
         </is>
       </c>
       <c r="E86" s="13" t="n">
-        <v>46218</v>
+        <v>46265</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>1500000</v>
+        <v>400000</v>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Przeździak</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -4217,12 +4180,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>4.3.2</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>HVAC for the technological buildings</t>
+          <t>Technical Consultant for certification and for complying with European Directives</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -4231,16 +4194,12 @@
         </is>
       </c>
       <c r="E87" s="13" t="n">
-        <v>46218</v>
+        <v>46295</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>3107033</v>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Przeździak</t>
-        </is>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="G87" s="5" t="n"/>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -4250,12 +4209,12 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>4.3.3</t>
+          <t>5.10.13.1</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HVAC for the other buildings </t>
+          <t>Manual valves</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -4264,14 +4223,14 @@
         </is>
       </c>
       <c r="E88" s="13" t="n">
-        <v>46218</v>
+        <v>46295</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>1548256</v>
+        <v>2200000</v>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Magdalena Przeździak</t>
+          <t>Roger Gołombek</t>
         </is>
       </c>
     </row>
@@ -4283,12 +4242,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>2.11.1</t>
+          <t>5.7.3</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Painting</t>
+          <t>Bag filters delivery</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -4297,1408 +4256,12 @@
         </is>
       </c>
       <c r="E89" s="13" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>669442.8</v>
+        <v>400000</v>
       </c>
       <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>2.11.10</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>Plasterboard wall, sandwich panel wall</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E90" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F90" s="6" t="n">
-        <v>39026.75</v>
-      </c>
-      <c r="G90" s="5" t="n"/>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>2.11.11</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>Glass wall</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E91" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F91" s="6" t="n">
-        <v>75045.3</v>
-      </c>
-      <c r="G91" s="5" t="n"/>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>2.11.12</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>Plastering</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E92" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F92" s="6" t="n">
-        <v>1241084.64</v>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>2.11.13</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>Carpet / polyamide</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E93" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F93" s="6" t="n">
-        <v>87497.52</v>
-      </c>
-      <c r="G93" s="5" t="n"/>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>2.11.14</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>Wall and column protection up to 2.5 m + hydrophobic protection</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E94" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F94" s="6" t="n">
-        <v>186490.48</v>
-      </c>
-      <c r="G94" s="5" t="n"/>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>2.11.2</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>Furniture</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E95" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F95" s="6" t="n">
-        <v>631074</v>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>2.11.3</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>Tiles</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E96" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F96" s="6" t="n">
-        <v>498448.22</v>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>2.11.4</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>Raised floor</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E97" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F97" s="6" t="n">
-        <v>621907.75</v>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>2.11.5</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>Concrete floor + screed</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>enquiry</t>
-        </is>
-      </c>
-      <c r="E98" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F98" s="6" t="n">
-        <v>610629.23</v>
-      </c>
-      <c r="G98" s="5" t="n"/>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>2.11.5.4</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>Concrete flooring and screed with insulation</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E99" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F99" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="5" t="n"/>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>2.11.6</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>Microcement floor</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E100" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F100" s="6" t="n">
-        <v>133705.44</v>
-      </c>
-      <c r="G100" s="5" t="n"/>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>2.11.7</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>Resin floor</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E101" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F101" s="6" t="n">
-        <v>655174.75</v>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>2.11.8</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>Suspended ceilings</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E102" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F102" s="6" t="n">
-        <v>220670.05</v>
-      </c>
-      <c r="G102" s="5" t="n"/>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>2.11.9</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>Segmented sliding wall</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E103" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F103" s="6" t="n">
-        <v>65014.1</v>
-      </c>
-      <c r="G103" s="5" t="n"/>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>2.12.1</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>Passenger and good elevator</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>negotiation</t>
-        </is>
-      </c>
-      <c r="E104" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F104" s="6" t="n">
-        <v>415350</v>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>Izabela Malarecka</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
-        <is>
-          <t>2.12.2</t>
-        </is>
-      </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>Passenger elevator</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
-        <is>
-          <t>negotiation</t>
-        </is>
-      </c>
-      <c r="E105" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F105" s="6" t="n">
-        <v>98643.60000000001</v>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>Izabela Malarecka</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>Weigh bridge</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E106" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F106" s="6" t="n">
-        <v>551900</v>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>3.1.1.2</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>Implementation of power supply and control for HVAC devices</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E107" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F107" s="6" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>Radosław Zdancewicz</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>3.4.2</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>DCS System</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E108" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F108" s="6" t="n">
-        <v>2752000</v>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>5.1.1</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>Radioactivity detector</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E109" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F109" s="6" t="n">
-        <v>185000</v>
-      </c>
-      <c r="G109" s="5" t="n"/>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>5.10.6</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>Chemical dossing for thermal cycle and district heating</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E110" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F110" s="6" t="n">
-        <v>550000</v>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>5.13.9</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>Grate cooling system</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E111" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F111" s="6" t="n">
-        <v>731000</v>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>5.14.2</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>Mechanical installation of technological equipment</t>
-        </is>
-      </c>
-      <c r="D112" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E112" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F112" s="6" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>5.14.3</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>Devices support structures</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>enquiry</t>
-        </is>
-      </c>
-      <c r="E113" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F113" s="6" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>Robert Klimczak</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>5.3.4</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>Primary / secondary air ducts + Flue gas recirculation ducts + Auxiliary burners ducts + Supporting structures</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E114" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F114" s="6" t="n">
-        <v>2502500</v>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>Stanisław Rucki</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>5.3.5</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>Fire curtain for primary air opening</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E115" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F115" s="6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Przeździak</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>5.3.8</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>Camera for furnace monitoring</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E116" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F116" s="6" t="n">
-        <v>51600</v>
-      </c>
-      <c r="G116" s="5" t="n"/>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>5.4.6</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>Compensator between boiler and ECO</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E117" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F117" s="6" t="n">
-        <v>129000</v>
-      </c>
-      <c r="G117" s="5" t="n"/>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="C118" s="5" t="inlineStr">
-        <is>
-          <t>Refractory</t>
-        </is>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E118" s="13" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F118" s="6" t="n">
-        <v>3993000</v>
-      </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>5.10.10</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>Water tank 100 m3</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E119" s="13" t="n">
-        <v>46249</v>
-      </c>
-      <c r="F119" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>5.10.7</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>Main cooler</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E120" s="13" t="n">
-        <v>46249</v>
-      </c>
-      <c r="F120" s="6" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>Doors, windows, gates and hatches</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="n"/>
-      <c r="E121" s="13" t="n">
-        <v>46265</v>
-      </c>
-      <c r="F121" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" s="5" t="n"/>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>2.9.1</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>Gates</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E122" s="13" t="n">
-        <v>46265</v>
-      </c>
-      <c r="F122" s="6" t="n">
-        <v>1169928.68</v>
-      </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>2.9.2</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>Interior doors</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E123" s="13" t="n">
-        <v>46265</v>
-      </c>
-      <c r="F123" s="6" t="n">
-        <v>433041.85</v>
-      </c>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>Izabela Malarecka</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>2.9.3</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>Exterior doors</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E124" s="13" t="n">
-        <v>46265</v>
-      </c>
-      <c r="F124" s="6" t="n">
-        <v>164458.64</v>
-      </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>Izabela Malarecka</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>2.9.4</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E125" s="13" t="n">
-        <v>46265</v>
-      </c>
-      <c r="F125" s="6" t="n">
-        <v>366535.63</v>
-      </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>Izabela Malarecka</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>2.9.5</t>
-        </is>
-      </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t>Bunker windows</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E126" s="13" t="n">
-        <v>46265</v>
-      </c>
-      <c r="F126" s="6" t="n">
-        <v>205428.18</v>
-      </c>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>Izabela Malarecka</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>2.9.6</t>
-        </is>
-      </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>Hatches</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E127" s="13" t="n">
-        <v>46265</v>
-      </c>
-      <c r="F127" s="6" t="n">
-        <v>327190.64</v>
-      </c>
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>Magdalena Białorucka</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>GPO/GPZ power supply</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>enquiry</t>
-        </is>
-      </c>
-      <c r="E128" s="13" t="n">
-        <v>46265</v>
-      </c>
-      <c r="F128" s="6" t="n">
-        <v>11010000</v>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>Radosław Zdancewicz</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>3.3.2</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>GPO/GPZ power supply</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
-        <is>
-          <t>enquiry</t>
-        </is>
-      </c>
-      <c r="E129" s="13" t="n">
-        <v>46265</v>
-      </c>
-      <c r="F129" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" s="5" t="inlineStr">
-        <is>
-          <t>Radosław Zdancewicz</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>3.4.1.2</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>Delivery of instrumentation for the boiler</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E130" s="13" t="n">
-        <v>46265</v>
-      </c>
-      <c r="F130" s="6" t="n">
-        <v>300000</v>
-      </c>
-      <c r="G130" s="5" t="inlineStr">
-        <is>
-          <t>Radosław Zdancewicz</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>5.10.13.2</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>Motorized valves</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E131" s="13" t="n">
-        <v>46265</v>
-      </c>
-      <c r="F131" s="6" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="G131" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>5.10.13.3</t>
-        </is>
-      </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>Safety valves</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E132" s="13" t="n">
-        <v>46265</v>
-      </c>
-      <c r="F132" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G132" s="5" t="inlineStr">
-        <is>
-          <t>Roger Gołombek</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>Next orders 3 months</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>5.10.13.4</t>
-        </is>
-      </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>ON/OFF valves</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="E133" s="13" t="n">
-        <v>46265</v>
-      </c>
-      <c r="F133" s="6" t="n">
-        <v>400000</v>
-      </c>
-      <c r="G133" s="5" t="inlineStr">
         <is>
           <t>Roger Gołombek</t>
         </is>
@@ -5884,10 +4447,10 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>6583222.55</v>
+        <v>8934634.640000001</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6583222.55</v>
+        <v>8934634.640000001</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>6199140</v>
@@ -5915,10 +4478,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>9354454.439999999</v>
+        <v>12695702.15</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>15937676.99</v>
+        <v>21630336.79</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>1209845.03</v>
@@ -5946,10 +4509,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>15234603.88</v>
+        <v>20676138.25</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>31172280.87</v>
+        <v>42306475.04</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>7794586.93</v>
@@ -5977,10 +4540,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>19692376.45</v>
+        <v>26726149.31</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>50864657.32</v>
+        <v>69032624.34999999</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>12423640.08</v>
@@ -6008,10 +4571,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>35769965.4</v>
+        <v>48546372.17</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>86634622.72</v>
+        <v>117578996.52</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>11336449.17</v>
@@ -6039,10 +4602,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>37401116.06</v>
+        <v>50760141.35</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>124035738.78</v>
+        <v>168339137.87</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>13624888.02</v>
@@ -6070,10 +4633,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>36092527.46</v>
+        <v>48984147.76</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>160128266.24</v>
+        <v>217323285.63</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>14910518.13</v>
@@ -6087,11 +4650,7 @@
       <c r="H16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
+      <c r="I16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -6105,10 +4664,10 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>37583108.57</v>
+        <v>51007138.4</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>197711374.81</v>
+        <v>268330424.03</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>15028245.62</v>
@@ -6122,7 +4681,11 @@
       <c r="H17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -6136,10 +4699,10 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>27852201.13</v>
+        <v>21564903.24</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>225563575.94</v>
+        <v>289895327.27</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>24539477.12</v>
@@ -6167,10 +4730,10 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>27909418.28</v>
+        <v>21609204.31</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>253472994.22</v>
+        <v>311504531.58</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>31216463.12</v>
@@ -6198,10 +4761,10 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>26089618.29</v>
+        <v>20200202.18</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>279562612.51</v>
+        <v>331704733.76</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>27608192.85</v>
@@ -6229,10 +4792,10 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>44233090.56</v>
+        <v>34248004.8</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>323795703.07</v>
+        <v>365952738.56</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>26540967.3</v>
@@ -6260,10 +4823,10 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>30825004.67</v>
+        <v>23866632.29</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>354620707.74</v>
+        <v>389819370.85</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>28846792.41</v>
@@ -6291,10 +4854,10 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>17353615.01</v>
+        <v>13436246.1</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>371974322.75</v>
+        <v>403255616.95</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>27022580.63</v>
@@ -6322,10 +4885,10 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>16448333.12</v>
+        <v>12735320.64</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>388422655.87</v>
+        <v>415990937.59</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>28325747.31</v>
@@ -6353,10 +4916,10 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>16732222.01</v>
+        <v>12955125.06</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>405154877.88</v>
+        <v>428946062.65</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>35039986.08</v>
@@ -6384,10 +4947,10 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>14632253.17</v>
+        <v>11329198.8</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>419787131.05</v>
+        <v>440275261.45</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>33822381.41</v>
@@ -6415,10 +4978,10 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>7825647.37</v>
+        <v>6059102.03</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>427612778.42</v>
+        <v>446334363.48</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>25897922.24</v>
@@ -6446,10 +5009,10 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>7825647.37</v>
+        <v>6059102.03</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>435438425.79</v>
+        <v>452393465.51</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>28095849.06</v>
@@ -6477,10 +5040,10 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>9568638.189999999</v>
+        <v>7408633.73</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>445007063.98</v>
+        <v>459802099.24</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>20736784.02</v>
@@ -6508,10 +5071,10 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>9568638.189999999</v>
+        <v>7408633.72</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>454575702.17</v>
+        <v>467210732.96</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>17315684.93</v>
@@ -6539,10 +5102,10 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>9568638.199999999</v>
+        <v>7408633.74</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>464144340.37</v>
+        <v>474619366.7</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>15763709.59</v>
@@ -6570,10 +5133,10 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>8966792.470000001</v>
+        <v>6942647.41</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>473111132.84</v>
+        <v>481562014.11</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>12623620.61</v>
@@ -6601,10 +5164,10 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>7330590.56</v>
+        <v>5675798.31</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>480441723.4</v>
+        <v>487237812.42</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>10976891.07</v>
@@ -6632,10 +5195,10 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>5600622.36</v>
+        <v>4336349.53</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>486042345.76</v>
+        <v>491574161.95</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>11889923.67</v>
@@ -6663,10 +5226,10 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>5549096.79</v>
+        <v>4296455.23</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>491591442.55</v>
+        <v>495870617.18</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>0</v>
@@ -6694,10 +5257,10 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>3800823.45</v>
+        <v>2942833.48</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>495392266</v>
+        <v>498813450.66</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>1910542.1</v>
@@ -6725,10 +5288,10 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>3800823.45</v>
+        <v>2942833.48</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>499193089.45</v>
+        <v>501756284.14</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>2167008.58</v>
@@ -6756,10 +5319,10 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>3784912.33</v>
+        <v>2930514.1</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>502978001.78</v>
+        <v>504686798.24</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>758299.79</v>
@@ -6787,10 +5350,10 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>3784912.34</v>
+        <v>2930514.11</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>506762914.12</v>
+        <v>507617312.35</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>3740876.04</v>
@@ -6818,7 +5381,7 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>3784912.34</v>
+        <v>2930514.11</v>
       </c>
       <c r="D40" s="6" t="n">
         <v>510547826.46</v>
@@ -8874,16 +7437,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -11560,1326 +10123,6 @@
       </c>
       <c r="G89" s="5">
         <f>'10_Source_Orders_3M'!G89</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="5">
-        <f>'10_Source_Orders_3M'!A90</f>
-        <v/>
-      </c>
-      <c r="B90" s="5">
-        <f>'10_Source_Orders_3M'!B90</f>
-        <v/>
-      </c>
-      <c r="C90" s="5">
-        <f>'10_Source_Orders_3M'!C90</f>
-        <v/>
-      </c>
-      <c r="D90" s="5">
-        <f>'10_Source_Orders_3M'!D90</f>
-        <v/>
-      </c>
-      <c r="E90" s="13">
-        <f>'10_Source_Orders_3M'!E90</f>
-        <v/>
-      </c>
-      <c r="F90" s="6">
-        <f>'10_Source_Orders_3M'!F90</f>
-        <v/>
-      </c>
-      <c r="G90" s="5">
-        <f>'10_Source_Orders_3M'!G90</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="5">
-        <f>'10_Source_Orders_3M'!A91</f>
-        <v/>
-      </c>
-      <c r="B91" s="5">
-        <f>'10_Source_Orders_3M'!B91</f>
-        <v/>
-      </c>
-      <c r="C91" s="5">
-        <f>'10_Source_Orders_3M'!C91</f>
-        <v/>
-      </c>
-      <c r="D91" s="5">
-        <f>'10_Source_Orders_3M'!D91</f>
-        <v/>
-      </c>
-      <c r="E91" s="13">
-        <f>'10_Source_Orders_3M'!E91</f>
-        <v/>
-      </c>
-      <c r="F91" s="6">
-        <f>'10_Source_Orders_3M'!F91</f>
-        <v/>
-      </c>
-      <c r="G91" s="5">
-        <f>'10_Source_Orders_3M'!G91</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="5">
-        <f>'10_Source_Orders_3M'!A92</f>
-        <v/>
-      </c>
-      <c r="B92" s="5">
-        <f>'10_Source_Orders_3M'!B92</f>
-        <v/>
-      </c>
-      <c r="C92" s="5">
-        <f>'10_Source_Orders_3M'!C92</f>
-        <v/>
-      </c>
-      <c r="D92" s="5">
-        <f>'10_Source_Orders_3M'!D92</f>
-        <v/>
-      </c>
-      <c r="E92" s="13">
-        <f>'10_Source_Orders_3M'!E92</f>
-        <v/>
-      </c>
-      <c r="F92" s="6">
-        <f>'10_Source_Orders_3M'!F92</f>
-        <v/>
-      </c>
-      <c r="G92" s="5">
-        <f>'10_Source_Orders_3M'!G92</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="5">
-        <f>'10_Source_Orders_3M'!A93</f>
-        <v/>
-      </c>
-      <c r="B93" s="5">
-        <f>'10_Source_Orders_3M'!B93</f>
-        <v/>
-      </c>
-      <c r="C93" s="5">
-        <f>'10_Source_Orders_3M'!C93</f>
-        <v/>
-      </c>
-      <c r="D93" s="5">
-        <f>'10_Source_Orders_3M'!D93</f>
-        <v/>
-      </c>
-      <c r="E93" s="13">
-        <f>'10_Source_Orders_3M'!E93</f>
-        <v/>
-      </c>
-      <c r="F93" s="6">
-        <f>'10_Source_Orders_3M'!F93</f>
-        <v/>
-      </c>
-      <c r="G93" s="5">
-        <f>'10_Source_Orders_3M'!G93</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="5">
-        <f>'10_Source_Orders_3M'!A94</f>
-        <v/>
-      </c>
-      <c r="B94" s="5">
-        <f>'10_Source_Orders_3M'!B94</f>
-        <v/>
-      </c>
-      <c r="C94" s="5">
-        <f>'10_Source_Orders_3M'!C94</f>
-        <v/>
-      </c>
-      <c r="D94" s="5">
-        <f>'10_Source_Orders_3M'!D94</f>
-        <v/>
-      </c>
-      <c r="E94" s="13">
-        <f>'10_Source_Orders_3M'!E94</f>
-        <v/>
-      </c>
-      <c r="F94" s="6">
-        <f>'10_Source_Orders_3M'!F94</f>
-        <v/>
-      </c>
-      <c r="G94" s="5">
-        <f>'10_Source_Orders_3M'!G94</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="5">
-        <f>'10_Source_Orders_3M'!A95</f>
-        <v/>
-      </c>
-      <c r="B95" s="5">
-        <f>'10_Source_Orders_3M'!B95</f>
-        <v/>
-      </c>
-      <c r="C95" s="5">
-        <f>'10_Source_Orders_3M'!C95</f>
-        <v/>
-      </c>
-      <c r="D95" s="5">
-        <f>'10_Source_Orders_3M'!D95</f>
-        <v/>
-      </c>
-      <c r="E95" s="13">
-        <f>'10_Source_Orders_3M'!E95</f>
-        <v/>
-      </c>
-      <c r="F95" s="6">
-        <f>'10_Source_Orders_3M'!F95</f>
-        <v/>
-      </c>
-      <c r="G95" s="5">
-        <f>'10_Source_Orders_3M'!G95</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="5">
-        <f>'10_Source_Orders_3M'!A96</f>
-        <v/>
-      </c>
-      <c r="B96" s="5">
-        <f>'10_Source_Orders_3M'!B96</f>
-        <v/>
-      </c>
-      <c r="C96" s="5">
-        <f>'10_Source_Orders_3M'!C96</f>
-        <v/>
-      </c>
-      <c r="D96" s="5">
-        <f>'10_Source_Orders_3M'!D96</f>
-        <v/>
-      </c>
-      <c r="E96" s="13">
-        <f>'10_Source_Orders_3M'!E96</f>
-        <v/>
-      </c>
-      <c r="F96" s="6">
-        <f>'10_Source_Orders_3M'!F96</f>
-        <v/>
-      </c>
-      <c r="G96" s="5">
-        <f>'10_Source_Orders_3M'!G96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="5">
-        <f>'10_Source_Orders_3M'!A97</f>
-        <v/>
-      </c>
-      <c r="B97" s="5">
-        <f>'10_Source_Orders_3M'!B97</f>
-        <v/>
-      </c>
-      <c r="C97" s="5">
-        <f>'10_Source_Orders_3M'!C97</f>
-        <v/>
-      </c>
-      <c r="D97" s="5">
-        <f>'10_Source_Orders_3M'!D97</f>
-        <v/>
-      </c>
-      <c r="E97" s="13">
-        <f>'10_Source_Orders_3M'!E97</f>
-        <v/>
-      </c>
-      <c r="F97" s="6">
-        <f>'10_Source_Orders_3M'!F97</f>
-        <v/>
-      </c>
-      <c r="G97" s="5">
-        <f>'10_Source_Orders_3M'!G97</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="5">
-        <f>'10_Source_Orders_3M'!A98</f>
-        <v/>
-      </c>
-      <c r="B98" s="5">
-        <f>'10_Source_Orders_3M'!B98</f>
-        <v/>
-      </c>
-      <c r="C98" s="5">
-        <f>'10_Source_Orders_3M'!C98</f>
-        <v/>
-      </c>
-      <c r="D98" s="5">
-        <f>'10_Source_Orders_3M'!D98</f>
-        <v/>
-      </c>
-      <c r="E98" s="13">
-        <f>'10_Source_Orders_3M'!E98</f>
-        <v/>
-      </c>
-      <c r="F98" s="6">
-        <f>'10_Source_Orders_3M'!F98</f>
-        <v/>
-      </c>
-      <c r="G98" s="5">
-        <f>'10_Source_Orders_3M'!G98</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="5">
-        <f>'10_Source_Orders_3M'!A99</f>
-        <v/>
-      </c>
-      <c r="B99" s="5">
-        <f>'10_Source_Orders_3M'!B99</f>
-        <v/>
-      </c>
-      <c r="C99" s="5">
-        <f>'10_Source_Orders_3M'!C99</f>
-        <v/>
-      </c>
-      <c r="D99" s="5">
-        <f>'10_Source_Orders_3M'!D99</f>
-        <v/>
-      </c>
-      <c r="E99" s="13">
-        <f>'10_Source_Orders_3M'!E99</f>
-        <v/>
-      </c>
-      <c r="F99" s="6">
-        <f>'10_Source_Orders_3M'!F99</f>
-        <v/>
-      </c>
-      <c r="G99" s="5">
-        <f>'10_Source_Orders_3M'!G99</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="5">
-        <f>'10_Source_Orders_3M'!A100</f>
-        <v/>
-      </c>
-      <c r="B100" s="5">
-        <f>'10_Source_Orders_3M'!B100</f>
-        <v/>
-      </c>
-      <c r="C100" s="5">
-        <f>'10_Source_Orders_3M'!C100</f>
-        <v/>
-      </c>
-      <c r="D100" s="5">
-        <f>'10_Source_Orders_3M'!D100</f>
-        <v/>
-      </c>
-      <c r="E100" s="13">
-        <f>'10_Source_Orders_3M'!E100</f>
-        <v/>
-      </c>
-      <c r="F100" s="6">
-        <f>'10_Source_Orders_3M'!F100</f>
-        <v/>
-      </c>
-      <c r="G100" s="5">
-        <f>'10_Source_Orders_3M'!G100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="5">
-        <f>'10_Source_Orders_3M'!A101</f>
-        <v/>
-      </c>
-      <c r="B101" s="5">
-        <f>'10_Source_Orders_3M'!B101</f>
-        <v/>
-      </c>
-      <c r="C101" s="5">
-        <f>'10_Source_Orders_3M'!C101</f>
-        <v/>
-      </c>
-      <c r="D101" s="5">
-        <f>'10_Source_Orders_3M'!D101</f>
-        <v/>
-      </c>
-      <c r="E101" s="13">
-        <f>'10_Source_Orders_3M'!E101</f>
-        <v/>
-      </c>
-      <c r="F101" s="6">
-        <f>'10_Source_Orders_3M'!F101</f>
-        <v/>
-      </c>
-      <c r="G101" s="5">
-        <f>'10_Source_Orders_3M'!G101</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="5">
-        <f>'10_Source_Orders_3M'!A102</f>
-        <v/>
-      </c>
-      <c r="B102" s="5">
-        <f>'10_Source_Orders_3M'!B102</f>
-        <v/>
-      </c>
-      <c r="C102" s="5">
-        <f>'10_Source_Orders_3M'!C102</f>
-        <v/>
-      </c>
-      <c r="D102" s="5">
-        <f>'10_Source_Orders_3M'!D102</f>
-        <v/>
-      </c>
-      <c r="E102" s="13">
-        <f>'10_Source_Orders_3M'!E102</f>
-        <v/>
-      </c>
-      <c r="F102" s="6">
-        <f>'10_Source_Orders_3M'!F102</f>
-        <v/>
-      </c>
-      <c r="G102" s="5">
-        <f>'10_Source_Orders_3M'!G102</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="5">
-        <f>'10_Source_Orders_3M'!A103</f>
-        <v/>
-      </c>
-      <c r="B103" s="5">
-        <f>'10_Source_Orders_3M'!B103</f>
-        <v/>
-      </c>
-      <c r="C103" s="5">
-        <f>'10_Source_Orders_3M'!C103</f>
-        <v/>
-      </c>
-      <c r="D103" s="5">
-        <f>'10_Source_Orders_3M'!D103</f>
-        <v/>
-      </c>
-      <c r="E103" s="13">
-        <f>'10_Source_Orders_3M'!E103</f>
-        <v/>
-      </c>
-      <c r="F103" s="6">
-        <f>'10_Source_Orders_3M'!F103</f>
-        <v/>
-      </c>
-      <c r="G103" s="5">
-        <f>'10_Source_Orders_3M'!G103</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="5">
-        <f>'10_Source_Orders_3M'!A104</f>
-        <v/>
-      </c>
-      <c r="B104" s="5">
-        <f>'10_Source_Orders_3M'!B104</f>
-        <v/>
-      </c>
-      <c r="C104" s="5">
-        <f>'10_Source_Orders_3M'!C104</f>
-        <v/>
-      </c>
-      <c r="D104" s="5">
-        <f>'10_Source_Orders_3M'!D104</f>
-        <v/>
-      </c>
-      <c r="E104" s="13">
-        <f>'10_Source_Orders_3M'!E104</f>
-        <v/>
-      </c>
-      <c r="F104" s="6">
-        <f>'10_Source_Orders_3M'!F104</f>
-        <v/>
-      </c>
-      <c r="G104" s="5">
-        <f>'10_Source_Orders_3M'!G104</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="5">
-        <f>'10_Source_Orders_3M'!A105</f>
-        <v/>
-      </c>
-      <c r="B105" s="5">
-        <f>'10_Source_Orders_3M'!B105</f>
-        <v/>
-      </c>
-      <c r="C105" s="5">
-        <f>'10_Source_Orders_3M'!C105</f>
-        <v/>
-      </c>
-      <c r="D105" s="5">
-        <f>'10_Source_Orders_3M'!D105</f>
-        <v/>
-      </c>
-      <c r="E105" s="13">
-        <f>'10_Source_Orders_3M'!E105</f>
-        <v/>
-      </c>
-      <c r="F105" s="6">
-        <f>'10_Source_Orders_3M'!F105</f>
-        <v/>
-      </c>
-      <c r="G105" s="5">
-        <f>'10_Source_Orders_3M'!G105</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="5">
-        <f>'10_Source_Orders_3M'!A106</f>
-        <v/>
-      </c>
-      <c r="B106" s="5">
-        <f>'10_Source_Orders_3M'!B106</f>
-        <v/>
-      </c>
-      <c r="C106" s="5">
-        <f>'10_Source_Orders_3M'!C106</f>
-        <v/>
-      </c>
-      <c r="D106" s="5">
-        <f>'10_Source_Orders_3M'!D106</f>
-        <v/>
-      </c>
-      <c r="E106" s="13">
-        <f>'10_Source_Orders_3M'!E106</f>
-        <v/>
-      </c>
-      <c r="F106" s="6">
-        <f>'10_Source_Orders_3M'!F106</f>
-        <v/>
-      </c>
-      <c r="G106" s="5">
-        <f>'10_Source_Orders_3M'!G106</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="5">
-        <f>'10_Source_Orders_3M'!A107</f>
-        <v/>
-      </c>
-      <c r="B107" s="5">
-        <f>'10_Source_Orders_3M'!B107</f>
-        <v/>
-      </c>
-      <c r="C107" s="5">
-        <f>'10_Source_Orders_3M'!C107</f>
-        <v/>
-      </c>
-      <c r="D107" s="5">
-        <f>'10_Source_Orders_3M'!D107</f>
-        <v/>
-      </c>
-      <c r="E107" s="13">
-        <f>'10_Source_Orders_3M'!E107</f>
-        <v/>
-      </c>
-      <c r="F107" s="6">
-        <f>'10_Source_Orders_3M'!F107</f>
-        <v/>
-      </c>
-      <c r="G107" s="5">
-        <f>'10_Source_Orders_3M'!G107</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="5">
-        <f>'10_Source_Orders_3M'!A108</f>
-        <v/>
-      </c>
-      <c r="B108" s="5">
-        <f>'10_Source_Orders_3M'!B108</f>
-        <v/>
-      </c>
-      <c r="C108" s="5">
-        <f>'10_Source_Orders_3M'!C108</f>
-        <v/>
-      </c>
-      <c r="D108" s="5">
-        <f>'10_Source_Orders_3M'!D108</f>
-        <v/>
-      </c>
-      <c r="E108" s="13">
-        <f>'10_Source_Orders_3M'!E108</f>
-        <v/>
-      </c>
-      <c r="F108" s="6">
-        <f>'10_Source_Orders_3M'!F108</f>
-        <v/>
-      </c>
-      <c r="G108" s="5">
-        <f>'10_Source_Orders_3M'!G108</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="5">
-        <f>'10_Source_Orders_3M'!A109</f>
-        <v/>
-      </c>
-      <c r="B109" s="5">
-        <f>'10_Source_Orders_3M'!B109</f>
-        <v/>
-      </c>
-      <c r="C109" s="5">
-        <f>'10_Source_Orders_3M'!C109</f>
-        <v/>
-      </c>
-      <c r="D109" s="5">
-        <f>'10_Source_Orders_3M'!D109</f>
-        <v/>
-      </c>
-      <c r="E109" s="13">
-        <f>'10_Source_Orders_3M'!E109</f>
-        <v/>
-      </c>
-      <c r="F109" s="6">
-        <f>'10_Source_Orders_3M'!F109</f>
-        <v/>
-      </c>
-      <c r="G109" s="5">
-        <f>'10_Source_Orders_3M'!G109</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="5">
-        <f>'10_Source_Orders_3M'!A110</f>
-        <v/>
-      </c>
-      <c r="B110" s="5">
-        <f>'10_Source_Orders_3M'!B110</f>
-        <v/>
-      </c>
-      <c r="C110" s="5">
-        <f>'10_Source_Orders_3M'!C110</f>
-        <v/>
-      </c>
-      <c r="D110" s="5">
-        <f>'10_Source_Orders_3M'!D110</f>
-        <v/>
-      </c>
-      <c r="E110" s="13">
-        <f>'10_Source_Orders_3M'!E110</f>
-        <v/>
-      </c>
-      <c r="F110" s="6">
-        <f>'10_Source_Orders_3M'!F110</f>
-        <v/>
-      </c>
-      <c r="G110" s="5">
-        <f>'10_Source_Orders_3M'!G110</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="5">
-        <f>'10_Source_Orders_3M'!A111</f>
-        <v/>
-      </c>
-      <c r="B111" s="5">
-        <f>'10_Source_Orders_3M'!B111</f>
-        <v/>
-      </c>
-      <c r="C111" s="5">
-        <f>'10_Source_Orders_3M'!C111</f>
-        <v/>
-      </c>
-      <c r="D111" s="5">
-        <f>'10_Source_Orders_3M'!D111</f>
-        <v/>
-      </c>
-      <c r="E111" s="13">
-        <f>'10_Source_Orders_3M'!E111</f>
-        <v/>
-      </c>
-      <c r="F111" s="6">
-        <f>'10_Source_Orders_3M'!F111</f>
-        <v/>
-      </c>
-      <c r="G111" s="5">
-        <f>'10_Source_Orders_3M'!G111</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="5">
-        <f>'10_Source_Orders_3M'!A112</f>
-        <v/>
-      </c>
-      <c r="B112" s="5">
-        <f>'10_Source_Orders_3M'!B112</f>
-        <v/>
-      </c>
-      <c r="C112" s="5">
-        <f>'10_Source_Orders_3M'!C112</f>
-        <v/>
-      </c>
-      <c r="D112" s="5">
-        <f>'10_Source_Orders_3M'!D112</f>
-        <v/>
-      </c>
-      <c r="E112" s="13">
-        <f>'10_Source_Orders_3M'!E112</f>
-        <v/>
-      </c>
-      <c r="F112" s="6">
-        <f>'10_Source_Orders_3M'!F112</f>
-        <v/>
-      </c>
-      <c r="G112" s="5">
-        <f>'10_Source_Orders_3M'!G112</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="5">
-        <f>'10_Source_Orders_3M'!A113</f>
-        <v/>
-      </c>
-      <c r="B113" s="5">
-        <f>'10_Source_Orders_3M'!B113</f>
-        <v/>
-      </c>
-      <c r="C113" s="5">
-        <f>'10_Source_Orders_3M'!C113</f>
-        <v/>
-      </c>
-      <c r="D113" s="5">
-        <f>'10_Source_Orders_3M'!D113</f>
-        <v/>
-      </c>
-      <c r="E113" s="13">
-        <f>'10_Source_Orders_3M'!E113</f>
-        <v/>
-      </c>
-      <c r="F113" s="6">
-        <f>'10_Source_Orders_3M'!F113</f>
-        <v/>
-      </c>
-      <c r="G113" s="5">
-        <f>'10_Source_Orders_3M'!G113</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="5">
-        <f>'10_Source_Orders_3M'!A114</f>
-        <v/>
-      </c>
-      <c r="B114" s="5">
-        <f>'10_Source_Orders_3M'!B114</f>
-        <v/>
-      </c>
-      <c r="C114" s="5">
-        <f>'10_Source_Orders_3M'!C114</f>
-        <v/>
-      </c>
-      <c r="D114" s="5">
-        <f>'10_Source_Orders_3M'!D114</f>
-        <v/>
-      </c>
-      <c r="E114" s="13">
-        <f>'10_Source_Orders_3M'!E114</f>
-        <v/>
-      </c>
-      <c r="F114" s="6">
-        <f>'10_Source_Orders_3M'!F114</f>
-        <v/>
-      </c>
-      <c r="G114" s="5">
-        <f>'10_Source_Orders_3M'!G114</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="5">
-        <f>'10_Source_Orders_3M'!A115</f>
-        <v/>
-      </c>
-      <c r="B115" s="5">
-        <f>'10_Source_Orders_3M'!B115</f>
-        <v/>
-      </c>
-      <c r="C115" s="5">
-        <f>'10_Source_Orders_3M'!C115</f>
-        <v/>
-      </c>
-      <c r="D115" s="5">
-        <f>'10_Source_Orders_3M'!D115</f>
-        <v/>
-      </c>
-      <c r="E115" s="13">
-        <f>'10_Source_Orders_3M'!E115</f>
-        <v/>
-      </c>
-      <c r="F115" s="6">
-        <f>'10_Source_Orders_3M'!F115</f>
-        <v/>
-      </c>
-      <c r="G115" s="5">
-        <f>'10_Source_Orders_3M'!G115</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="5">
-        <f>'10_Source_Orders_3M'!A116</f>
-        <v/>
-      </c>
-      <c r="B116" s="5">
-        <f>'10_Source_Orders_3M'!B116</f>
-        <v/>
-      </c>
-      <c r="C116" s="5">
-        <f>'10_Source_Orders_3M'!C116</f>
-        <v/>
-      </c>
-      <c r="D116" s="5">
-        <f>'10_Source_Orders_3M'!D116</f>
-        <v/>
-      </c>
-      <c r="E116" s="13">
-        <f>'10_Source_Orders_3M'!E116</f>
-        <v/>
-      </c>
-      <c r="F116" s="6">
-        <f>'10_Source_Orders_3M'!F116</f>
-        <v/>
-      </c>
-      <c r="G116" s="5">
-        <f>'10_Source_Orders_3M'!G116</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="5">
-        <f>'10_Source_Orders_3M'!A117</f>
-        <v/>
-      </c>
-      <c r="B117" s="5">
-        <f>'10_Source_Orders_3M'!B117</f>
-        <v/>
-      </c>
-      <c r="C117" s="5">
-        <f>'10_Source_Orders_3M'!C117</f>
-        <v/>
-      </c>
-      <c r="D117" s="5">
-        <f>'10_Source_Orders_3M'!D117</f>
-        <v/>
-      </c>
-      <c r="E117" s="13">
-        <f>'10_Source_Orders_3M'!E117</f>
-        <v/>
-      </c>
-      <c r="F117" s="6">
-        <f>'10_Source_Orders_3M'!F117</f>
-        <v/>
-      </c>
-      <c r="G117" s="5">
-        <f>'10_Source_Orders_3M'!G117</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="5">
-        <f>'10_Source_Orders_3M'!A118</f>
-        <v/>
-      </c>
-      <c r="B118" s="5">
-        <f>'10_Source_Orders_3M'!B118</f>
-        <v/>
-      </c>
-      <c r="C118" s="5">
-        <f>'10_Source_Orders_3M'!C118</f>
-        <v/>
-      </c>
-      <c r="D118" s="5">
-        <f>'10_Source_Orders_3M'!D118</f>
-        <v/>
-      </c>
-      <c r="E118" s="13">
-        <f>'10_Source_Orders_3M'!E118</f>
-        <v/>
-      </c>
-      <c r="F118" s="6">
-        <f>'10_Source_Orders_3M'!F118</f>
-        <v/>
-      </c>
-      <c r="G118" s="5">
-        <f>'10_Source_Orders_3M'!G118</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="5">
-        <f>'10_Source_Orders_3M'!A119</f>
-        <v/>
-      </c>
-      <c r="B119" s="5">
-        <f>'10_Source_Orders_3M'!B119</f>
-        <v/>
-      </c>
-      <c r="C119" s="5">
-        <f>'10_Source_Orders_3M'!C119</f>
-        <v/>
-      </c>
-      <c r="D119" s="5">
-        <f>'10_Source_Orders_3M'!D119</f>
-        <v/>
-      </c>
-      <c r="E119" s="13">
-        <f>'10_Source_Orders_3M'!E119</f>
-        <v/>
-      </c>
-      <c r="F119" s="6">
-        <f>'10_Source_Orders_3M'!F119</f>
-        <v/>
-      </c>
-      <c r="G119" s="5">
-        <f>'10_Source_Orders_3M'!G119</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="5">
-        <f>'10_Source_Orders_3M'!A120</f>
-        <v/>
-      </c>
-      <c r="B120" s="5">
-        <f>'10_Source_Orders_3M'!B120</f>
-        <v/>
-      </c>
-      <c r="C120" s="5">
-        <f>'10_Source_Orders_3M'!C120</f>
-        <v/>
-      </c>
-      <c r="D120" s="5">
-        <f>'10_Source_Orders_3M'!D120</f>
-        <v/>
-      </c>
-      <c r="E120" s="13">
-        <f>'10_Source_Orders_3M'!E120</f>
-        <v/>
-      </c>
-      <c r="F120" s="6">
-        <f>'10_Source_Orders_3M'!F120</f>
-        <v/>
-      </c>
-      <c r="G120" s="5">
-        <f>'10_Source_Orders_3M'!G120</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="5">
-        <f>'10_Source_Orders_3M'!A121</f>
-        <v/>
-      </c>
-      <c r="B121" s="5">
-        <f>'10_Source_Orders_3M'!B121</f>
-        <v/>
-      </c>
-      <c r="C121" s="5">
-        <f>'10_Source_Orders_3M'!C121</f>
-        <v/>
-      </c>
-      <c r="D121" s="5">
-        <f>'10_Source_Orders_3M'!D121</f>
-        <v/>
-      </c>
-      <c r="E121" s="13">
-        <f>'10_Source_Orders_3M'!E121</f>
-        <v/>
-      </c>
-      <c r="F121" s="6">
-        <f>'10_Source_Orders_3M'!F121</f>
-        <v/>
-      </c>
-      <c r="G121" s="5">
-        <f>'10_Source_Orders_3M'!G121</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="5">
-        <f>'10_Source_Orders_3M'!A122</f>
-        <v/>
-      </c>
-      <c r="B122" s="5">
-        <f>'10_Source_Orders_3M'!B122</f>
-        <v/>
-      </c>
-      <c r="C122" s="5">
-        <f>'10_Source_Orders_3M'!C122</f>
-        <v/>
-      </c>
-      <c r="D122" s="5">
-        <f>'10_Source_Orders_3M'!D122</f>
-        <v/>
-      </c>
-      <c r="E122" s="13">
-        <f>'10_Source_Orders_3M'!E122</f>
-        <v/>
-      </c>
-      <c r="F122" s="6">
-        <f>'10_Source_Orders_3M'!F122</f>
-        <v/>
-      </c>
-      <c r="G122" s="5">
-        <f>'10_Source_Orders_3M'!G122</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="5">
-        <f>'10_Source_Orders_3M'!A123</f>
-        <v/>
-      </c>
-      <c r="B123" s="5">
-        <f>'10_Source_Orders_3M'!B123</f>
-        <v/>
-      </c>
-      <c r="C123" s="5">
-        <f>'10_Source_Orders_3M'!C123</f>
-        <v/>
-      </c>
-      <c r="D123" s="5">
-        <f>'10_Source_Orders_3M'!D123</f>
-        <v/>
-      </c>
-      <c r="E123" s="13">
-        <f>'10_Source_Orders_3M'!E123</f>
-        <v/>
-      </c>
-      <c r="F123" s="6">
-        <f>'10_Source_Orders_3M'!F123</f>
-        <v/>
-      </c>
-      <c r="G123" s="5">
-        <f>'10_Source_Orders_3M'!G123</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="5">
-        <f>'10_Source_Orders_3M'!A124</f>
-        <v/>
-      </c>
-      <c r="B124" s="5">
-        <f>'10_Source_Orders_3M'!B124</f>
-        <v/>
-      </c>
-      <c r="C124" s="5">
-        <f>'10_Source_Orders_3M'!C124</f>
-        <v/>
-      </c>
-      <c r="D124" s="5">
-        <f>'10_Source_Orders_3M'!D124</f>
-        <v/>
-      </c>
-      <c r="E124" s="13">
-        <f>'10_Source_Orders_3M'!E124</f>
-        <v/>
-      </c>
-      <c r="F124" s="6">
-        <f>'10_Source_Orders_3M'!F124</f>
-        <v/>
-      </c>
-      <c r="G124" s="5">
-        <f>'10_Source_Orders_3M'!G124</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="5">
-        <f>'10_Source_Orders_3M'!A125</f>
-        <v/>
-      </c>
-      <c r="B125" s="5">
-        <f>'10_Source_Orders_3M'!B125</f>
-        <v/>
-      </c>
-      <c r="C125" s="5">
-        <f>'10_Source_Orders_3M'!C125</f>
-        <v/>
-      </c>
-      <c r="D125" s="5">
-        <f>'10_Source_Orders_3M'!D125</f>
-        <v/>
-      </c>
-      <c r="E125" s="13">
-        <f>'10_Source_Orders_3M'!E125</f>
-        <v/>
-      </c>
-      <c r="F125" s="6">
-        <f>'10_Source_Orders_3M'!F125</f>
-        <v/>
-      </c>
-      <c r="G125" s="5">
-        <f>'10_Source_Orders_3M'!G125</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="5">
-        <f>'10_Source_Orders_3M'!A126</f>
-        <v/>
-      </c>
-      <c r="B126" s="5">
-        <f>'10_Source_Orders_3M'!B126</f>
-        <v/>
-      </c>
-      <c r="C126" s="5">
-        <f>'10_Source_Orders_3M'!C126</f>
-        <v/>
-      </c>
-      <c r="D126" s="5">
-        <f>'10_Source_Orders_3M'!D126</f>
-        <v/>
-      </c>
-      <c r="E126" s="13">
-        <f>'10_Source_Orders_3M'!E126</f>
-        <v/>
-      </c>
-      <c r="F126" s="6">
-        <f>'10_Source_Orders_3M'!F126</f>
-        <v/>
-      </c>
-      <c r="G126" s="5">
-        <f>'10_Source_Orders_3M'!G126</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="5">
-        <f>'10_Source_Orders_3M'!A127</f>
-        <v/>
-      </c>
-      <c r="B127" s="5">
-        <f>'10_Source_Orders_3M'!B127</f>
-        <v/>
-      </c>
-      <c r="C127" s="5">
-        <f>'10_Source_Orders_3M'!C127</f>
-        <v/>
-      </c>
-      <c r="D127" s="5">
-        <f>'10_Source_Orders_3M'!D127</f>
-        <v/>
-      </c>
-      <c r="E127" s="13">
-        <f>'10_Source_Orders_3M'!E127</f>
-        <v/>
-      </c>
-      <c r="F127" s="6">
-        <f>'10_Source_Orders_3M'!F127</f>
-        <v/>
-      </c>
-      <c r="G127" s="5">
-        <f>'10_Source_Orders_3M'!G127</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="5">
-        <f>'10_Source_Orders_3M'!A128</f>
-        <v/>
-      </c>
-      <c r="B128" s="5">
-        <f>'10_Source_Orders_3M'!B128</f>
-        <v/>
-      </c>
-      <c r="C128" s="5">
-        <f>'10_Source_Orders_3M'!C128</f>
-        <v/>
-      </c>
-      <c r="D128" s="5">
-        <f>'10_Source_Orders_3M'!D128</f>
-        <v/>
-      </c>
-      <c r="E128" s="13">
-        <f>'10_Source_Orders_3M'!E128</f>
-        <v/>
-      </c>
-      <c r="F128" s="6">
-        <f>'10_Source_Orders_3M'!F128</f>
-        <v/>
-      </c>
-      <c r="G128" s="5">
-        <f>'10_Source_Orders_3M'!G128</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="5">
-        <f>'10_Source_Orders_3M'!A129</f>
-        <v/>
-      </c>
-      <c r="B129" s="5">
-        <f>'10_Source_Orders_3M'!B129</f>
-        <v/>
-      </c>
-      <c r="C129" s="5">
-        <f>'10_Source_Orders_3M'!C129</f>
-        <v/>
-      </c>
-      <c r="D129" s="5">
-        <f>'10_Source_Orders_3M'!D129</f>
-        <v/>
-      </c>
-      <c r="E129" s="13">
-        <f>'10_Source_Orders_3M'!E129</f>
-        <v/>
-      </c>
-      <c r="F129" s="6">
-        <f>'10_Source_Orders_3M'!F129</f>
-        <v/>
-      </c>
-      <c r="G129" s="5">
-        <f>'10_Source_Orders_3M'!G129</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="5">
-        <f>'10_Source_Orders_3M'!A130</f>
-        <v/>
-      </c>
-      <c r="B130" s="5">
-        <f>'10_Source_Orders_3M'!B130</f>
-        <v/>
-      </c>
-      <c r="C130" s="5">
-        <f>'10_Source_Orders_3M'!C130</f>
-        <v/>
-      </c>
-      <c r="D130" s="5">
-        <f>'10_Source_Orders_3M'!D130</f>
-        <v/>
-      </c>
-      <c r="E130" s="13">
-        <f>'10_Source_Orders_3M'!E130</f>
-        <v/>
-      </c>
-      <c r="F130" s="6">
-        <f>'10_Source_Orders_3M'!F130</f>
-        <v/>
-      </c>
-      <c r="G130" s="5">
-        <f>'10_Source_Orders_3M'!G130</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="5">
-        <f>'10_Source_Orders_3M'!A131</f>
-        <v/>
-      </c>
-      <c r="B131" s="5">
-        <f>'10_Source_Orders_3M'!B131</f>
-        <v/>
-      </c>
-      <c r="C131" s="5">
-        <f>'10_Source_Orders_3M'!C131</f>
-        <v/>
-      </c>
-      <c r="D131" s="5">
-        <f>'10_Source_Orders_3M'!D131</f>
-        <v/>
-      </c>
-      <c r="E131" s="13">
-        <f>'10_Source_Orders_3M'!E131</f>
-        <v/>
-      </c>
-      <c r="F131" s="6">
-        <f>'10_Source_Orders_3M'!F131</f>
-        <v/>
-      </c>
-      <c r="G131" s="5">
-        <f>'10_Source_Orders_3M'!G131</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="5">
-        <f>'10_Source_Orders_3M'!A132</f>
-        <v/>
-      </c>
-      <c r="B132" s="5">
-        <f>'10_Source_Orders_3M'!B132</f>
-        <v/>
-      </c>
-      <c r="C132" s="5">
-        <f>'10_Source_Orders_3M'!C132</f>
-        <v/>
-      </c>
-      <c r="D132" s="5">
-        <f>'10_Source_Orders_3M'!D132</f>
-        <v/>
-      </c>
-      <c r="E132" s="13">
-        <f>'10_Source_Orders_3M'!E132</f>
-        <v/>
-      </c>
-      <c r="F132" s="6">
-        <f>'10_Source_Orders_3M'!F132</f>
-        <v/>
-      </c>
-      <c r="G132" s="5">
-        <f>'10_Source_Orders_3M'!G132</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="5">
-        <f>'10_Source_Orders_3M'!A133</f>
-        <v/>
-      </c>
-      <c r="B133" s="5">
-        <f>'10_Source_Orders_3M'!B133</f>
-        <v/>
-      </c>
-      <c r="C133" s="5">
-        <f>'10_Source_Orders_3M'!C133</f>
-        <v/>
-      </c>
-      <c r="D133" s="5">
-        <f>'10_Source_Orders_3M'!D133</f>
-        <v/>
-      </c>
-      <c r="E133" s="13">
-        <f>'10_Source_Orders_3M'!E133</f>
-        <v/>
-      </c>
-      <c r="F133" s="6">
-        <f>'10_Source_Orders_3M'!F133</f>
-        <v/>
-      </c>
-      <c r="G133" s="5">
-        <f>'10_Source_Orders_3M'!G133</f>
         <v/>
       </c>
     </row>
@@ -14666,7 +11909,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>501457853.0261627</v>
+        <v>501457853.0157034</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -14788,7 +12031,7 @@
         <v>30550000</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>27170000.00787945</v>
+        <v>27170000.00460673</v>
       </c>
       <c r="G12" s="6">
         <f>F12-E12</f>
@@ -14830,7 +12073,7 @@
         <v>113409768</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>108109767.0099526</v>
+        <v>108109767.0078188</v>
       </c>
       <c r="G13" s="6">
         <f>F13-E13</f>
@@ -14841,11 +12084,11 @@
         <v/>
       </c>
       <c r="I13" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>I39 / AB39</t>
+          <t>I38 / AB38</t>
         </is>
       </c>
     </row>
@@ -14883,11 +12126,11 @@
         <v/>
       </c>
       <c r="I14" s="5" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>I152 / AB152</t>
+          <t>I149 / AB149</t>
         </is>
       </c>
     </row>
@@ -14925,11 +12168,11 @@
         <v/>
       </c>
       <c r="I15" s="5" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>I169 / AB169</t>
+          <t>I166 / AB166</t>
         </is>
       </c>
     </row>
@@ -14956,7 +12199,7 @@
         <v>293798902</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>258666646.0016457</v>
+        <v>258666645.9970825</v>
       </c>
       <c r="G16" s="6">
         <f>F16-E16</f>
@@ -14967,11 +12210,11 @@
         <v/>
       </c>
       <c r="I16" s="5" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>I194 / AB194</t>
+          <t>I191 / AB191</t>
         </is>
       </c>
     </row>
@@ -15009,11 +12252,11 @@
         <v/>
       </c>
       <c r="I17" s="5" t="n">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>I276 / AB276</t>
+          <t>I265 / AB265</t>
         </is>
       </c>
     </row>
@@ -15051,11 +12294,11 @@
         <v/>
       </c>
       <c r="I18" s="5" t="n">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>I295 / AB295</t>
+          <t>I284 / AB284</t>
         </is>
       </c>
     </row>
@@ -15089,11 +12332,11 @@
         <v/>
       </c>
       <c r="I19" s="5" t="n">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>I298 / AB298</t>
+          <t>I287 / AB287</t>
         </is>
       </c>
     </row>
@@ -15116,7 +12359,7 @@
         <v>505757853</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>501457853.0261629</v>
+        <v>501457853.0157036</v>
       </c>
       <c r="G20" s="6">
         <f>F20-E20</f>
@@ -15127,11 +12370,11 @@
         <v/>
       </c>
       <c r="I20" s="5" t="n">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>I302 / AB302</t>
+          <t>I291 / AB291</t>
         </is>
       </c>
     </row>
@@ -15169,11 +12412,11 @@
         <v/>
       </c>
       <c r="I21" s="5" t="n">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>I309 / AB309</t>
+          <t>I298 / AB298</t>
         </is>
       </c>
     </row>
@@ -15200,7 +12443,7 @@
         <v>546148867.15</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>563914021.2406631</v>
+        <v>563593205.4394034</v>
       </c>
       <c r="G22" s="6">
         <f>F22-E22</f>
@@ -15211,11 +12454,11 @@
         <v/>
       </c>
       <c r="I22" s="5" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>I460 / AB460</t>
+          <t>I440 / AB440</t>
         </is>
       </c>
     </row>
@@ -15238,7 +12481,7 @@
         <v>85237132.84999999</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>63171978.76</v>
+        <v>63492794.56</v>
       </c>
       <c r="G23" s="6">
         <f>F23-E23</f>
@@ -15249,11 +12492,11 @@
         <v/>
       </c>
       <c r="I23" s="5" t="n">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>I461 / AB461</t>
+          <t>I441 / AB441</t>
         </is>
       </c>
     </row>
@@ -15276,7 +12519,7 @@
         <v>0.1560694125299533</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.1120241320139829</v>
+        <v>0.1126571327461233</v>
       </c>
       <c r="G24" s="6">
         <f>F24-E24</f>
@@ -15287,11 +12530,11 @@
         <v/>
       </c>
       <c r="I24" s="5" t="n">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>I462 / AB462</t>
+          <t>I442 / AB442</t>
         </is>
       </c>
     </row>
@@ -15325,11 +12568,11 @@
         <v/>
       </c>
       <c r="I25" s="5" t="n">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>I472 / AB472</t>
+          <t>I452 / AB452</t>
         </is>
       </c>
     </row>
@@ -15363,11 +12606,11 @@
         <v/>
       </c>
       <c r="I26" s="5" t="n">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>I473 / AB473</t>
+          <t>I453 / AB453</t>
         </is>
       </c>
     </row>
@@ -15406,11 +12649,11 @@
         <v/>
       </c>
       <c r="I27" s="5" t="n">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>I474 / AB474</t>
+          <t>I454 / AB454</t>
         </is>
       </c>
     </row>
@@ -15444,11 +12687,11 @@
         <v/>
       </c>
       <c r="I28" s="5" t="n">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>I477 / AB477</t>
+          <t>I457 / AB457</t>
         </is>
       </c>
     </row>
@@ -15471,7 +12714,7 @@
         <v>85237132.84999999</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>63171978.76</v>
+        <v>63492794.56</v>
       </c>
       <c r="G29" s="6">
         <f>F29-E29</f>
@@ -15482,11 +12725,11 @@
         <v/>
       </c>
       <c r="I29" s="5" t="n">
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>I478 / AB478</t>
+          <t>I458 / AB458</t>
         </is>
       </c>
     </row>
@@ -15513,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>63171978.76</v>
+        <v>63492794.56</v>
       </c>
       <c r="G30" s="6">
         <f>F30-E30</f>
@@ -15524,11 +12767,11 @@
         <v/>
       </c>
       <c r="I30" s="5" t="n">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>I479 / AB479</t>
+          <t>I459 / AB459</t>
         </is>
       </c>
     </row>
@@ -15551,7 +12794,7 @@
         <v>45080960.4</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>31178095.37389287</v>
+        <v>31178095.3777719</v>
       </c>
       <c r="G31" s="6">
         <f>F31-E31</f>
@@ -15562,11 +12805,11 @@
         <v/>
       </c>
       <c r="I31" s="5" t="n">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>I495 / AB495</t>
+          <t>I475 / AB475</t>
         </is>
       </c>
     </row>
@@ -15589,7 +12832,7 @@
         <v>40156172.45</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>31993883.38610713</v>
+        <v>32314699.18222811</v>
       </c>
       <c r="G32" s="6">
         <f>F32-E32</f>
@@ -15600,11 +12843,11 @@
         <v/>
       </c>
       <c r="I32" s="5" t="n">
-        <v>497</v>
+        <v>477</v>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>I497 / AB497</t>
+          <t>I477 / AB477</t>
         </is>
       </c>
     </row>
@@ -15627,7 +12870,7 @@
         <v>0.06360003619022277</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.05101992930173394</v>
+        <v>0.05153152706682673</v>
       </c>
       <c r="G33" s="6">
         <f>F33-E33</f>
@@ -15638,11 +12881,11 @@
         <v/>
       </c>
       <c r="I33" s="5" t="n">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>I498 / AB498</t>
+          <t>I478 / AB478</t>
         </is>
       </c>
     </row>
@@ -15665,7 +12908,7 @@
         <v>40156172.45</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>54092418.53610712</v>
+        <v>54413234.33222811</v>
       </c>
       <c r="G34" s="6">
         <f>F34-E34</f>
@@ -15676,11 +12919,11 @@
         <v/>
       </c>
       <c r="I34" s="5" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>I500 / AB500</t>
+          <t>I480 / AB480</t>
         </is>
       </c>
     </row>
@@ -15703,7 +12946,7 @@
         <v>0.06360003619022277</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.086259968387282</v>
+        <v>0.08677156615237482</v>
       </c>
       <c r="G35" s="6">
         <f>F35-E35</f>
@@ -15714,11 +12957,11 @@
         <v/>
       </c>
       <c r="I35" s="5" t="n">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>I501 / AB501</t>
+          <t>I481 / AB481</t>
         </is>
       </c>
     </row>
@@ -15752,11 +12995,11 @@
         <v/>
       </c>
       <c r="I36" s="5" t="n">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>I508 / AB508</t>
+          <t>I488 / AB488</t>
         </is>
       </c>
     </row>
@@ -15790,11 +13033,11 @@
         <v/>
       </c>
       <c r="I37" s="5" t="n">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>I509 / AB509</t>
+          <t>I489 / AB489</t>
         </is>
       </c>
     </row>
@@ -15990,7 +13233,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3208174.442857143</v>
+        <v>3080461.270952381</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
@@ -16012,7 +13255,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>2945486.035326664</v>
+        <v>10298268.19915018</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
@@ -16034,7 +13277,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>8660477.960361201</v>
+        <v>24920618.49075124</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -16056,7 +13299,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>9268774.713444706</v>
+        <v>11044595.67496808</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -16078,7 +13321,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>14089177.38587141</v>
+        <v>12651060.24080475</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -16100,7 +13343,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>16485911.39555095</v>
+        <v>16840968.47857952</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
@@ -16122,7 +13365,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>20643153.40577257</v>
+        <v>21259070.9007059</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
@@ -16144,7 +13387,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>23979424.97513761</v>
+        <v>17153971.63890618</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
@@ -16166,7 +13409,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>21232534.24430617</v>
+        <v>19773194.85023951</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
@@ -16188,7 +13431,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>30017252.04165062</v>
+        <v>24861930.3932784</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
@@ -16210,7 +13453,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>31870412.96156729</v>
+        <v>27968549.50484506</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
@@ -16232,7 +13475,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>38417537.23536131</v>
+        <v>35342841.76083907</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
@@ -16254,7 +13497,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>35478557.11787304</v>
+        <v>30823036.89110636</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
@@ -16276,7 +13519,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>33749485.0879524</v>
+        <v>32016185.05832859</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
@@ -16298,7 +13541,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>28477081.03691748</v>
+        <v>26848740.96685081</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
@@ -16320,7 +13563,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>25834726.82630295</v>
+        <v>23300575.31623628</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
@@ -16342,7 +13585,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>18470721.62641472</v>
+        <v>17197990.11634805</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
@@ -16364,7 +13607,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>21807506.74504805</v>
+        <v>22446419.55108138</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
@@ -16386,7 +13629,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>15249589.74607027</v>
+        <v>10601806.8521036</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
@@ -16408,7 +13651,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>7723682.16648138</v>
+        <v>8350089.772514713</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
@@ -16430,7 +13673,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>23574224.23447027</v>
+        <v>24637776.5005036</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
@@ -16452,7 +13695,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>5587448.632869981</v>
+        <v>5817816.966203314</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
@@ -16474,7 +13717,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>4173720.89985887</v>
+        <v>3279069.233192204</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
@@ -16496,7 +13739,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>3033344.05385887</v>
+        <v>2859802.387192203</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
@@ -16518,7 +13761,7 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>477296.0005011495</v>
+        <v>308626.9264270754</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
@@ -16540,7 +13783,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>3504157.514945594</v>
+        <v>3335488.44087152</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
@@ -16562,7 +13805,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>1838854.97050115</v>
+        <v>966685.0738344828</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
@@ -16584,7 +13827,7 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>34553.33</v>
+        <v>0</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
@@ -16650,7 +13893,7 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>17276.68</v>
+        <v>0</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
@@ -16672,7 +13915,7 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>144394</v>
+        <v>0</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
@@ -16694,7 +13937,7 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>32741012.29</v>
+        <v>44750308.29</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
